--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/11511.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/11511.webp</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/11817.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/11817.png</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12026.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12026.jpg</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12027.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12027.webp</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12028.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12028.webp</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12174.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12174.webp</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10043.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10043.webp</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10092.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10092.webp</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10115.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10115.webp</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10217.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10217.webp</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10255.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10255.jpg</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10364.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10364.webp</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10395.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10395.webp</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10396.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10396.webp</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10652.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10652.webp</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10745.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10745.webp</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10866.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10866.webp</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10877.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10877.webp</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10900.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10900.webp</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10910.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10910.webp</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10914.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10914.webp</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10915.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10915.webp</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10946.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10946.webp</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10957.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10957.webp</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10978.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10978.webp</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11005.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11005.webp</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11054.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11054.jpg</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11055.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11055.webp</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11059.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11059.webp</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11061.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11061.webp</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11062.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11062.webp</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11077.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11077.webp</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11091.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11091.webp</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11110.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11110.webp</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11116.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11116.webp</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11121.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11121.webp</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11124.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11124.png</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11125.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11125.webp</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11132.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11132.webp</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11136.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11136.webp</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11137.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11137.webp</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11160.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11160.webp</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11175.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11175.webp</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11259.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11259.webp</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11325.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11325.webp</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11326.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11326.webp</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11329.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11329.jpg</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11331.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11331.webp</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11332.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11332.webp</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11334.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11334.webp</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11335.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11335.jpg</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11337.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11337.webp</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11338.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11338.webp</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11340.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11340.webp</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11341.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11341.webp</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11342.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11342.webp</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11400.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11400.jpg</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11401.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11401.webp</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12052.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12052.webp</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12091.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12091.webp</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.webp</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10044.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10044.webp</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10068.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10068.webp</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10073.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10073.webp</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11803.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11803.png</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11848.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11848.webp</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11861.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11861.webp</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11902.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11902.webp</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11939.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11939.webp</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11996.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11996.webp</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.webp</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12039.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12039.webp</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12071.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12071.webp</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12086.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12086.webp</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12072.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12072.png</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10277.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10277.webp</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10278.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10278.webp</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10873.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10873.webp</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11480.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11480.webp</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11895.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11895.webp</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.webp</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11940.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11940.webp</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11941.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11941.webp</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/10944.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/10944.webp</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11517.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11517.webp</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11594.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11594.webp</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11622.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11622.webp</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11678.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11678.jpg</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11800.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11800.webp</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11809.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11809.jpg</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11815.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11815.webp</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11819.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11819.webp</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11868.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11868.webp</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11870.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11870.webp</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11871.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11871.webp</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11880.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11880.webp</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11906.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11906.webp</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11920.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11920.webp</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11971.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11971.webp</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10276.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10276.webp</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10504.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10504.webp</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10982.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10982.webp</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11127.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11127.webp</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11490.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11490.webp</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11505.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11505.webp</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11555.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11555.webp</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11691.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11691.webp</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11704.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11704.webp</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11719.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11719.webp</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11726.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11726.webp</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11754.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11754.jpg</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11757.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11757.webp</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11227,7 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11758.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11758.webp</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11760.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11760.webp</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11762.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11762.webp</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11763.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11763.webp</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11767.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11767.webp</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.webp</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11771.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11771.webp</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11772.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11772.webp</t>
         </is>
       </c>
     </row>
@@ -11920,7 +11920,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11774.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11774.webp</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11777.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11777.webp</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.webp</t>
         </is>
       </c>
     </row>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11780.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11780.webp</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11781.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11781.webp</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11782.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11782.webp</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11783.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11783.webp</t>
         </is>
       </c>
     </row>
@@ -12613,7 +12613,7 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.webp</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.webp</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.webp</t>
         </is>
       </c>
     </row>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11790.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11790.webp</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11791.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11791.webp</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11794.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11794.webp</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11795.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11795.webp</t>
         </is>
       </c>
     </row>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11952.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11952.webp</t>
         </is>
       </c>
     </row>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11953.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11953.webp</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.webp</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/12093.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/12093.webp</t>
         </is>
       </c>
     </row>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10097.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10097.png</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10883.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10883.webp</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11094.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11094.webp</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="V176" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11104.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11104.webp</t>
         </is>
       </c>
     </row>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.webp</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.webp</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11479.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11479.webp</t>
         </is>
       </c>
     </row>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11483.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11483.webp</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11508.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11508.webp</t>
         </is>
       </c>
     </row>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.webp</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11641.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11641.webp</t>
         </is>
       </c>
     </row>
@@ -14692,7 +14692,7 @@
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11662.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11662.png</t>
         </is>
       </c>
     </row>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11693.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11693.png</t>
         </is>
       </c>
     </row>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11713.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11713.webp</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11728.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11728.webp</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11730.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11730.webp</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11828.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11828.webp</t>
         </is>
       </c>
     </row>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11836.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11836.png</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11929.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11929.webp</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11943.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11943.png</t>
         </is>
       </c>
     </row>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12035.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12035.webp</t>
         </is>
       </c>
     </row>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12054.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12054.jpg</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.webp</t>
         </is>
       </c>
     </row>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.webp</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.webp</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.webp</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16155,7 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11528.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11528.webp</t>
         </is>
       </c>
     </row>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.webp</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16309,7 @@
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.jpg</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.webp</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16463,7 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.webp</t>
         </is>
       </c>
     </row>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.webp</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11687.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11687.webp</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.webp</t>
         </is>
       </c>
     </row>
@@ -16925,7 +16925,7 @@
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11732.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11732.jpg</t>
         </is>
       </c>
     </row>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.webp</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.webp</t>
         </is>
       </c>
     </row>
@@ -17387,7 +17387,7 @@
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11743.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11743.webp</t>
         </is>
       </c>
     </row>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.png</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.webp</t>
         </is>
       </c>
     </row>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.webp</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.webp</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.webp</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.webp</t>
         </is>
       </c>
     </row>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.webp</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.webp</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.jpg</t>
         </is>
       </c>
     </row>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.webp</t>
         </is>
       </c>
     </row>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11961.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11961.webp</t>
         </is>
       </c>
     </row>
@@ -18696,7 +18696,7 @@
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12002.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12002.webp</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.webp</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12084.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12084.webp</t>
         </is>
       </c>
     </row>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.jpg</t>
         </is>
       </c>
     </row>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.webp</t>
         </is>
       </c>
     </row>
@@ -19081,7 +19081,7 @@
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.webp</t>
         </is>
       </c>
     </row>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.webp</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.webp</t>
         </is>
       </c>
     </row>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11518.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11518.jpg</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.webp</t>
         </is>
       </c>
     </row>
@@ -19466,7 +19466,7 @@
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.webp</t>
         </is>
       </c>
     </row>
@@ -19543,7 +19543,7 @@
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.webp</t>
         </is>
       </c>
     </row>
@@ -19620,7 +19620,7 @@
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11698.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11698.webp</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.webp</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.webp</t>
         </is>
       </c>
     </row>
@@ -19851,7 +19851,7 @@
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.webp</t>
         </is>
       </c>
     </row>
@@ -19928,7 +19928,7 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.webp</t>
         </is>
       </c>
     </row>
@@ -20005,7 +20005,7 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.webp</t>
         </is>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.webp</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10102.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10102.webp</t>
         </is>
       </c>
     </row>
@@ -20236,7 +20236,7 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.webp</t>
         </is>
       </c>
     </row>
@@ -20313,7 +20313,7 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.webp</t>
         </is>
       </c>
     </row>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.webp</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.jpg</t>
         </is>
       </c>
     </row>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.webp</t>
         </is>
       </c>
     </row>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.png</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.webp</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20852,7 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.webp</t>
         </is>
       </c>
     </row>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.webp</t>
         </is>
       </c>
     </row>
@@ -21006,7 +21006,7 @@
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.webp</t>
         </is>
       </c>
     </row>
@@ -21160,7 +21160,7 @@
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.webp</t>
         </is>
       </c>
     </row>
@@ -21237,7 +21237,7 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.webp</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.webp</t>
         </is>
       </c>
     </row>
@@ -21391,7 +21391,7 @@
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.webp</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.webp</t>
         </is>
       </c>
     </row>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.webp</t>
         </is>
       </c>
     </row>
@@ -21622,7 +21622,7 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.webp</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.png</t>
         </is>
       </c>
     </row>
@@ -21853,7 +21853,7 @@
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.webp</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.webp</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.webp</t>
         </is>
       </c>
     </row>
@@ -22084,7 +22084,7 @@
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.webp</t>
         </is>
       </c>
     </row>
@@ -22161,7 +22161,7 @@
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.webp</t>
         </is>
       </c>
     </row>
@@ -22238,7 +22238,7 @@
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.webp</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.webp</t>
         </is>
       </c>
     </row>
@@ -22392,7 +22392,7 @@
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.webp</t>
         </is>
       </c>
     </row>
@@ -22469,7 +22469,7 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.webp</t>
         </is>
       </c>
     </row>
@@ -22546,7 +22546,7 @@
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.webp</t>
         </is>
       </c>
     </row>
@@ -22623,7 +22623,7 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.webp</t>
         </is>
       </c>
     </row>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.webp</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.jpg</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.webp</t>
         </is>
       </c>
     </row>
@@ -22931,7 +22931,7 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.webp</t>
         </is>
       </c>
     </row>
@@ -23008,7 +23008,7 @@
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.webp</t>
         </is>
       </c>
     </row>
@@ -23085,7 +23085,7 @@
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.webp</t>
         </is>
       </c>
     </row>
@@ -23162,7 +23162,7 @@
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.webp</t>
         </is>
       </c>
     </row>
@@ -23239,7 +23239,7 @@
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.webp</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.webp</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.webp</t>
         </is>
       </c>
     </row>
@@ -23470,7 +23470,7 @@
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.webp</t>
         </is>
       </c>
     </row>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.webp</t>
         </is>
       </c>
     </row>
@@ -23624,7 +23624,7 @@
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.webp</t>
         </is>
       </c>
     </row>
@@ -23701,7 +23701,7 @@
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.webp</t>
         </is>
       </c>
     </row>
@@ -23778,7 +23778,7 @@
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.webp</t>
         </is>
       </c>
     </row>
@@ -23855,7 +23855,7 @@
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.webp</t>
         </is>
       </c>
     </row>
@@ -24009,7 +24009,7 @@
       </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.webp</t>
         </is>
       </c>
     </row>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.webp</t>
         </is>
       </c>
     </row>
@@ -24163,7 +24163,7 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.webp</t>
         </is>
       </c>
     </row>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.webp</t>
         </is>
       </c>
     </row>
@@ -24317,7 +24317,7 @@
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.webp</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.webp</t>
         </is>
       </c>
     </row>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="V312" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.webp</t>
         </is>
       </c>
     </row>
@@ -24548,7 +24548,7 @@
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.webp</t>
         </is>
       </c>
     </row>
@@ -24702,7 +24702,7 @@
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.webp</t>
         </is>
       </c>
     </row>
@@ -24856,7 +24856,7 @@
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.webp</t>
         </is>
       </c>
     </row>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.webp</t>
         </is>
       </c>
     </row>
@@ -25010,7 +25010,7 @@
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.webp</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.webp</t>
         </is>
       </c>
     </row>
@@ -25318,7 +25318,7 @@
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.webp</t>
         </is>
       </c>
     </row>
@@ -25472,7 +25472,7 @@
       </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.webp</t>
         </is>
       </c>
     </row>
@@ -25549,7 +25549,7 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.webp</t>
         </is>
       </c>
     </row>
@@ -25626,7 +25626,7 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.webp</t>
         </is>
       </c>
     </row>
@@ -25703,7 +25703,7 @@
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.webp</t>
         </is>
       </c>
     </row>
@@ -25780,7 +25780,7 @@
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.png</t>
         </is>
       </c>
     </row>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="V330" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.webp</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="V331" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.webp</t>
         </is>
       </c>
     </row>
@@ -26011,7 +26011,7 @@
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.webp</t>
         </is>
       </c>
     </row>
@@ -26088,7 +26088,7 @@
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.webp</t>
         </is>
       </c>
     </row>
@@ -26165,7 +26165,7 @@
       </c>
       <c r="V334" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.webp</t>
         </is>
       </c>
     </row>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.webp</t>
         </is>
       </c>
     </row>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="V338" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.webp</t>
         </is>
       </c>
     </row>
@@ -26550,7 +26550,7 @@
       </c>
       <c r="V339" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12104.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12104.webp</t>
         </is>
       </c>
     </row>
@@ -26627,7 +26627,7 @@
       </c>
       <c r="V340" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.webp</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="V341" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.webp</t>
         </is>
       </c>
     </row>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="V342" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.webp</t>
         </is>
       </c>
     </row>
@@ -26858,7 +26858,7 @@
       </c>
       <c r="V343" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.webp</t>
         </is>
       </c>
     </row>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="V345" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.webp</t>
         </is>
       </c>
     </row>
@@ -27166,7 +27166,7 @@
       </c>
       <c r="V347" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.webp</t>
         </is>
       </c>
     </row>
@@ -27397,7 +27397,7 @@
       </c>
       <c r="V350" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.webp</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="V351" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.webp</t>
         </is>
       </c>
     </row>
@@ -27551,7 +27551,7 @@
       </c>
       <c r="V352" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.webp</t>
         </is>
       </c>
     </row>
@@ -27628,7 +27628,7 @@
       </c>
       <c r="V353" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.webp</t>
         </is>
       </c>
     </row>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="V354" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
         </is>
       </c>
     </row>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="V355" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12162.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12162.webp</t>
         </is>
       </c>
     </row>
@@ -27859,7 +27859,7 @@
       </c>
       <c r="V356" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.webp</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/11511.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/11511.jpg</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12027.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12027.png</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12174.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12174.png</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10043.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10043.jpg</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10092.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10092.jpg</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10115.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10115.jpg</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10217.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10217.jpg</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10364.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10364.jpg</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10395.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10395.jpg</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10396.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10396.jpg</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10652.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10652.jpg</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10745.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10745.jpg</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10877.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10877.jpg</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10900.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10900.jpg</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10910.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10910.jpg</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10914.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10914.jpg</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10915.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10915.jpg</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10946.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10946.jpg</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10957.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10957.jpg</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10978.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10978.png</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11005.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11005.jpg</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11055.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11055.jpg</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11059.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11059.jpg</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11061.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11061.jpg</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11062.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11062.jpg</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11077.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11077.jpg</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11110.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11110.jpg</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11116.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11116.jpg</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11125.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11125.jpg</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11132.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11132.jpg</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11136.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11136.png</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11137.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11137.jpg</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11160.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11160.jpg</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11175.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11175.jpg</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11259.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11259.jpg</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11325.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11325.jpg</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11331.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11331.jpg</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11332.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11332.jpg</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11334.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11334.png</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11337.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11337.png</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11338.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11338.png</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11340.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11340.jpg</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11341.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11341.jpg</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11342.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11342.jpg</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11401.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11401.jpg</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12052.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12052.jpg</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12091.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12091.jpg</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.jpg</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10073.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10073.png</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11803.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11803.webp</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11848.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11848.png</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11861.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11861.jpg</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11902.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11902.png</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11939.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11939.png</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.jpg</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12039.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12039.jpg</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12086.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12086.jpg</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12072.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12072.jpg</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10277.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10277.jpg</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10873.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10873.jpg</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11480.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11480.jpg</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11895.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11895.jpg</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.png</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11951.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11951.webp</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/10944.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/10944.png</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11517.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11517.png</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11594.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11594.jpg</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11800.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11800.jpg</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11815.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11815.jpg</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11819.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11819.jpg</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11868.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11868.jpg</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11880.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11880.jpg</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11906.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11906.jpg</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11920.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11920.jpg</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11968.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11968.jpg</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11971.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11971.png</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10276.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10276.jpg</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10504.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10504.jpg</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10982.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/10982.jpg</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11127.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11127.jpg</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11490.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11490.jpg</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11505.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11505.jpg</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11555.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11555.jpg</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11691.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11691.jpg</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11704.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11704.jpg</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11719.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11719.png</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11726.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11726.png</t>
         </is>
       </c>
     </row>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11750.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11750.png</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11757.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11757.jpg</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11227,7 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11758.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11758.jpg</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11762.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11762.png</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11763.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11763.png</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11767.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11767.png</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.jpg</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11771.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11771.png</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11772.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11772.jpg</t>
         </is>
       </c>
     </row>
@@ -11920,7 +11920,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11774.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11774.png</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11777.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11777.jpg</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.jpg</t>
         </is>
       </c>
     </row>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11780.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11780.jpg</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11781.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11781.jpg</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11782.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11782.jpg</t>
         </is>
       </c>
     </row>
@@ -12613,7 +12613,7 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.png</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.jpg</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.jpg</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11794.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11794.jpg</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11795.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11795.jpg</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11796.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11796.png</t>
         </is>
       </c>
     </row>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11952.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11952.jpg</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.png</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/12093.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/12093.jpg</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10883.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10883.jpg</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11094.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11094.jpg</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="V176" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11104.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11104.jpg</t>
         </is>
       </c>
     </row>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.png</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.png</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11479.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11479.jpg</t>
         </is>
       </c>
     </row>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11483.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11483.jpg</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11508.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11508.jpg</t>
         </is>
       </c>
     </row>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.png</t>
         </is>
       </c>
     </row>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11713.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11713.jpg</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11728.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11728.jpg</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11730.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11730.jpg</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11828.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11828.jpg</t>
         </is>
       </c>
     </row>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11836.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11836.jpg</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11929.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11929.jpg</t>
         </is>
       </c>
     </row>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12035.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12035.png</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.jpg</t>
         </is>
       </c>
     </row>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.jpg</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.jpg</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.jpg</t>
         </is>
       </c>
     </row>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.jpg</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.jpg</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16463,7 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.jpg</t>
         </is>
       </c>
     </row>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.jpg</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11686.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11686.png</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.jpg</t>
         </is>
       </c>
     </row>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.jpg</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.jpg</t>
         </is>
       </c>
     </row>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.jpg</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.jpg</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.jpg</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.jpg</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.jpg</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.jpg</t>
         </is>
       </c>
     </row>
@@ -18157,7 +18157,7 @@
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11912.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11912.jpg</t>
         </is>
       </c>
     </row>
@@ -18311,7 +18311,7 @@
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11958.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11958.jpg</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.jpg</t>
         </is>
       </c>
     </row>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.png</t>
         </is>
       </c>
     </row>
@@ -19081,7 +19081,7 @@
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.jpg</t>
         </is>
       </c>
     </row>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.jpg</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.jpg</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.jpg</t>
         </is>
       </c>
     </row>
@@ -19466,7 +19466,7 @@
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.jpg</t>
         </is>
       </c>
     </row>
@@ -19543,7 +19543,7 @@
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.jpg</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.jpg</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.png</t>
         </is>
       </c>
     </row>
@@ -19851,7 +19851,7 @@
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.jpg</t>
         </is>
       </c>
     </row>
@@ -19928,7 +19928,7 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.jpg</t>
         </is>
       </c>
     </row>
@@ -20005,7 +20005,7 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.jpg</t>
         </is>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.jpg</t>
         </is>
       </c>
     </row>
@@ -20236,7 +20236,7 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.jpg</t>
         </is>
       </c>
     </row>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
         </is>
       </c>
     </row>
@@ -20544,7 +20544,7 @@
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.jpg</t>
         </is>
       </c>
     </row>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
         </is>
       </c>
     </row>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.png</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20852,7 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.png</t>
         </is>
       </c>
     </row>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
         </is>
       </c>
     </row>
@@ -21160,7 +21160,7 @@
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
         </is>
       </c>
     </row>
@@ -21237,7 +21237,7 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.png</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.jpg</t>
         </is>
       </c>
     </row>
@@ -21622,7 +21622,7 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
         </is>
       </c>
     </row>
@@ -21776,7 +21776,7 @@
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.jpg</t>
         </is>
       </c>
     </row>
@@ -21853,7 +21853,7 @@
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.jpg</t>
         </is>
       </c>
     </row>
@@ -22084,7 +22084,7 @@
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
         </is>
       </c>
     </row>
@@ -22161,7 +22161,7 @@
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
         </is>
       </c>
     </row>
@@ -22238,7 +22238,7 @@
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.png</t>
         </is>
       </c>
     </row>
@@ -22392,7 +22392,7 @@
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
         </is>
       </c>
     </row>
@@ -22469,7 +22469,7 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
         </is>
       </c>
     </row>
@@ -22623,7 +22623,7 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
         </is>
       </c>
     </row>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.png</t>
         </is>
       </c>
     </row>
@@ -22931,7 +22931,7 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.jpg</t>
         </is>
       </c>
     </row>
@@ -23008,7 +23008,7 @@
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
         </is>
       </c>
     </row>
@@ -23085,7 +23085,7 @@
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
         </is>
       </c>
     </row>
@@ -23162,7 +23162,7 @@
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
         </is>
       </c>
     </row>
@@ -23239,7 +23239,7 @@
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.jpg</t>
         </is>
       </c>
     </row>
@@ -23470,7 +23470,7 @@
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.jpg</t>
         </is>
       </c>
     </row>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.jpg</t>
         </is>
       </c>
     </row>
@@ -23624,7 +23624,7 @@
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.png</t>
         </is>
       </c>
     </row>
@@ -23701,7 +23701,7 @@
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.png</t>
         </is>
       </c>
     </row>
@@ -23855,7 +23855,7 @@
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
         </is>
       </c>
     </row>
@@ -24009,7 +24009,7 @@
       </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
         </is>
       </c>
     </row>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
         </is>
       </c>
     </row>
@@ -24163,7 +24163,7 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
         </is>
       </c>
     </row>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
         </is>
       </c>
     </row>
@@ -24317,7 +24317,7 @@
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.jpg</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.jpg</t>
         </is>
       </c>
     </row>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="V312" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.png</t>
         </is>
       </c>
     </row>
@@ -24548,7 +24548,7 @@
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.png</t>
         </is>
       </c>
     </row>
@@ -24702,7 +24702,7 @@
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
         </is>
       </c>
     </row>
@@ -24779,7 +24779,7 @@
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.jpg</t>
         </is>
       </c>
     </row>
@@ -24856,7 +24856,7 @@
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.jpg</t>
         </is>
       </c>
     </row>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.png</t>
         </is>
       </c>
     </row>
@@ -25010,7 +25010,7 @@
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
         </is>
       </c>
     </row>
@@ -25318,7 +25318,7 @@
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
         </is>
       </c>
     </row>
@@ -25472,7 +25472,7 @@
       </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.jpg</t>
         </is>
       </c>
     </row>
@@ -25549,7 +25549,7 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
         </is>
       </c>
     </row>
@@ -25626,7 +25626,7 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.jpg</t>
         </is>
       </c>
     </row>
@@ -25703,7 +25703,7 @@
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.png</t>
         </is>
       </c>
     </row>
@@ -25780,7 +25780,7 @@
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
         </is>
       </c>
     </row>
@@ -26088,7 +26088,7 @@
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
         </is>
       </c>
     </row>
@@ -26165,7 +26165,7 @@
       </c>
       <c r="V334" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
         </is>
       </c>
     </row>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.png</t>
         </is>
       </c>
     </row>
@@ -26396,7 +26396,7 @@
       </c>
       <c r="V337" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.jpg</t>
         </is>
       </c>
     </row>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="V338" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
         </is>
       </c>
     </row>
@@ -26627,7 +26627,7 @@
       </c>
       <c r="V340" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="V341" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
         </is>
       </c>
     </row>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="V342" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
         </is>
       </c>
     </row>
@@ -26858,7 +26858,7 @@
       </c>
       <c r="V343" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
         </is>
       </c>
     </row>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="V345" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.png</t>
         </is>
       </c>
     </row>
@@ -27166,7 +27166,7 @@
       </c>
       <c r="V347" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.jpg</t>
         </is>
       </c>
     </row>
@@ -27320,7 +27320,7 @@
       </c>
       <c r="V349" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.webp</t>
         </is>
       </c>
     </row>
@@ -27551,7 +27551,7 @@
       </c>
       <c r="V352" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
         </is>
       </c>
     </row>
@@ -27628,7 +27628,7 @@
       </c>
       <c r="V353" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
         </is>
       </c>
     </row>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="V354" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.jpg</t>
         </is>
       </c>
     </row>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="V355" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12162.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12162.png</t>
         </is>
       </c>
     </row>
@@ -27859,7 +27859,7 @@
       </c>
       <c r="V356" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.png</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/11817.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/11817.jpg</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12027.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12027.webp</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12028.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12028.jpg</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10255.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10255.webp</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10866.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10866.jpg</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10900.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10900.webp</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10901.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10901.webp</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10957.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10957.png</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10978.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10978.jpg</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11005.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11005.webp</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11054.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11054.png</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11055.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11055.webp</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11091.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11091.jpg</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11092.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11092.jpg</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11120.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11120.jpg</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11121.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11121.jpg</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11124.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11124.webp</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11136.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11136.jpg</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11326.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11326.jpg</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11329.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11329.png</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11334.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11334.jpg</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11337.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11337.jpg</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11338.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11338.jpg</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11339.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11339.png</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11400.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11400.webp</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11402.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11402.webp</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12091.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12091.webp</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12158.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12158.jpg</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12175.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12175.jpg</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.webp</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10044.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10044.jpg</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10073.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10073.jpg</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11848.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11848.jpg</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11902.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11902.jpg</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11939.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11939.webp</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11996.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11996.jpg</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.png</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12071.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12071.jpg</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10278.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10278.jpg</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10873.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10873.png</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.jpg</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11940.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11940.jpg</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11941.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11941.jpg</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11951.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11951.png</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11809.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11809.png</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11868.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11868.png</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11490.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11490.png</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.png</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11796.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11796.jpg</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12053.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12053.webp</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.png</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16309,7 @@
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.webp</t>
         </is>
       </c>
     </row>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.png</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.webp</t>
         </is>
       </c>
     </row>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.jpg</t>
         </is>
       </c>
     </row>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.jpg</t>
         </is>
       </c>
     </row>
@@ -19928,7 +19928,7 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.webp</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20852,7 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.png</t>
         </is>
       </c>
     </row>
@@ -25549,7 +25549,7 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.webp</t>
         </is>
       </c>
     </row>
@@ -25626,7 +25626,7 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.webp</t>
         </is>
       </c>
     </row>
@@ -26011,7 +26011,7 @@
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
         </is>
       </c>
     </row>
@@ -26319,7 +26319,7 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12028.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12028.webp</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10745.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10745.png</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10900.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10900.jpg</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10901.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10901.jpg</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10957.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/10957.jpg</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11055.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11055.jpg</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11120.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11120.webp</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11124.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11124.jpg</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11136.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11136.png</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11339.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/11339.jpg</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12158.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12158.webp</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.jpg</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10044.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10044.png</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11902.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11902.png</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11939.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11939.jpg</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11996.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11996.webp</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.jpg</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12071.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12071.webp</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10873.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10873.jpg</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11480.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11480.webp</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.png</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11941.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11941.webp</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11553.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11553.jpg</t>
         </is>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11753.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11753.png</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.png</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11791.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11791.jpg</t>
         </is>
       </c>
     </row>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11966.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11966.png</t>
         </is>
       </c>
     </row>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.webp</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.webp</t>
         </is>
       </c>
     </row>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.webp</t>
         </is>
       </c>
     </row>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.jpg</t>
         </is>
       </c>
     </row>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.jpg</t>
         </is>
       </c>
     </row>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.webp</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.webp</t>
         </is>
       </c>
     </row>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.webp</t>
         </is>
       </c>
     </row>
@@ -18619,7 +18619,7 @@
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11962.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11962.webp</t>
         </is>
       </c>
     </row>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.webp</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.webp</t>
         </is>
       </c>
     </row>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.webp</t>
         </is>
       </c>
     </row>
@@ -20313,7 +20313,7 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.jpg</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.webp</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20852,7 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.png</t>
         </is>
       </c>
     </row>
@@ -21391,7 +21391,7 @@
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.jpg</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
         </is>
       </c>
     </row>
@@ -25549,7 +25549,7 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
         </is>
       </c>
     </row>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="V354" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
         </is>
       </c>
     </row>
@@ -27859,7 +27859,7 @@
       </c>
       <c r="V356" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.jpg</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF356"/>
+  <dimension ref="A1:AF353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,7 +909,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12027.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12027.png</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10037.png</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10044.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/10044.jpg</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.webp</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12071.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/12071.jpg</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10278.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10278.webp</t>
         </is>
       </c>
     </row>
@@ -10155,34 +10155,34 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>11127</v>
+        <v>11490</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FARINHA DE LIMAO 20G</t>
+          <t>TRIGO PARA KIBE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J127" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>2.5</v>
+        <v>9.9</v>
       </c>
       <c r="O127" t="n">
-        <v>2.5</v>
+        <v>9.9</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -10217,31 +10217,31 @@
         </is>
       </c>
       <c r="T127" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11127.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11490.png</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>11490</v>
+        <v>11505</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TRIGO PARA KIBE</t>
+          <t>TAPIOCA GRANULADA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -10277,10 +10277,10 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>9.9</v>
+        <v>12.9</v>
       </c>
       <c r="O128" t="n">
-        <v>9.9</v>
+        <v>12.9</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -10303,22 +10303,22 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11490.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11505.jpg</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>11505</v>
+        <v>11553</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TAPIOCA GRANULADA</t>
+          <t>POLVILHO DOCE (FECULA MANDIOCA)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="O129" t="n">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -10380,22 +10380,22 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11505.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11553.jpg</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>11553</v>
+        <v>11555</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>POLVILHO DOCE (FECULA MANDIOCA)</t>
+          <t>POLVILHO AZEDO</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -10431,10 +10431,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="O130" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -10457,22 +10457,22 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11553.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11555.jpg</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>11555</v>
+        <v>11691</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>POLVILHO AZEDO</t>
+          <t>GOMA DO NORTE OLINDA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -10534,22 +10534,22 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11555.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11691.jpg</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>11691</v>
+        <v>11704</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>GOMA DO NORTE OLINDA</t>
+          <t>GERMEM DE TRIGO TOSTADO</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="O132" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
@@ -10611,22 +10611,22 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11691.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11704.jpg</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>11704</v>
+        <v>11719</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>GERMEM DE TRIGO TOSTADO</t>
+          <t>FUBA MIMOSO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -10662,10 +10662,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>32</v>
+        <v>9.5</v>
       </c>
       <c r="O133" t="n">
-        <v>32</v>
+        <v>9.5</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
@@ -10688,22 +10688,22 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11704.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11719.png</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>11719</v>
+        <v>11726</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FUBA MIMOSO</t>
+          <t>FLOCOS DE ARROZ BOLINHA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -10739,10 +10739,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>9.5</v>
+        <v>31</v>
       </c>
       <c r="O134" t="n">
-        <v>9.5</v>
+        <v>31</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -10765,22 +10765,22 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11719.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11726.png</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>11726</v>
+        <v>11750</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>351</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FLOCOS DE ARROZ BOLINHA</t>
+          <t>FECULA DE BATATA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>31</v>
+        <v>13.8</v>
       </c>
       <c r="O135" t="n">
-        <v>31</v>
+        <v>13.8</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
@@ -10842,22 +10842,22 @@
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11726.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11750.jpg</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>11750</v>
+        <v>11753</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FECULA DE BATATA</t>
+          <t>FARINHA QUINUA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -10893,10 +10893,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>13.8</v>
+        <v>65</v>
       </c>
       <c r="O136" t="n">
-        <v>13.8</v>
+        <v>65</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -10919,22 +10919,22 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11750.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11753.png</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>11753</v>
+        <v>11754</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FARINHA QUINUA</t>
+          <t>FARINHA PANKO</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -10970,10 +10970,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="O137" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -10996,22 +10996,22 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11753.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11754.jpg</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>11754</v>
+        <v>11757</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>133</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FARINHA PANKO</t>
+          <t>FARINHA DE TRIGO INTEGRAL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>35</v>
+        <v>10.8</v>
       </c>
       <c r="O138" t="n">
-        <v>35</v>
+        <v>10.8</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
@@ -11073,37 +11073,37 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11754.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11757.jpg</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>11757</v>
+        <v>11758</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO INTEGRAL</t>
+          <t>FARINHA DE SORGO 100G</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H139" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I139" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J139" t="n">
         <v>100</v>
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>10.8</v>
+        <v>2.5</v>
       </c>
       <c r="O139" t="n">
-        <v>10.8</v>
+        <v>2.5</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
@@ -11141,46 +11141,46 @@
         </is>
       </c>
       <c r="T139" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11757.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11758.jpg</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>11758</v>
+        <v>11760</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FARINHA DE SORGO 100G</t>
+          <t>FARINHA DE SOJA</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H140" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I140" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J140" t="n">
         <v>100</v>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>2.5</v>
+        <v>23.5</v>
       </c>
       <c r="O140" t="n">
-        <v>2.5</v>
+        <v>23.5</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -11218,31 +11218,31 @@
         </is>
       </c>
       <c r="T140" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11758.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11760.webp</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>11760</v>
+        <v>11762</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FARINHA DE SOJA</t>
+          <t>FARINHA DE ROSCA</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>23.5</v>
+        <v>9.9</v>
       </c>
       <c r="O141" t="n">
-        <v>23.5</v>
+        <v>9.9</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -11304,22 +11304,22 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11760.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11762.png</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>11762</v>
+        <v>11763</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FARINHA DE ROSCA</t>
+          <t>FARINHA DE MILHO BRANCA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -11355,10 +11355,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>9.9</v>
+        <v>32</v>
       </c>
       <c r="O142" t="n">
-        <v>9.9</v>
+        <v>32</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -11381,22 +11381,22 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11762.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11763.png</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>11763</v>
+        <v>11765</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FARINHA DE MILHO BRANCA</t>
+          <t>FARINHA DE MILHO AMARELA</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="O143" t="n">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
@@ -11458,22 +11458,22 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11763.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11765.png</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>11765</v>
+        <v>11767</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FARINHA DE MILHO AMARELA</t>
+          <t>FARINHA DE MARACUJA</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -11509,10 +11509,10 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>16.5</v>
+        <v>55</v>
       </c>
       <c r="O144" t="n">
-        <v>16.5</v>
+        <v>55</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
@@ -11535,22 +11535,22 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11765.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11767.webp</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>11767</v>
+        <v>11769</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FARINHA DE MARACUJA</t>
+          <t>FARINHA DE MANDIOCA GROSSA</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>55</v>
+        <v>7.8</v>
       </c>
       <c r="O145" t="n">
-        <v>55</v>
+        <v>7.8</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -11612,22 +11612,22 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11767.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.jpg</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>11769</v>
+        <v>11771</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FARINHA DE MANDIOCA GROSSA</t>
+          <t>FARINHA DE MANDIOCA FINA</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -11689,22 +11689,22 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11771.png</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>11771</v>
+        <v>11772</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FARINHA DE MANDIOCA FINA</t>
+          <t>FARINHA DE MACA (FIBRA)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -11740,10 +11740,10 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>7.8</v>
+        <v>68</v>
       </c>
       <c r="O147" t="n">
-        <v>7.8</v>
+        <v>68</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
@@ -11766,22 +11766,22 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11771.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11772.jpg</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>11772</v>
+        <v>11774</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>131</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FARINHA DE MACA (FIBRA)</t>
+          <t>FARINHA DE LINHACA MARROM</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -11817,10 +11817,10 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>68</v>
+        <v>23.5</v>
       </c>
       <c r="O148" t="n">
-        <v>68</v>
+        <v>23.5</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -11843,22 +11843,22 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11772.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11774.png</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>11774</v>
+        <v>11776</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FARINHA DE LINHACA MARROM</t>
+          <t>FARINHA DE LINHACA DOURADA</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -11920,22 +11920,22 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11774.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11776.jpg</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>11776</v>
+        <v>11777</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FARINHA DE LINHACA DOURADA</t>
+          <t>FARINHA DE LIMAO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -11971,10 +11971,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>23.5</v>
+        <v>80</v>
       </c>
       <c r="O150" t="n">
-        <v>23.5</v>
+        <v>80</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -11997,22 +11997,22 @@
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11776.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11777.jpg</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>11777</v>
+        <v>11778</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>FARINHA DE LIMAO</t>
+          <t>FARINHA DE GRAO DE BICO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -12048,10 +12048,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="O151" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
@@ -12074,22 +12074,22 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11777.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.png</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>11778</v>
+        <v>11779</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FARINHA DE GRAO DE BICO</t>
+          <t>FARINHA DE GLUTEN 500G</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -12125,10 +12125,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O152" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
@@ -12151,22 +12151,22 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11779.jpg</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>11779</v>
+        <v>11780</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FARINHA DE GLUTEN 500G</t>
+          <t>FARINHA DE FEIJAO BRANCO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="O153" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -12228,22 +12228,22 @@
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11779.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11780.jpg</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>11780</v>
+        <v>11781</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>856</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FARINHA DE FEIJAO BRANCO</t>
+          <t>FARINHA DE COCO BRANCA</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="O154" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -12305,40 +12305,40 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11780.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11781.png</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>11781</v>
+        <v>11782</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FARINHA DE COCO BRANCA</t>
+          <t>FARINHA DE CHIA 200G</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNI</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H155" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I155" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J155" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -12356,10 +12356,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="O155" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -12373,49 +12373,49 @@
         </is>
       </c>
       <c r="T155" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11781.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11782.jpg</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>11782</v>
+        <v>11783</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FARINHA DE CHIA 200G</t>
+          <t>FARINHA DE CENTEIO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>UNI</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H156" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I156" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J156" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -12433,10 +12433,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>8</v>
+        <v>15.8</v>
       </c>
       <c r="O156" t="n">
-        <v>8</v>
+        <v>15.8</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -12450,31 +12450,31 @@
         </is>
       </c>
       <c r="T156" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11782.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11783.webp</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>11783</v>
+        <v>11784</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FARINHA DE CENTEIO</t>
+          <t>FARINHA DE CASTANHA DE CAJU</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>15.8</v>
+        <v>65</v>
       </c>
       <c r="O157" t="n">
-        <v>15.8</v>
+        <v>65</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -12536,22 +12536,22 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11783.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.png</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>11784</v>
+        <v>11786</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>586</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FARINHA DE CASTANHA DE CAJU</t>
+          <t>FARINHA DE BERINJELA</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="O158" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -12613,22 +12613,22 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11786.jpg</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>11786</v>
+        <v>11787</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FARINHA DE BERINJELA</t>
+          <t>FARINHA DE BATATA DOCE 100G</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>55</v>
+        <v>4.5</v>
       </c>
       <c r="O159" t="n">
-        <v>55</v>
+        <v>4.5</v>
       </c>
       <c r="P159" t="n">
         <v>0</v>
@@ -12690,22 +12690,22 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11786.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.png</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>11787</v>
+        <v>11789</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FARINHA DE BATATA DOCE 100G</t>
+          <t>FARINHA DE BANANA VERDE</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -12741,10 +12741,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>4.5</v>
+        <v>35</v>
       </c>
       <c r="O160" t="n">
-        <v>4.5</v>
+        <v>35</v>
       </c>
       <c r="P160" t="n">
         <v>0</v>
@@ -12767,22 +12767,22 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.jpg</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>11789</v>
+        <v>11790</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FARINHA DE BANANA VERDE</t>
+          <t>FARINHA DE AVEIA</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -12818,10 +12818,10 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>35</v>
+        <v>9.9</v>
       </c>
       <c r="O161" t="n">
-        <v>35</v>
+        <v>9.9</v>
       </c>
       <c r="P161" t="n">
         <v>0</v>
@@ -12844,22 +12844,22 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11790.webp</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>11790</v>
+        <v>11791</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FARINHA DE AVEIA</t>
+          <t>FARINHA DE ARROZ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -12895,10 +12895,10 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>9.9</v>
+        <v>11.5</v>
       </c>
       <c r="O162" t="n">
-        <v>9.9</v>
+        <v>11.5</v>
       </c>
       <c r="P162" t="n">
         <v>0</v>
@@ -12921,37 +12921,37 @@
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11790.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11791.jpg</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>11791</v>
+        <v>11792</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FARINHA DE ARROZ</t>
+          <t>FARINHA DE AMORA 100G</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H163" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I163" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J163" t="n">
         <v>100</v>
@@ -12972,10 +12972,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="O163" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="P163" t="n">
         <v>0</v>
@@ -12989,46 +12989,46 @@
         </is>
       </c>
       <c r="T163" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11791.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11792.jpg</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>11792</v>
+        <v>11794</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>980</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FARINHA DE AMORA 100G</t>
+          <t>FARINHA DE AMENDOA</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H164" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I164" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J164" t="n">
         <v>100</v>
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="O164" t="n">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="P164" t="n">
         <v>0</v>
@@ -13066,31 +13066,31 @@
         </is>
       </c>
       <c r="T164" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11792.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11794.jpg</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>11794</v>
+        <v>11795</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FARINHA DE AMENDOA</t>
+          <t>FARELO DE TRIGO TOSTADO</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -13126,10 +13126,10 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="O165" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -13152,22 +13152,22 @@
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11794.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11795.jpg</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>11795</v>
+        <v>11796</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>149</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FARELO DE TRIGO TOSTADO</t>
+          <t>FARELO DE AVEIA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -13203,10 +13203,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O166" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P166" t="n">
         <v>0</v>
@@ -13229,22 +13229,22 @@
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11795.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11796.jpg</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>11796</v>
+        <v>11952</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FARELO DE AVEIA</t>
+          <t>AVEIA LAMINADA</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>15</v>
+        <v>9.9</v>
       </c>
       <c r="O167" t="n">
-        <v>15</v>
+        <v>9.9</v>
       </c>
       <c r="P167" t="n">
         <v>0</v>
@@ -13306,22 +13306,22 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11796.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11952.webp</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>11952</v>
+        <v>11953</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AVEIA LAMINADA</t>
+          <t>AVEIA FLOCOS</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -13383,22 +13383,22 @@
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11952.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11953.webp</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>11953</v>
+        <v>11966</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AVEIA FLOCOS</t>
+          <t>ARARUTA 250G</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>9.9</v>
+        <v>29.9</v>
       </c>
       <c r="O169" t="n">
-        <v>9.9</v>
+        <v>29.9</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
@@ -13460,22 +13460,22 @@
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11953.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11966.webp</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>11966</v>
+        <v>11972</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ARARUTA 250G</t>
+          <t>AMIDO DE MILHO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>29.9</v>
+        <v>8</v>
       </c>
       <c r="O170" t="n">
-        <v>29.9</v>
+        <v>8</v>
       </c>
       <c r="P170" t="n">
         <v>0</v>
@@ -13537,22 +13537,22 @@
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11966.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.png</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>11972</v>
+        <v>12093</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>AMIDO DE MILHO</t>
+          <t>FARINHA DE CHIA</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -13588,10 +13588,10 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="O171" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="P171" t="n">
         <v>0</v>
@@ -13614,37 +13614,37 @@
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/12093.jpg</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>12093</v>
+        <v>10097</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FARINHA DE CHIA</t>
+          <t>GOJI BERRY 100G</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H172" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J172" t="n">
         <v>100</v>
@@ -13661,14 +13661,14 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>FARINACEOS E FARINHAS NATURAIS</t>
+          <t>FRUTAS SECAS</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>40</v>
+        <v>8.9</v>
       </c>
       <c r="O172" t="n">
-        <v>40</v>
+        <v>8.9</v>
       </c>
       <c r="P172" t="n">
         <v>0</v>
@@ -13686,42 +13686,42 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/12093.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10097.png</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>10097</v>
+        <v>10883</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>681</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>GOJI BERRY 100G</t>
+          <t>MORANGO DESIDRATADO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H173" t="n">
         <v>5</v>
       </c>
       <c r="I173" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J173" t="n">
         <v>100</v>
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>8.9</v>
+        <v>120</v>
       </c>
       <c r="O173" t="n">
-        <v>8.9</v>
+        <v>120</v>
       </c>
       <c r="P173" t="n">
         <v>0</v>
@@ -13763,27 +13763,27 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10097.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10883.jpg</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>10883</v>
+        <v>11094</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>526</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MORANGO DESIDRATADO</t>
+          <t>MIX DE FRUTAS VERMELHAS</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="O174" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="P174" t="n">
         <v>0</v>
@@ -13845,22 +13845,22 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10883.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11094.jpg</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>11094</v>
+        <v>11104</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>MIX DE FRUTAS VERMELHAS</t>
+          <t>LIMAO EM TIRAS CRISTALIZADO</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -13896,10 +13896,10 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="O175" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="P175" t="n">
         <v>0</v>
@@ -13922,22 +13922,22 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11094.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11104.jpg</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>11104</v>
+        <v>11446</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>LIMAO EM TIRAS CRISTALIZADO</t>
+          <t>CEREJA EM CALDA SEM CABO LATA 1.8 KG</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -13973,10 +13973,10 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="O176" t="n">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="P176" t="n">
         <v>0</v>
@@ -13999,22 +13999,22 @@
       </c>
       <c r="V176" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11104.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.webp</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>11446</v>
+        <v>11447</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CEREJA EM CALDA SEM CABO LATA 1.8 KG</t>
+          <t>CEREJA EM CALDA COM CABO LATA COM 1.65KG</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -14050,10 +14050,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>96</v>
+        <v>163.9</v>
       </c>
       <c r="O177" t="n">
-        <v>96</v>
+        <v>163.9</v>
       </c>
       <c r="P177" t="n">
         <v>0</v>
@@ -14076,22 +14076,22 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.webp</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>11447</v>
+        <v>11479</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>296</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CEREJA EM CALDA COM CABO LATA COM 1.65KG</t>
+          <t>UVA PASSA PRETA</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>163.9</v>
+        <v>36.5</v>
       </c>
       <c r="O178" t="n">
-        <v>163.9</v>
+        <v>36.5</v>
       </c>
       <c r="P178" t="n">
         <v>0</v>
@@ -14153,22 +14153,22 @@
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11479.jpg</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>11479</v>
+        <v>11483</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>UVA PASSA PRETA</t>
+          <t>UVA PASSA BRANCA</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>36.5</v>
+        <v>65</v>
       </c>
       <c r="O179" t="n">
-        <v>36.5</v>
+        <v>65</v>
       </c>
       <c r="P179" t="n">
         <v>0</v>
@@ -14230,22 +14230,22 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11479.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11483.jpg</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>11483</v>
+        <v>11508</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>153</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>UVA PASSA BRANCA</t>
+          <t>TAMARA SEM CAROCO</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="O180" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="P180" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11483.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11508.jpg</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>11508</v>
+        <v>11509</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TAMARA SEM CAROCO</t>
+          <t>TAMARA JUMBO</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="O181" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="P181" t="n">
         <v>0</v>
@@ -14384,22 +14384,22 @@
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11508.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.jpg</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>11509</v>
+        <v>11612</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TAMARA JUMBO</t>
+          <t>MIX DE FRUTAS</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -14435,10 +14435,10 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="O182" t="n">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="P182" t="n">
         <v>0</v>
@@ -14461,22 +14461,22 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11612.jpg</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>11612</v>
+        <v>11641</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MIX DE FRUTAS</t>
+          <t>MACA DESIDRATADA DESCASCADAS EM RODELAS</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -14512,10 +14512,10 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="P183" t="n">
         <v>0</v>
@@ -14538,22 +14538,22 @@
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11612.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11641.webp</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>11641</v>
+        <v>11662</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MACA DESIDRATADA DESCASCADAS EM RODELAS</t>
+          <t>LARANJA EM TIRAS CRISTALIZADAS</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P184" t="n">
         <v>0</v>
@@ -14615,22 +14615,22 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11641.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11662.png</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>11662</v>
+        <v>11693</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>LARANJA EM TIRAS CRISTALIZADAS</t>
+          <t>GOJI BERRY</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -14666,10 +14666,10 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="O185" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
@@ -14692,22 +14692,22 @@
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11662.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11693.png</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>11693</v>
+        <v>11710</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>GOJI BERRY</t>
+          <t>GENGIBRE EM CUBOS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -14743,10 +14743,10 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="O186" t="n">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="P186" t="n">
         <v>0</v>
@@ -14769,22 +14769,22 @@
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11693.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11710.jpg</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>11710</v>
+        <v>11713</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>GENGIBRE EM CUBOS</t>
+          <t>GARCINIA FRUTAS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -14820,10 +14820,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="O187" t="n">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="P187" t="n">
         <v>0</v>
@@ -14846,22 +14846,22 @@
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11710.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11713.jpg</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>11713</v>
+        <v>11723</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>124</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>GARCINIA FRUTAS</t>
+          <t>FRUTAS CRISTALIZADAS</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -14897,10 +14897,10 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="O188" t="n">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="P188" t="n">
         <v>0</v>
@@ -14923,22 +14923,22 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11713.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11723.jpg</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>11723</v>
+        <v>11728</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FRUTAS CRISTALIZADAS</t>
+          <t>FIGO TURCO SECO</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -14974,10 +14974,10 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="O189" t="n">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="P189" t="n">
         <v>0</v>
@@ -15000,22 +15000,22 @@
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11723.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11728.jpg</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>11728</v>
+        <v>11730</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>FIGO TURCO SECO</t>
+          <t>FIGO CRISTALIZADO</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -15051,10 +15051,10 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="O190" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="P190" t="n">
         <v>0</v>
@@ -15077,22 +15077,22 @@
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11728.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11730.jpg</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>11730</v>
+        <v>11828</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>FIGO CRISTALIZADO</t>
+          <t>DAMASCO</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -15128,13 +15128,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="O191" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Q191" t="n">
         <v>0</v>
@@ -15154,22 +15154,22 @@
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11730.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11828.jpg</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>11828</v>
+        <v>11836</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DAMASCO</t>
+          <t>CRANBERRY INTEIRO</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -15205,13 +15205,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="O192" t="n">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="P192" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
         <v>0</v>
@@ -15231,22 +15231,22 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11828.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11836.jpg</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>11836</v>
+        <v>11929</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>CRANBERRY INTEIRO</t>
+          <t>BLUE BERRY</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>85</v>
+        <v>278</v>
       </c>
       <c r="O193" t="n">
-        <v>85</v>
+        <v>278</v>
       </c>
       <c r="P193" t="n">
         <v>0</v>
@@ -15308,22 +15308,22 @@
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11836.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11929.jpg</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>11929</v>
+        <v>11943</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BLUE BERRY</t>
+          <t>BANANA PASSA</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>278</v>
+        <v>55</v>
       </c>
       <c r="O194" t="n">
-        <v>278</v>
+        <v>55</v>
       </c>
       <c r="P194" t="n">
         <v>0</v>
@@ -15385,22 +15385,22 @@
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11929.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11943.png</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>11943</v>
+        <v>12001</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>BANANA PASSA</t>
+          <t>AMEIXA SEM CAROCO</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -15462,22 +15462,22 @@
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11943.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12001.jpg</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>12001</v>
+        <v>12035</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>AMEIXA SEM CAROCO</t>
+          <t>ABACAXI CRISTALIZADO</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -15513,10 +15513,10 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="O196" t="n">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="P196" t="n">
         <v>0</v>
@@ -15539,22 +15539,22 @@
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12001.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12035.png</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>12035</v>
+        <v>12053</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ABACAXI CRISTALIZADO</t>
+          <t>KIWI GLACEAGO</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O197" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P197" t="n">
         <v>0</v>
@@ -15616,22 +15616,22 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12035.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12053.webp</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>12053</v>
+        <v>12054</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>KIWI GLACEAGO</t>
+          <t>CEREJA DESIDRATADA</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -15667,10 +15667,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="O198" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="P198" t="n">
         <v>0</v>
@@ -15693,22 +15693,22 @@
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12053.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12054.jpg</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>12054</v>
+        <v>12151</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>488</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>CEREJA DESIDRATADA</t>
+          <t>TAMARA LARGE JUMBO</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -15744,10 +15744,10 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O199" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="P199" t="n">
         <v>0</v>
@@ -15770,22 +15770,22 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12054.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.jpg</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>12151</v>
+        <v>10831</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>306</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TAMARA LARGE JUMBO</t>
+          <t>FENO GREGO MOIDO</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -15797,7 +15797,7 @@
         <v>10</v>
       </c>
       <c r="H200" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I200" t="n">
         <v>5</v>
@@ -15817,14 +15817,14 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>FRUTAS SECAS</t>
+          <t>GRAOS</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="O200" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="P200" t="n">
         <v>0</v>
@@ -15842,27 +15842,27 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>100gr</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.jpg</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>10831</v>
+        <v>11491</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>527</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FENO GREGO MOIDO</t>
+          <t>TRIGO EM GRAO</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -15898,10 +15898,10 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="O201" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="P201" t="n">
         <v>0</v>
@@ -15924,22 +15924,22 @@
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.jpg</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>11491</v>
+        <v>11515</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>TRIGO EM GRAO</t>
+          <t>SOJA GRAO</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -15975,10 +15975,10 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="O202" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="P202" t="n">
         <v>0</v>
@@ -16001,22 +16001,22 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.jpg</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>11515</v>
+        <v>11528</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SOJA GRAO</t>
+          <t>SAGU</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -16052,10 +16052,10 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>9.9</v>
+        <v>16</v>
       </c>
       <c r="O203" t="n">
-        <v>9.9</v>
+        <v>16</v>
       </c>
       <c r="P203" t="n">
         <v>0</v>
@@ -16078,22 +16078,22 @@
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11528.webp</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>11528</v>
+        <v>11535</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>SAGU</t>
+          <t>QUIRELA 500G</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -16129,10 +16129,10 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>16</v>
+        <v>3.6</v>
       </c>
       <c r="O204" t="n">
-        <v>16</v>
+        <v>3.6</v>
       </c>
       <c r="P204" t="n">
         <v>0</v>
@@ -16155,22 +16155,22 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11528.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.jpg</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>11535</v>
+        <v>11536</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>QUIRELA 500G</t>
+          <t>QUINUA GRAO</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>3.6</v>
+        <v>38</v>
       </c>
       <c r="O205" t="n">
-        <v>3.6</v>
+        <v>38</v>
       </c>
       <c r="P205" t="n">
         <v>0</v>
@@ -16232,22 +16232,22 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.webp</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>11536</v>
+        <v>11610</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>QUINUA GRAO</t>
+          <t>MIX QUINUA</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O206" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="P206" t="n">
         <v>0</v>
@@ -16309,22 +16309,22 @@
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.jpg</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>11610</v>
+        <v>11617</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>MIX QUINUA</t>
+          <t>MILHO DE PIPOCA</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>46</v>
+        <v>7.5</v>
       </c>
       <c r="O207" t="n">
-        <v>46</v>
+        <v>7.5</v>
       </c>
       <c r="P207" t="n">
         <v>0</v>
@@ -16386,22 +16386,22 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.jpg</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>11617</v>
+        <v>11651</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>MILHO DE PIPOCA</t>
+          <t>LENTILHA VERMELHA</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -16437,10 +16437,10 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>7.5</v>
+        <v>24.5</v>
       </c>
       <c r="O208" t="n">
-        <v>7.5</v>
+        <v>24.5</v>
       </c>
       <c r="P208" t="n">
         <v>0</v>
@@ -16463,22 +16463,22 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.jpg</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>11651</v>
+        <v>11652</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>LENTILHA VERMELHA</t>
+          <t>LENTILHA</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -16514,10 +16514,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
       <c r="O209" t="n">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
       <c r="P209" t="n">
         <v>0</v>
@@ -16540,22 +16540,22 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11652.jpg</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>11652</v>
+        <v>11686</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>LENTILHA</t>
+          <t>GRAO DE BICO  MIUDO</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -16591,10 +16591,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="O210" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="P210" t="n">
         <v>0</v>
@@ -16617,22 +16617,22 @@
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11652.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11686.png</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>11686</v>
+        <v>11687</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>GRAO DE BICO  MIUDO</t>
+          <t>GRAO DE BICO GRAUDO</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>17.5</v>
+        <v>26.9</v>
       </c>
       <c r="O211" t="n">
-        <v>17.5</v>
+        <v>26.9</v>
       </c>
       <c r="P211" t="n">
         <v>0</v>
@@ -16694,22 +16694,22 @@
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11686.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11687.webp</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>11687</v>
+        <v>11731</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>GRAO DE BICO GRAUDO</t>
+          <t>FENO GREGO EM GRAOS</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -16745,10 +16745,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>26.9</v>
+        <v>34</v>
       </c>
       <c r="O212" t="n">
-        <v>26.9</v>
+        <v>34</v>
       </c>
       <c r="P212" t="n">
         <v>0</v>
@@ -16771,27 +16771,27 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11687.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.jpg</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>11731</v>
+        <v>11732</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>FENO GREGO EM GRAOS</t>
+          <t>FEIJAO VERMELHO 500G</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -16822,10 +16822,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="O213" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="P213" t="n">
         <v>0</v>
@@ -16839,36 +16839,36 @@
         </is>
       </c>
       <c r="T213" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>100gr</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11732.jpg</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>11732</v>
+        <v>11734</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>519</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>FEIJAO VERMELHO 500G</t>
+          <t>FEIJAO ROXAO</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -16899,10 +16899,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>11</v>
+        <v>24.8</v>
       </c>
       <c r="O214" t="n">
-        <v>11</v>
+        <v>24.8</v>
       </c>
       <c r="P214" t="n">
         <v>0</v>
@@ -16916,31 +16916,31 @@
         </is>
       </c>
       <c r="T214" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100gr</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11732.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11734.jpg</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>11734</v>
+        <v>11735</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>FEIJAO ROXAO</t>
+          <t>FEIJAO ROSINHA</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -16976,10 +16976,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>24.8</v>
+        <v>18</v>
       </c>
       <c r="O215" t="n">
-        <v>24.8</v>
+        <v>18</v>
       </c>
       <c r="P215" t="n">
         <v>0</v>
@@ -17002,22 +17002,22 @@
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11734.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.jpg</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>11735</v>
+        <v>11737</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>FEIJAO ROSINHA</t>
+          <t>FEIJAO PRETO</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>18</v>
+        <v>8.9</v>
       </c>
       <c r="O216" t="n">
-        <v>18</v>
+        <v>8.9</v>
       </c>
       <c r="P216" t="n">
         <v>0</v>
@@ -17079,22 +17079,22 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11737.png</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>11737</v>
+        <v>11738</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>FEIJAO PRETO</t>
+          <t>FEIJAO MOYASHI</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>8.9</v>
+        <v>19</v>
       </c>
       <c r="O217" t="n">
-        <v>8.9</v>
+        <v>19</v>
       </c>
       <c r="P217" t="n">
         <v>0</v>
@@ -17156,22 +17156,22 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11737.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.jpg</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>11738</v>
+        <v>11741</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>FEIJAO MOYASHI</t>
+          <t>FEIJAO FRADINHO</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -17207,10 +17207,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>19</v>
+        <v>9.9</v>
       </c>
       <c r="O218" t="n">
-        <v>19</v>
+        <v>9.9</v>
       </c>
       <c r="P218" t="n">
         <v>0</v>
@@ -17233,22 +17233,22 @@
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.webp</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>11741</v>
+        <v>11743</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FEIJAO FRADINHO</t>
+          <t>FEIJAO CORDA</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="O219" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="P219" t="n">
         <v>0</v>
@@ -17310,22 +17310,22 @@
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11743.webp</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>11743</v>
+        <v>11744</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FEIJAO CORDA</t>
+          <t>FEIJAO CARIOCA</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -17361,10 +17361,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="O220" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="P220" t="n">
         <v>0</v>
@@ -17387,22 +17387,22 @@
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11743.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.jpg</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>11744</v>
+        <v>11745</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FEIJAO CARIOCA</t>
+          <t>FEIJAO BRANCO</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -17438,10 +17438,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="O221" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="P221" t="n">
         <v>0</v>
@@ -17464,22 +17464,22 @@
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.jpg</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>11745</v>
+        <v>11747</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>FEIJAO BRANCO</t>
+          <t>FEIJAO BOLINHA</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -17515,10 +17515,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>15.9</v>
+        <v>24.9</v>
       </c>
       <c r="O222" t="n">
-        <v>15.9</v>
+        <v>24.9</v>
       </c>
       <c r="P222" t="n">
         <v>0</v>
@@ -17541,22 +17541,22 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11747.jpg</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>11747</v>
+        <v>11748</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>335</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FEIJAO BOLINHA</t>
+          <t>FEIJAO AZUKI</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -17592,10 +17592,10 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>24.9</v>
+        <v>19</v>
       </c>
       <c r="O223" t="n">
-        <v>24.9</v>
+        <v>19</v>
       </c>
       <c r="P223" t="n">
         <v>0</v>
@@ -17618,22 +17618,22 @@
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11747.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.jpg</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>11748</v>
+        <v>11749</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FEIJAO AZUKI</t>
+          <t>FEIJAO ANDU</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -17669,10 +17669,10 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>19</v>
+        <v>26.9</v>
       </c>
       <c r="O224" t="n">
-        <v>19</v>
+        <v>26.9</v>
       </c>
       <c r="P224" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.jpg</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>11749</v>
+        <v>11751</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FEIJAO ANDU</t>
+          <t>FAVA BRANCA MIUDA</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -17746,10 +17746,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>26.9</v>
+        <v>42</v>
       </c>
       <c r="O225" t="n">
-        <v>26.9</v>
+        <v>42</v>
       </c>
       <c r="P225" t="n">
         <v>0</v>
@@ -17772,22 +17772,22 @@
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.jpg</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>11751</v>
+        <v>11752</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FAVA BRANCA MIUDA</t>
+          <t>FAVA BRANCA GRAUDA</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -17823,10 +17823,10 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>42</v>
+        <v>32.9</v>
       </c>
       <c r="O226" t="n">
-        <v>42</v>
+        <v>32.9</v>
       </c>
       <c r="P226" t="n">
         <v>0</v>
@@ -17849,22 +17849,22 @@
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.jpg</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>11752</v>
+        <v>11804</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>FAVA BRANCA GRAUDA</t>
+          <t>ERVILHA PARTIDA</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -17900,10 +17900,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>32.9</v>
+        <v>16</v>
       </c>
       <c r="O227" t="n">
-        <v>32.9</v>
+        <v>16</v>
       </c>
       <c r="P227" t="n">
         <v>0</v>
@@ -17926,22 +17926,22 @@
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.webp</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>11804</v>
+        <v>11911</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ERVILHA PARTIDA</t>
+          <t>CANJICA BRANCA</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>16</v>
+        <v>9.9</v>
       </c>
       <c r="O228" t="n">
-        <v>16</v>
+        <v>9.9</v>
       </c>
       <c r="P228" t="n">
         <v>0</v>
@@ -18003,22 +18003,22 @@
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.jpg</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>11911</v>
+        <v>11912</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CANJICA BRANCA</t>
+          <t>CANJICA AMARELA</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -18054,10 +18054,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>9.9</v>
+        <v>6.25</v>
       </c>
       <c r="O229" t="n">
-        <v>9.9</v>
+        <v>6.25</v>
       </c>
       <c r="P229" t="n">
         <v>0</v>
@@ -18080,27 +18080,27 @@
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11912.jpg</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>11912</v>
+        <v>11957</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>CANJICA AMARELA</t>
+          <t>ARROZ VERMELHO 500G</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -18131,10 +18131,10 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="O230" t="n">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="P230" t="n">
         <v>0</v>
@@ -18148,36 +18148,36 @@
         </is>
       </c>
       <c r="T230" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>100gr</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11912.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.jpg</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>11957</v>
+        <v>11958</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ARROZ VERMELHO 500G</t>
+          <t>ARROZ NEGRO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="O231" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="P231" t="n">
         <v>0</v>
@@ -18225,31 +18225,31 @@
         </is>
       </c>
       <c r="T231" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100gr</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11958.jpg</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>11958</v>
+        <v>11959</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ARROZ NEGRO</t>
+          <t>ARROZ INTEGRAL CATETO BRANCO</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -18285,10 +18285,10 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>49</v>
+        <v>22.5</v>
       </c>
       <c r="O232" t="n">
-        <v>49</v>
+        <v>22.5</v>
       </c>
       <c r="P232" t="n">
         <v>0</v>
@@ -18311,22 +18311,22 @@
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11958.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.png</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>11959</v>
+        <v>11960</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ARROZ INTEGRAL CATETO BRANCO</t>
+          <t>ARROZ INTEGRAL AGULHA MISTO</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -18362,10 +18362,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>22.5</v>
+        <v>15.9</v>
       </c>
       <c r="O233" t="n">
-        <v>22.5</v>
+        <v>15.9</v>
       </c>
       <c r="P233" t="n">
         <v>0</v>
@@ -18388,22 +18388,22 @@
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11960.jpg</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>11960</v>
+        <v>11961</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>297</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ARROZ INTEGRAL AGULHA MISTO</t>
+          <t>ARROZ INTEGRAL AGULHA BRANCO</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -18439,10 +18439,10 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>15.9</v>
+        <v>13.5</v>
       </c>
       <c r="O234" t="n">
-        <v>15.9</v>
+        <v>13.5</v>
       </c>
       <c r="P234" t="n">
         <v>0</v>
@@ -18465,22 +18465,22 @@
       </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11960.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11961.jpg</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>11961</v>
+        <v>11962</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ARROZ INTEGRAL AGULHA BRANCO</t>
+          <t>ARROZ 7 GRAOS</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -18516,10 +18516,10 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="O235" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="P235" t="n">
         <v>0</v>
@@ -18542,22 +18542,22 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11961.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11962.webp</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>11962</v>
+        <v>12002</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ARROZ 7 GRAOS</t>
+          <t>AMARANTO GRAO</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -18593,10 +18593,10 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="O236" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="P236" t="n">
         <v>0</v>
@@ -18619,22 +18619,22 @@
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11962.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12002.webp</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>12002</v>
+        <v>12077</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>AMARANTO GRAO</t>
+          <t>CAFE GRAO A GRANEL</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -18670,10 +18670,10 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="O237" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="P237" t="n">
         <v>0</v>
@@ -18696,22 +18696,22 @@
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12002.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.jpg</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>12077</v>
+        <v>12084</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CAFE GRAO A GRANEL</t>
+          <t>FEIJAO RAJADO</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -18747,10 +18747,10 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>98</v>
+        <v>17.9</v>
       </c>
       <c r="O238" t="n">
-        <v>98</v>
+        <v>17.9</v>
       </c>
       <c r="P238" t="n">
         <v>0</v>
@@ -18773,22 +18773,22 @@
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12084.webp</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>12084</v>
+        <v>12101</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>FEIJAO RAJADO</t>
+          <t>ARROZ VERMELHO GRANEL</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -18824,10 +18824,10 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>17.9</v>
+        <v>10</v>
       </c>
       <c r="O239" t="n">
-        <v>17.9</v>
+        <v>10</v>
       </c>
       <c r="P239" t="n">
         <v>0</v>
@@ -18850,22 +18850,22 @@
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12084.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.jpg</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>12101</v>
+        <v>12102</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>741</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ARROZ VERMELHO GRANEL</t>
+          <t>QUIRELA</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -18901,10 +18901,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O240" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P240" t="n">
         <v>0</v>
@@ -18927,22 +18927,22 @@
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.jpg</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>12102</v>
+        <v>10449</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>QUIRELA</t>
+          <t>GERGELIM TORRADO</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -18974,14 +18974,14 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>GRAOS</t>
+          <t>SEMENTES</t>
         </is>
       </c>
       <c r="N241" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="O241" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="P241" t="n">
         <v>0</v>
@@ -18999,27 +18999,27 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>100gr</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.jpg</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>10449</v>
+        <v>10988</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>GERGELIM TORRADO</t>
+          <t>GIRASSOL S/CASCA TORRADO</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -19055,10 +19055,10 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O242" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="P242" t="n">
         <v>0</v>
@@ -19081,40 +19081,40 @@
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.jpg</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>10988</v>
+        <v>11184</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>GIRASSOL S/CASCA TORRADO</t>
+          <t>SEMENTE DE MELANCIA 25G</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UN</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H243" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I243" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J243" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -19132,10 +19132,10 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="O243" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="P243" t="n">
         <v>0</v>
@@ -19149,49 +19149,49 @@
         </is>
       </c>
       <c r="T243" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.jpg</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>11184</v>
+        <v>11518</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>SEMENTE DE MELANCIA 25G</t>
+          <t>SEMENTE DE ABOBORA S/C TOR S/S</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H244" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I244" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J244" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -19209,10 +19209,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="O244" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="P244" t="n">
         <v>0</v>
@@ -19226,31 +19226,31 @@
         </is>
       </c>
       <c r="T244" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11518.jpg</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>11518</v>
+        <v>11519</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>SEMENTE DE ABOBORA S/C TOR S/S</t>
+          <t>SEMENTE DE ABOBORA CRUA S/ CASCA</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -19286,10 +19286,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="O245" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="P245" t="n">
         <v>0</v>
@@ -19312,22 +19312,22 @@
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11518.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.jpg</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>11519</v>
+        <v>11645</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>SEMENTE DE ABOBORA CRUA S/ CASCA</t>
+          <t>LINHACA MARROM SEMENTE</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -19363,10 +19363,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="O246" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="P246" t="n">
         <v>0</v>
@@ -19389,22 +19389,22 @@
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.jpg</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>11645</v>
+        <v>11646</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>LINHACA MARROM SEMENTE</t>
+          <t>LINHACA DOURADA SEMENTE</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -19440,10 +19440,10 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="O247" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="P247" t="n">
         <v>0</v>
@@ -19466,22 +19466,22 @@
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.jpg</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>11646</v>
+        <v>11698</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>LINHACA DOURADA SEMENTE</t>
+          <t>GIRASSOL S/CASCA</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -19517,10 +19517,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="O248" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="P248" t="n">
         <v>0</v>
@@ -19543,22 +19543,22 @@
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11698.webp</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>11698</v>
+        <v>11705</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>GIRASSOL S/CASCA</t>
+          <t>GERGELIM S/ PELE</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -19594,10 +19594,10 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O249" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P249" t="n">
         <v>0</v>
@@ -19620,22 +19620,22 @@
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11698.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.jpg</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>11705</v>
+        <v>11706</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>GERGELIM S/ PELE</t>
+          <t>GERGELIM PRETO</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -19671,10 +19671,10 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="O250" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="P250" t="n">
         <v>0</v>
@@ -19697,22 +19697,22 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.png</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>11706</v>
+        <v>11707</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>GERGELIM PRETO</t>
+          <t>GERGELIM C/ PELE</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -19748,10 +19748,10 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="O251" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="P251" t="n">
         <v>0</v>
@@ -19774,22 +19774,22 @@
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.jpg</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>11707</v>
+        <v>11865</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>822</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>GERGELIM C/ PELE</t>
+          <t>CHIA PREMIUM</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -19825,10 +19825,10 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O252" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="P252" t="n">
         <v>0</v>
@@ -19851,22 +19851,22 @@
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.webp</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>11865</v>
+        <v>10058</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>CHIA PREMIUM</t>
+          <t>PIMENTA BRANCA GRAO</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -19898,14 +19898,14 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>SEMENTES</t>
+          <t>TEMPEROS A GRANEL</t>
         </is>
       </c>
       <c r="N253" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="O253" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="P253" t="n">
         <v>0</v>
@@ -19928,22 +19928,22 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.jpg</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>10058</v>
+        <v>10061</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>PIMENTA BRANCA GRAO</t>
+          <t>CALDO DE PEIXE</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -19979,10 +19979,10 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="O254" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="P254" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.webp</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>10061</v>
+        <v>10102</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>CALDO DE PEIXE</t>
+          <t>TEMPERO TAILANDES</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -20056,10 +20056,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="O255" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="P255" t="n">
         <v>0</v>
@@ -20082,27 +20082,27 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10102.webp</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>10102</v>
+        <v>10171</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>TEMPERO TAILANDES</t>
+          <t>LEMON C/ ERVAS FINAS 500G</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNI</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -20112,10 +20112,10 @@
         <v>10</v>
       </c>
       <c r="I256" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J256" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -20133,10 +20133,10 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="O256" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="P256" t="n">
         <v>0</v>
@@ -20150,36 +20150,36 @@
         </is>
       </c>
       <c r="T256" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10102.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.webp</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>10171</v>
+        <v>10256</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>LEMON C/ ERVAS FINAS 500G</t>
+          <t>OREGANO EM PO 20G</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>UNI</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -20189,10 +20189,10 @@
         <v>10</v>
       </c>
       <c r="I257" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J257" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O257" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P257" t="n">
         <v>0</v>
@@ -20227,31 +20227,31 @@
         </is>
       </c>
       <c r="T257" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.webp</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>10256</v>
+        <v>10264</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>OREGANO EM PO 20G</t>
+          <t>MANJERICAO EM PO</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -20287,10 +20287,10 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="O258" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P258" t="n">
         <v>0</v>
@@ -20313,22 +20313,22 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>10264</v>
+        <v>10306</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>MANJERICAO EM PO</t>
+          <t>CANELA PO PURA PREMIUM</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="O259" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="P259" t="n">
         <v>0</v>
@@ -20390,22 +20390,22 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.jpg</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>10306</v>
+        <v>10308</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>CANELA PO PURA PREMIUM</t>
+          <t>CHIMICHURRI DEFUMADO</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -20441,10 +20441,10 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="O260" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="P260" t="n">
         <v>0</v>
@@ -20467,22 +20467,22 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.jpg</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>10308</v>
+        <v>10550</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>CHIMICHURRI DEFUMADO</t>
+          <t>ORANGE PEPPER</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -20518,10 +20518,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="O261" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="P261" t="n">
         <v>0</v>
@@ -20544,22 +20544,22 @@
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>10550</v>
+        <v>10720</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ORANGE PEPPER</t>
+          <t>ALHO ROXO SOLTO</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -20595,10 +20595,10 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O262" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P262" t="n">
         <v>0</v>
@@ -20621,22 +20621,22 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>10720</v>
+        <v>10887</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ALHO ROXO SOLTO</t>
+          <t>ACAFRAO IMPORTADO</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -20672,10 +20672,10 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O263" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P263" t="n">
         <v>0</v>
@@ -20698,22 +20698,22 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>10887</v>
+        <v>10902</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ACAFRAO IMPORTADO</t>
+          <t>TEMPERO BAIANO SEM PIMENTA</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -20749,10 +20749,10 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="O264" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="P264" t="n">
         <v>0</v>
@@ -20775,22 +20775,22 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>10902</v>
+        <v>10967</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO SEM PIMENTA</t>
+          <t>CREME DE CEBOLA</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -20826,10 +20826,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="O265" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="P265" t="n">
         <v>0</v>
@@ -20852,22 +20852,22 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>10967</v>
+        <v>11029</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CREME DE CEBOLA</t>
+          <t>CEBOLA CRISPY</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -20903,10 +20903,10 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="O266" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="P266" t="n">
         <v>0</v>
@@ -20929,22 +20929,22 @@
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.webp</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>11029</v>
+        <v>11167</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>CEBOLA CRISPY</t>
+          <t>FIT EDU GUEDES</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -20980,10 +20980,10 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="O267" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="P267" t="n">
         <v>0</v>
@@ -21006,22 +21006,22 @@
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11167.jpg</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>11167</v>
+        <v>11168</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>FIT EDU GUEDES</t>
+          <t>TEMPERO MINEIRO</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -21057,10 +21057,10 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="O268" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="P268" t="n">
         <v>0</v>
@@ -21083,22 +21083,22 @@
       </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11167.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>11168</v>
+        <v>11170</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>TEMPERO MINEIRO</t>
+          <t>FIT COMPLETO</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -21134,10 +21134,10 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O269" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P269" t="n">
         <v>0</v>
@@ -21160,22 +21160,22 @@
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>11170</v>
+        <v>11237</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>FIT COMPLETO</t>
+          <t>TEMPERO SIRIO</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -21211,10 +21211,10 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O270" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="P270" t="n">
         <v>0</v>
@@ -21237,40 +21237,40 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.png</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>11237</v>
+        <v>11382</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>TEMPERO SIRIO</t>
+          <t>GARAM MASALA 20G</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UN</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H271" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I271" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J271" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -21288,10 +21288,10 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>38</v>
+        <v>2.5</v>
       </c>
       <c r="O271" t="n">
-        <v>38</v>
+        <v>2.5</v>
       </c>
       <c r="P271" t="n">
         <v>0</v>
@@ -21305,49 +21305,49 @@
         </is>
       </c>
       <c r="T271" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.webp</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>11382</v>
+        <v>11466</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>GARAM MASALA 20G</t>
+          <t>ZIMBRO</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H272" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I272" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J272" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -21365,10 +21365,10 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>2.5</v>
+        <v>229</v>
       </c>
       <c r="O272" t="n">
-        <v>2.5</v>
+        <v>229</v>
       </c>
       <c r="P272" t="n">
         <v>0</v>
@@ -21382,31 +21382,31 @@
         </is>
       </c>
       <c r="T272" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.jpg</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>11466</v>
+        <v>11468</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>971</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ZIMBRO</t>
+          <t>ZATTAR</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -21442,10 +21442,10 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>229</v>
+        <v>55</v>
       </c>
       <c r="O273" t="n">
-        <v>229</v>
+        <v>55</v>
       </c>
       <c r="P273" t="n">
         <v>0</v>
@@ -21468,22 +21468,22 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.webp</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>11468</v>
+        <v>11473</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ZATTAR</t>
+          <t>VINAGRETE</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -21519,10 +21519,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="O274" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="P274" t="n">
         <v>0</v>
@@ -21545,22 +21545,22 @@
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>11473</v>
+        <v>11487</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>VINAGRETE</t>
+          <t>PEGA MARIDO</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -21596,10 +21596,10 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="O275" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P275" t="n">
         <v>0</v>
@@ -21622,22 +21622,22 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.webp</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>11487</v>
+        <v>11493</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>PEGA MARIDO</t>
+          <t>TOMILHO</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="O276" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="P276" t="n">
         <v>0</v>
@@ -21699,22 +21699,22 @@
       </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.jpg</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>11493</v>
+        <v>11496</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>TOMILHO</t>
+          <t>TEMPERO FEIJAO</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -21750,10 +21750,10 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="O277" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="P277" t="n">
         <v>0</v>
@@ -21776,22 +21776,22 @@
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>11496</v>
+        <v>11497</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>TEMPERO FEIJAO</t>
+          <t>LEMON COM ERVAS FINAS</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -21827,10 +21827,10 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="O278" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P278" t="n">
         <v>0</v>
@@ -21853,22 +21853,22 @@
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.webp</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>11497</v>
+        <v>11499</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>LEMON COM ERVAS FINAS</t>
+          <t>TEMPERO BAIANO PO</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -21904,10 +21904,10 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="O279" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="P279" t="n">
         <v>0</v>
@@ -21930,22 +21930,22 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>11499</v>
+        <v>11500</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO PO</t>
+          <t>TEMPERO BAIANO GRAO</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -21981,10 +21981,10 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="O280" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="P280" t="n">
         <v>0</v>
@@ -22007,22 +22007,22 @@
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>11500</v>
+        <v>11502</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO GRAO</t>
+          <t>TEMPERO ANA MARIA</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="O281" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="P281" t="n">
         <v>0</v>
@@ -22084,22 +22084,22 @@
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>11502</v>
+        <v>11523</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>TEMPERO ANA MARIA</t>
+          <t>SALSA DESIDRATADA</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -22135,10 +22135,10 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="O282" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P282" t="n">
         <v>0</v>
@@ -22161,22 +22161,22 @@
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>11523</v>
+        <v>11563</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SALSA DESIDRATADA</t>
+          <t>PIMENTA SIRIA PO (JAMAICA)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -22212,10 +22212,10 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="O283" t="n">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="P283" t="n">
         <v>0</v>
@@ -22238,22 +22238,22 @@
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>11563</v>
+        <v>11565</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>PIMENTA SIRIA PO (JAMAICA)</t>
+          <t>PIMENTA SIRIA GRAO (JAMAICA)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -22289,10 +22289,10 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="O284" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="P284" t="n">
         <v>0</v>
@@ -22315,22 +22315,22 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>11565</v>
+        <v>11567</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>PIMENTA SIRIA GRAO (JAMAICA)</t>
+          <t>PIMENTA ROSA</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="O285" t="n">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="P285" t="n">
         <v>0</v>
@@ -22392,22 +22392,22 @@
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>11567</v>
+        <v>11568</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>PIMENTA ROSA</t>
+          <t>PIMENTA DO REINO PRETA PO</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -22443,10 +22443,10 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="O286" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="P286" t="n">
         <v>0</v>
@@ -22469,22 +22469,22 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.webp</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>11568</v>
+        <v>11569</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO PRETA PO</t>
+          <t>PIMENTA DO REINO  PRETA  GRAO</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -22520,10 +22520,10 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O287" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="P287" t="n">
         <v>0</v>
@@ -22546,22 +22546,22 @@
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>11569</v>
+        <v>11570</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO  PRETA  GRAO</t>
+          <t>PIMENTA DO REINO BRANCA EM PO</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -22597,10 +22597,10 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="O288" t="n">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="P288" t="n">
         <v>0</v>
@@ -22623,22 +22623,22 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.png</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>11570</v>
+        <v>11571</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO BRANCA EM PO</t>
+          <t>PIMENTA CHILLI</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -22674,10 +22674,10 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="O289" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="P289" t="n">
         <v>0</v>
@@ -22700,22 +22700,22 @@
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.jpg</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>11571</v>
+        <v>11572</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>PIMENTA CHILLI</t>
+          <t>PIMENTA CALABRESA FLOCOS</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -22751,10 +22751,10 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="O290" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="P290" t="n">
         <v>0</v>
@@ -22777,22 +22777,22 @@
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.webp</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>11572</v>
+        <v>11573</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>607</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>PIMENTA CALABRESA FLOCOS</t>
+          <t>PIMENTA CAYENA</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -22828,10 +22828,10 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="O291" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="P291" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.jpg</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>11573</v>
+        <v>11584</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>PIMENTA CAYENA</t>
+          <t>PAPRICA PICANTE</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -22905,10 +22905,10 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="O292" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="P292" t="n">
         <v>0</v>
@@ -22931,22 +22931,22 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>11584</v>
+        <v>11586</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>PAPRICA PICANTE</t>
+          <t>PAPRICA DOCE</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -23008,22 +23008,22 @@
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>11586</v>
+        <v>11588</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>PAPRICA DOCE</t>
+          <t>PAPRICA DEFUMADA</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -23085,22 +23085,22 @@
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>11588</v>
+        <v>11592</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>PAPRICA DEFUMADA</t>
+          <t>OREGANO</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -23136,10 +23136,10 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O295" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="P295" t="n">
         <v>0</v>
@@ -23162,22 +23162,22 @@
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>11592</v>
+        <v>11602</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>OREGANO</t>
+          <t>NOZ MOSCADA PO</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -23213,10 +23213,10 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="O296" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="P296" t="n">
         <v>0</v>
@@ -23239,22 +23239,22 @@
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>11602</v>
+        <v>11607</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>NOZ MOSCADA PO</t>
+          <t>MOSTARDA PO PURA</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -23290,10 +23290,10 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="O297" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -23316,22 +23316,22 @@
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.png</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>11607</v>
+        <v>11608</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>MOSTARDA PO PURA</t>
+          <t>MOSTARDA GRAO</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -23367,10 +23367,10 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="O298" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="P298" t="n">
         <v>0</v>
@@ -23393,22 +23393,22 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.jpg</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>11608</v>
+        <v>11629</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>MOSTARDA GRAO</t>
+          <t>MANJERONA DESIDRATADO</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -23444,10 +23444,10 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="O299" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="P299" t="n">
         <v>0</v>
@@ -23470,22 +23470,22 @@
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.jpg</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>11629</v>
+        <v>11630</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>MANJERONA DESIDRATADO</t>
+          <t>MANJERICAO DESIDRATADO</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -23521,10 +23521,10 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O300" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P300" t="n">
         <v>0</v>
@@ -23547,22 +23547,22 @@
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.png</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>11630</v>
+        <v>11642</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>MANJERICAO DESIDRATADO</t>
+          <t>LOURO EM PO</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -23598,10 +23598,10 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="O301" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="P301" t="n">
         <v>0</v>
@@ -23624,22 +23624,22 @@
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.png</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>11642</v>
+        <v>11643</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>811</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>LOURO EM PO</t>
+          <t>LOURO EM FOLHA</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -23675,10 +23675,10 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="O302" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="P302" t="n">
         <v>0</v>
@@ -23701,22 +23701,22 @@
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.webp</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>11643</v>
+        <v>11647</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>LOURO EM FOLHA</t>
+          <t>LEMON PEPPER 0% SODIO</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -23752,10 +23752,10 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O303" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P303" t="n">
         <v>0</v>
@@ -23778,22 +23778,22 @@
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.webp</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>11647</v>
+        <v>11655</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>LEMON PEPPER 0% SODIO</t>
+          <t>LEMON PEPPER</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -23829,10 +23829,10 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="O304" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="P304" t="n">
         <v>0</v>
@@ -23855,22 +23855,22 @@
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.webp</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>11655</v>
+        <v>11717</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>LEMON PEPPER</t>
+          <t>FUMACA EM PO</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -23906,10 +23906,10 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="O305" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P305" t="n">
         <v>0</v>
@@ -23932,22 +23932,22 @@
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>11717</v>
+        <v>11806</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>FUMACA EM PO</t>
+          <t>ERVAS FINAS</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -23983,10 +23983,10 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="O306" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -24009,22 +24009,22 @@
       </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>11806</v>
+        <v>11818</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>ERVAS FINAS</t>
+          <t>ENDRO</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -24060,10 +24060,10 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="O307" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -24086,22 +24086,22 @@
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>11818</v>
+        <v>11822</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>ENDRO</t>
+          <t>EDU GUEDES</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -24137,10 +24137,10 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="O308" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P308" t="n">
         <v>0</v>
@@ -24163,22 +24163,22 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>11822</v>
+        <v>11830</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>EDU GUEDES</t>
+          <t>CURRY</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -24214,10 +24214,10 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O309" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P309" t="n">
         <v>0</v>
@@ -24240,22 +24240,22 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.jpg</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>11830</v>
+        <v>11833</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>CURRY</t>
+          <t>CRAVO MOIDO</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -24291,10 +24291,10 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="O310" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="P310" t="n">
         <v>0</v>
@@ -24317,22 +24317,22 @@
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.jpg</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>11833</v>
+        <v>11834</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>CRAVO MOIDO</t>
+          <t>CRAVO GRAO</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -24368,10 +24368,10 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="O311" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="P311" t="n">
         <v>0</v>
@@ -24394,22 +24394,22 @@
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.png</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>11834</v>
+        <v>11838</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>CRAVO GRAO</t>
+          <t>COMINHO PO PURO</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -24445,10 +24445,10 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="O312" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="P312" t="n">
         <v>0</v>
@@ -24471,22 +24471,22 @@
       </c>
       <c r="V312" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.png</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>11838</v>
+        <v>11839</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>COMINHO PO PURO</t>
+          <t>COMINHO GRAO 99%</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="O313" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="P313" t="n">
         <v>0</v>
@@ -24548,22 +24548,22 @@
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11839.png</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>11839</v>
+        <v>11840</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>571</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>COMINHO GRAO 99%</t>
+          <t>COLORAU</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -24599,10 +24599,10 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="O314" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="P314" t="n">
         <v>0</v>
@@ -24625,22 +24625,22 @@
       </c>
       <c r="V314" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11839.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>11840</v>
+        <v>11843</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>COLORAU</t>
+          <t>COENTRO GRAO</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -24676,10 +24676,10 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="O315" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="P315" t="n">
         <v>0</v>
@@ -24702,22 +24702,22 @@
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.jpg</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>11843</v>
+        <v>11844</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>COENTRO GRAO</t>
+          <t>COENTRO FOLHAS</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -24753,10 +24753,10 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>17.5</v>
+        <v>64</v>
       </c>
       <c r="O316" t="n">
-        <v>17.5</v>
+        <v>64</v>
       </c>
       <c r="P316" t="n">
         <v>0</v>
@@ -24779,22 +24779,22 @@
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.jpg</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>11844</v>
+        <v>11845</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>COENTRO FOLHAS</t>
+          <t>COENTRO EM PO</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -24830,10 +24830,10 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="O317" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="P317" t="n">
         <v>0</v>
@@ -24856,22 +24856,22 @@
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.png</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>11845</v>
+        <v>11863</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>404</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>COENTRO EM PO</t>
+          <t>CHIMICHURRI SEM PIMENTA</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -24907,10 +24907,10 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="O318" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="P318" t="n">
         <v>0</v>
@@ -24933,22 +24933,22 @@
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>11863</v>
+        <v>11864</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>CHIMICHURRI SEM PIMENTA</t>
+          <t>CHIMICHURRI COM PIMENTA</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -25010,22 +25010,22 @@
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11864.webp</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>11864</v>
+        <v>11874</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CHIMICHURRI COM PIMENTA</t>
+          <t>CEBOLINHA DESIDRATADA</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -25061,10 +25061,10 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O320" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P320" t="n">
         <v>0</v>
@@ -25087,22 +25087,22 @@
       </c>
       <c r="V320" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11864.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11874.webp</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>11874</v>
+        <v>11875</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CEBOLINHA DESIDRATADA</t>
+          <t>CEBOLA, ALHO E SALSA</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -25138,10 +25138,10 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O321" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P321" t="n">
         <v>0</v>
@@ -25164,22 +25164,22 @@
       </c>
       <c r="V321" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11874.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>11875</v>
+        <v>11877</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CEBOLA, ALHO E SALSA</t>
+          <t>CEBOLA FLOCOS</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -25215,10 +25215,10 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O322" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P322" t="n">
         <v>0</v>
@@ -25241,22 +25241,22 @@
       </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>11877</v>
+        <v>11879</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>982</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>CEBOLA FLOCOS</t>
+          <t>CEBOLA EM PO</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -25292,10 +25292,10 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="O323" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P323" t="n">
         <v>0</v>
@@ -25318,22 +25318,22 @@
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11879.jpg</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>11879</v>
+        <v>11909</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CEBOLA EM PO</t>
+          <t>CARDAMOMO SEMENTES</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -25369,10 +25369,10 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>45</v>
+        <v>680</v>
       </c>
       <c r="O324" t="n">
-        <v>45</v>
+        <v>680</v>
       </c>
       <c r="P324" t="n">
         <v>0</v>
@@ -25395,22 +25395,22 @@
       </c>
       <c r="V324" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11879.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.jpg</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>11909</v>
+        <v>11910</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>CARDAMOMO SEMENTES</t>
+          <t>CARDAMOMO PO</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -25472,22 +25472,22 @@
       </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>11910</v>
+        <v>11913</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>CARDAMOMO PO</t>
+          <t>CANELA EM PO PURA</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -25523,10 +25523,10 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>680</v>
+        <v>35</v>
       </c>
       <c r="O326" t="n">
-        <v>680</v>
+        <v>35</v>
       </c>
       <c r="P326" t="n">
         <v>0</v>
@@ -25549,22 +25549,22 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.jpg</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>11913</v>
+        <v>11931</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>CANELA EM PO PURA</t>
+          <t>BICARBONATO DE SODIO</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -25600,10 +25600,10 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>35</v>
+        <v>10.5</v>
       </c>
       <c r="O327" t="n">
-        <v>35</v>
+        <v>10.5</v>
       </c>
       <c r="P327" t="n">
         <v>0</v>
@@ -25626,22 +25626,22 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.png</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>11931</v>
+        <v>12004</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>BICARBONATO DE SODIO</t>
+          <t>ALHO ROXO</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -25677,10 +25677,10 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>10.5</v>
+        <v>49</v>
       </c>
       <c r="O328" t="n">
-        <v>10.5</v>
+        <v>49</v>
       </c>
       <c r="P328" t="n">
         <v>0</v>
@@ -25703,22 +25703,22 @@
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>12004</v>
+        <v>12006</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ALHO ROXO</t>
+          <t>ALHO LAMINADO DESIDRATADO</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -25754,10 +25754,10 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="O329" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="P329" t="n">
         <v>0</v>
@@ -25780,22 +25780,22 @@
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.webp</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>12006</v>
+        <v>12008</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>ALHO LAMINADO DESIDRATADO</t>
+          <t>ALHO GRANULADO</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -25831,10 +25831,10 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="O330" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="P330" t="n">
         <v>0</v>
@@ -25857,22 +25857,22 @@
       </c>
       <c r="V330" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.webp</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>12008</v>
+        <v>12010</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>422</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>ALHO GRANULADO</t>
+          <t>ALHO FRITO</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -25908,10 +25908,10 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O331" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P331" t="n">
         <v>0</v>
@@ -25934,22 +25934,22 @@
       </c>
       <c r="V331" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>12010</v>
+        <v>12011</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>ALHO FRITO</t>
+          <t>ALHO EM PO 100% PURO</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -25985,10 +25985,10 @@
         </is>
       </c>
       <c r="N332" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O332" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P332" t="n">
         <v>0</v>
@@ -26011,22 +26011,22 @@
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>12011</v>
+        <v>12019</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>ALHO EM PO 100% PURO</t>
+          <t>ALECRIM</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -26088,22 +26088,22 @@
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>12019</v>
+        <v>12023</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>ALECRIM</t>
+          <t>AIPO</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -26139,10 +26139,10 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O334" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P334" t="n">
         <v>0</v>
@@ -26165,22 +26165,22 @@
       </c>
       <c r="V334" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12023.jpg</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>12023</v>
+        <v>12031</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>AIPO</t>
+          <t>ACAFRAO NACIONAL</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -26216,10 +26216,10 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="O335" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="P335" t="n">
         <v>0</v>
@@ -26242,22 +26242,22 @@
       </c>
       <c r="V335" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12023.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>12031</v>
+        <v>12080</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>ACAFRAO NACIONAL</t>
+          <t>CALDO DE GALINHA</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -26293,10 +26293,10 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="O336" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="P336" t="n">
         <v>0</v>
@@ -26319,22 +26319,22 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.jpg</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>12080</v>
+        <v>12098</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>CALDO DE GALINHA</t>
+          <t>CALDO DE LEGUMES</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -26370,10 +26370,10 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O337" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P337" t="n">
         <v>0</v>
@@ -26396,22 +26396,22 @@
       </c>
       <c r="V337" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>12098</v>
+        <v>12105</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>CALDO DE LEGUMES</t>
+          <t>EDU GUEDES</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -26447,10 +26447,10 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O338" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P338" t="n">
         <v>0</v>
@@ -26473,22 +26473,22 @@
       </c>
       <c r="V338" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>12104</v>
+        <v>12106</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO PRETA PO CONDIMENTADA</t>
+          <t>ANA MARIA</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -26524,10 +26524,10 @@
         </is>
       </c>
       <c r="N339" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O339" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P339" t="n">
         <v>0</v>
@@ -26550,22 +26550,22 @@
       </c>
       <c r="V339" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12104.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>12105</v>
+        <v>12107</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>EDU GUEDES</t>
+          <t>CEBOLA, ALHO E SALSA</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -26601,10 +26601,10 @@
         </is>
       </c>
       <c r="N340" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="O340" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P340" t="n">
         <v>0</v>
@@ -26627,22 +26627,22 @@
       </c>
       <c r="V340" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>12106</v>
+        <v>12108</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>ANA MARIA</t>
+          <t>CHIMICHURRI SEM PIMENTA</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -26678,10 +26678,10 @@
         </is>
       </c>
       <c r="N341" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="O341" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="P341" t="n">
         <v>0</v>
@@ -26704,22 +26704,22 @@
       </c>
       <c r="V341" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>12107</v>
+        <v>12109</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>CEBOLA, ALHO E SALSA</t>
+          <t>CHIMICHURRI COM PIMENTA</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -26755,10 +26755,10 @@
         </is>
       </c>
       <c r="N342" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="O342" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P342" t="n">
         <v>0</v>
@@ -26781,22 +26781,22 @@
       </c>
       <c r="V342" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12109.webp</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>12108</v>
+        <v>12096</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>CHIMICHURRI SEM PIMENTA</t>
+          <t>PEGA MARIDO FIT</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -26832,10 +26832,10 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="O343" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P343" t="n">
         <v>0</v>
@@ -26858,22 +26858,22 @@
       </c>
       <c r="V343" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.webp</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>12109</v>
+        <v>12097</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>CHIMICHURRI COM PIMENTA</t>
+          <t>EDU GUEDES FIT</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -26935,22 +26935,22 @@
       </c>
       <c r="V344" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12109.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12097.jpg</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>12096</v>
+        <v>12119</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>PEGA MARIDO FIT</t>
+          <t>CEBOLA GRANULADA</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -26986,10 +26986,10 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="O345" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="P345" t="n">
         <v>0</v>
@@ -27012,22 +27012,22 @@
       </c>
       <c r="V345" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.jpg</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>12097</v>
+        <v>12115</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>EDU GUEDES FIT</t>
+          <t>LEMON PEPPER C/ GLUTAMATO</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -27063,10 +27063,10 @@
         </is>
       </c>
       <c r="N346" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O346" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P346" t="n">
         <v>0</v>
@@ -27089,22 +27089,22 @@
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12097.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.webp</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>12119</v>
+        <v>12145</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>CEBOLA GRANULADA</t>
+          <t>CHIMICHURRI FIT</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -27140,10 +27140,10 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="O347" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="P347" t="n">
         <v>0</v>
@@ -27166,22 +27166,22 @@
       </c>
       <c r="V347" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.webp</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>12115</v>
+        <v>12146</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>LEMON PEPPER C/ GLUTAMATO</t>
+          <t>CHIMICHURRI C/ PIMENTA FIT</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -27217,10 +27217,10 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O348" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P348" t="n">
         <v>0</v>
@@ -27243,22 +27243,22 @@
       </c>
       <c r="V348" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.webp</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>12145</v>
+        <v>12147</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>716</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>CHIMICHURRI FIT</t>
+          <t>LEMON PEPPER FIT</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -27294,10 +27294,10 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="O349" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P349" t="n">
         <v>0</v>
@@ -27320,22 +27320,22 @@
       </c>
       <c r="V349" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.webp</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>12146</v>
+        <v>12148</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>CHIMICHURRI C/ PIMENTA FIT</t>
+          <t>TEMPERO ANA MARIA FIT</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -27371,10 +27371,10 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="O350" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="P350" t="n">
         <v>0</v>
@@ -27397,37 +27397,37 @@
       </c>
       <c r="V350" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>12147</v>
+        <v>12160</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>LEMON PEPPER FIT</t>
+          <t>MOSTARDA GRAO MARROM 100G</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H351" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I351" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J351" t="n">
         <v>100</v>
@@ -27448,10 +27448,10 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="O351" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="P351" t="n">
         <v>0</v>
@@ -27465,31 +27465,31 @@
         </is>
       </c>
       <c r="T351" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U351" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V351" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>12148</v>
+        <v>12161</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>TEMPERO ANA MARIA FIT</t>
+          <t>NOZ MOSCADA PO CONDIMENTADA</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -27525,10 +27525,10 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="O352" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="P352" t="n">
         <v>0</v>
@@ -27551,37 +27551,37 @@
       </c>
       <c r="V352" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>12160</v>
+        <v>12164</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>MOSTARDA GRAO MARROM 100G</t>
+          <t>PIMENTA JAMAICA (SIRIA PO)</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G353" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H353" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I353" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J353" t="n">
         <v>100</v>
@@ -27602,10 +27602,10 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="O353" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="P353" t="n">
         <v>0</v>
@@ -27619,245 +27619,14 @@
         </is>
       </c>
       <c r="T353" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U353" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V353" t="inlineStr">
-        <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
-        <v>12161</v>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>NOZ MOSCADA PO CONDIMENTADA</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="G354" t="n">
-        <v>10</v>
-      </c>
-      <c r="H354" t="n">
-        <v>10</v>
-      </c>
-      <c r="I354" t="n">
-        <v>5</v>
-      </c>
-      <c r="J354" t="n">
-        <v>100</v>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t>TEMPEROS A GRANEL</t>
-        </is>
-      </c>
-      <c r="N354" t="n">
-        <v>160</v>
-      </c>
-      <c r="O354" t="n">
-        <v>160</v>
-      </c>
-      <c r="P354" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="T354" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U354" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="V354" t="inlineStr">
-        <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
-        <v>12162</v>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>COMINHO PO CONDIMENTADO</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="G355" t="n">
-        <v>10</v>
-      </c>
-      <c r="H355" t="n">
-        <v>10</v>
-      </c>
-      <c r="I355" t="n">
-        <v>5</v>
-      </c>
-      <c r="J355" t="n">
-        <v>100</v>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>TEMPEROS A GRANEL</t>
-        </is>
-      </c>
-      <c r="N355" t="n">
-        <v>65</v>
-      </c>
-      <c r="O355" t="n">
-        <v>65</v>
-      </c>
-      <c r="P355" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
-      <c r="S355" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="T355" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U355" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="V355" t="inlineStr">
-        <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12162.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
-        <v>12164</v>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>PIMENTA JAMAICA (SIRIA PO)</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="G356" t="n">
-        <v>10</v>
-      </c>
-      <c r="H356" t="n">
-        <v>10</v>
-      </c>
-      <c r="I356" t="n">
-        <v>5</v>
-      </c>
-      <c r="J356" t="n">
-        <v>100</v>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M356" t="inlineStr">
-        <is>
-          <t>TEMPEROS A GRANEL</t>
-        </is>
-      </c>
-      <c r="N356" t="n">
-        <v>85</v>
-      </c>
-      <c r="O356" t="n">
-        <v>85</v>
-      </c>
-      <c r="P356" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
-      <c r="S356" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="T356" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U356" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="V356" t="inlineStr">
         <is>
           <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.jpg</t>
         </is>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -12151,7 +12151,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11779.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11779.webp</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.jpg</t>
         </is>
       </c>
     </row>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11953.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11953.png</t>
         </is>
       </c>
     </row>
@@ -20005,7 +20005,7 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.jpg</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.jpg</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.jpg</t>
         </is>
       </c>
     </row>
@@ -21622,7 +21622,7 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.jpg</t>
         </is>
       </c>
     </row>
@@ -22623,7 +22623,7 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.jpg</t>
         </is>
       </c>
     </row>
@@ -23778,7 +23778,7 @@
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
         </is>
       </c>
     </row>
@@ -25626,7 +25626,7 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.webp</t>
         </is>
       </c>
     </row>
@@ -26858,7 +26858,7 @@
       </c>
       <c r="V343" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.jpg</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.jpg</t>
         </is>
       </c>
     </row>
@@ -27320,7 +27320,7 @@
       </c>
       <c r="V349" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.jpg</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -20005,7 +20005,7 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.png</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.png</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -1063,7 +1063,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12174.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/adocantes-naturais/12174.jpg</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11996.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11996.jpg</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/chips-e-snacks/11998.jpg</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/10944.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/10944.jpg</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11594.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11594.png</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11868.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11868.jpg</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11968.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/11968.png</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11771.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11771.jpg</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11774.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11774.jpg</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11779.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11779.jpg</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.png</t>
         </is>
       </c>
     </row>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.jpg</t>
         </is>
       </c>
     </row>
@@ -22469,7 +22469,7 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.jpg</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -7685,7 +7685,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11480.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11480.png</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11898.jpg</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11940.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11940.webp</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/10886.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/ervas/10886.webp</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11762.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11762.jpg</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11765.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11765.jpg</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11767.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11767.jpg</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11778.jpg</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -11612,7 +11612,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.webp</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11779.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11779.webp</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.jpg</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11662.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11662.jpg</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF353"/>
+  <dimension ref="A1:AF352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12176.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12176.webp</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10278.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/10278.jpg</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11941.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/drageados/11941.jpg</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.png</t>
         </is>
       </c>
     </row>
@@ -12311,34 +12311,34 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>11782</v>
+        <v>11783</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FARINHA DE CHIA 200G</t>
+          <t>FARINHA DE CENTEIO</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>UNI</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H155" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I155" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J155" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -12356,10 +12356,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>8</v>
+        <v>15.8</v>
       </c>
       <c r="O155" t="n">
-        <v>8</v>
+        <v>15.8</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -12373,31 +12373,31 @@
         </is>
       </c>
       <c r="T155" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11782.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11783.webp</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>11783</v>
+        <v>11784</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FARINHA DE CENTEIO</t>
+          <t>FARINHA DE CASTANHA DE CAJU</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -12433,10 +12433,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>15.8</v>
+        <v>65</v>
       </c>
       <c r="O156" t="n">
-        <v>15.8</v>
+        <v>65</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -12459,22 +12459,22 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11783.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.jpg</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>11784</v>
+        <v>11786</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>586</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FARINHA DE CASTANHA DE CAJU</t>
+          <t>FARINHA DE BERINJELA</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="O157" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -12536,22 +12536,22 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11784.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11786.jpg</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>11786</v>
+        <v>11787</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FARINHA DE BERINJELA</t>
+          <t>FARINHA DE BATATA DOCE 100G</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>55</v>
+        <v>4.5</v>
       </c>
       <c r="O158" t="n">
-        <v>55</v>
+        <v>4.5</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -12613,22 +12613,22 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11786.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.jpg</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>11787</v>
+        <v>11789</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FARINHA DE BATATA DOCE 100G</t>
+          <t>FARINHA DE BANANA VERDE</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>4.5</v>
+        <v>35</v>
       </c>
       <c r="O159" t="n">
-        <v>4.5</v>
+        <v>35</v>
       </c>
       <c r="P159" t="n">
         <v>0</v>
@@ -12690,22 +12690,22 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11787.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.jpg</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>11789</v>
+        <v>11790</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FARINHA DE BANANA VERDE</t>
+          <t>FARINHA DE AVEIA</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -12741,10 +12741,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>35</v>
+        <v>9.9</v>
       </c>
       <c r="O160" t="n">
-        <v>35</v>
+        <v>9.9</v>
       </c>
       <c r="P160" t="n">
         <v>0</v>
@@ -12767,22 +12767,22 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11789.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11790.jpg</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>11790</v>
+        <v>11791</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FARINHA DE AVEIA</t>
+          <t>FARINHA DE ARROZ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -12818,10 +12818,10 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>9.9</v>
+        <v>11.5</v>
       </c>
       <c r="O161" t="n">
-        <v>9.9</v>
+        <v>11.5</v>
       </c>
       <c r="P161" t="n">
         <v>0</v>
@@ -12844,37 +12844,37 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11790.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11791.jpg</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>11791</v>
+        <v>11792</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FARINHA DE ARROZ</t>
+          <t>FARINHA DE AMORA 100G</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H162" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I162" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J162" t="n">
         <v>100</v>
@@ -12895,10 +12895,10 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="O162" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="P162" t="n">
         <v>0</v>
@@ -12912,46 +12912,46 @@
         </is>
       </c>
       <c r="T162" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11791.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11792.jpg</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>11792</v>
+        <v>11794</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>980</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FARINHA DE AMORA 100G</t>
+          <t>FARINHA DE AMENDOA</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H163" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I163" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J163" t="n">
         <v>100</v>
@@ -12972,10 +12972,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="O163" t="n">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="P163" t="n">
         <v>0</v>
@@ -12989,31 +12989,31 @@
         </is>
       </c>
       <c r="T163" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11792.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11794.jpg</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>11794</v>
+        <v>11795</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FARINHA DE AMENDOA</t>
+          <t>FARELO DE TRIGO TOSTADO</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="O164" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="P164" t="n">
         <v>0</v>
@@ -13075,22 +13075,22 @@
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11794.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11795.jpg</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>11795</v>
+        <v>11796</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>149</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FARELO DE TRIGO TOSTADO</t>
+          <t>FARELO DE AVEIA</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -13126,10 +13126,10 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O165" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -13152,22 +13152,22 @@
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11795.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11796.jpg</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>11796</v>
+        <v>11952</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FARELO DE AVEIA</t>
+          <t>AVEIA LAMINADA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -13203,10 +13203,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>15</v>
+        <v>9.9</v>
       </c>
       <c r="O166" t="n">
-        <v>15</v>
+        <v>9.9</v>
       </c>
       <c r="P166" t="n">
         <v>0</v>
@@ -13229,22 +13229,22 @@
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11796.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11952.webp</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>11952</v>
+        <v>11953</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AVEIA LAMINADA</t>
+          <t>AVEIA FLOCOS</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11952.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11953.png</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>11953</v>
+        <v>11966</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AVEIA FLOCOS</t>
+          <t>ARARUTA 250G</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>9.9</v>
+        <v>29.9</v>
       </c>
       <c r="O168" t="n">
-        <v>9.9</v>
+        <v>29.9</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
@@ -13383,22 +13383,22 @@
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11953.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11966.webp</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>11966</v>
+        <v>11972</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ARARUTA 250G</t>
+          <t>AMIDO DE MILHO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>29.9</v>
+        <v>8</v>
       </c>
       <c r="O169" t="n">
-        <v>29.9</v>
+        <v>8</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
@@ -13460,22 +13460,22 @@
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11966.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.jpg</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>11972</v>
+        <v>12093</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AMIDO DE MILHO</t>
+          <t>FARINHA DE CHIA</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="O170" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="P170" t="n">
         <v>0</v>
@@ -13537,37 +13537,37 @@
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11972.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/12093.jpg</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>12093</v>
+        <v>10097</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FARINHA DE CHIA</t>
+          <t>GOJI BERRY 100G</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H171" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I171" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J171" t="n">
         <v>100</v>
@@ -13584,14 +13584,14 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>FARINACEOS E FARINHAS NATURAIS</t>
+          <t>FRUTAS SECAS</t>
         </is>
       </c>
       <c r="N171" t="n">
-        <v>40</v>
+        <v>8.9</v>
       </c>
       <c r="O171" t="n">
-        <v>40</v>
+        <v>8.9</v>
       </c>
       <c r="P171" t="n">
         <v>0</v>
@@ -13609,42 +13609,42 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/12093.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10097.png</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>10097</v>
+        <v>10883</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>681</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>GOJI BERRY 100G</t>
+          <t>MORANGO DESIDRATADO</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H172" t="n">
         <v>5</v>
       </c>
       <c r="I172" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J172" t="n">
         <v>100</v>
@@ -13665,10 +13665,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>8.9</v>
+        <v>120</v>
       </c>
       <c r="O172" t="n">
-        <v>8.9</v>
+        <v>120</v>
       </c>
       <c r="P172" t="n">
         <v>0</v>
@@ -13686,27 +13686,27 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10097.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10883.jpg</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>10883</v>
+        <v>11094</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>526</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MORANGO DESIDRATADO</t>
+          <t>MIX DE FRUTAS VERMELHAS</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -13742,10 +13742,10 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="O173" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="P173" t="n">
         <v>0</v>
@@ -13768,22 +13768,22 @@
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/10883.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11094.jpg</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>11094</v>
+        <v>11104</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MIX DE FRUTAS VERMELHAS</t>
+          <t>LIMAO EM TIRAS CRISTALIZADO</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="O174" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="P174" t="n">
         <v>0</v>
@@ -13845,22 +13845,22 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11094.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11104.jpg</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>11104</v>
+        <v>11446</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>LIMAO EM TIRAS CRISTALIZADO</t>
+          <t>CEREJA EM CALDA SEM CABO LATA 1.8 KG</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -13896,10 +13896,10 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="O175" t="n">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="P175" t="n">
         <v>0</v>
@@ -13922,22 +13922,22 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11104.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.webp</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>11446</v>
+        <v>11447</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CEREJA EM CALDA SEM CABO LATA 1.8 KG</t>
+          <t>CEREJA EM CALDA COM CABO LATA COM 1.65KG</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -13973,10 +13973,10 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>96</v>
+        <v>163.9</v>
       </c>
       <c r="O176" t="n">
-        <v>96</v>
+        <v>163.9</v>
       </c>
       <c r="P176" t="n">
         <v>0</v>
@@ -13999,22 +13999,22 @@
       </c>
       <c r="V176" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11446.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.webp</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>11447</v>
+        <v>11479</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>296</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CEREJA EM CALDA COM CABO LATA COM 1.65KG</t>
+          <t>UVA PASSA PRETA</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -14050,10 +14050,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>163.9</v>
+        <v>36.5</v>
       </c>
       <c r="O177" t="n">
-        <v>163.9</v>
+        <v>36.5</v>
       </c>
       <c r="P177" t="n">
         <v>0</v>
@@ -14076,22 +14076,22 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11447.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11479.jpg</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>11479</v>
+        <v>11483</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>UVA PASSA PRETA</t>
+          <t>UVA PASSA BRANCA</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>36.5</v>
+        <v>65</v>
       </c>
       <c r="O178" t="n">
-        <v>36.5</v>
+        <v>65</v>
       </c>
       <c r="P178" t="n">
         <v>0</v>
@@ -14153,22 +14153,22 @@
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11479.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11483.jpg</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>11483</v>
+        <v>11508</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>153</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>UVA PASSA BRANCA</t>
+          <t>TAMARA SEM CAROCO</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -14204,10 +14204,10 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="O179" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="P179" t="n">
         <v>0</v>
@@ -14230,22 +14230,22 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11483.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11508.jpg</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>11508</v>
+        <v>11509</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TAMARA SEM CAROCO</t>
+          <t>TAMARA JUMBO</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="O180" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="P180" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11508.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.jpg</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>11509</v>
+        <v>11612</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TAMARA JUMBO</t>
+          <t>MIX DE FRUTAS</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="O181" t="n">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="P181" t="n">
         <v>0</v>
@@ -14384,22 +14384,22 @@
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11612.jpg</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>11612</v>
+        <v>11641</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>MIX DE FRUTAS</t>
+          <t>MACA DESIDRATADA DESCASCADAS EM RODELAS</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -14435,10 +14435,10 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="P182" t="n">
         <v>0</v>
@@ -14461,22 +14461,22 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11612.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11641.webp</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>11641</v>
+        <v>11662</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MACA DESIDRATADA DESCASCADAS EM RODELAS</t>
+          <t>LARANJA EM TIRAS CRISTALIZADAS</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -14512,10 +14512,10 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O183" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P183" t="n">
         <v>0</v>
@@ -14538,22 +14538,22 @@
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11641.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11662.jpg</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>11662</v>
+        <v>11693</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>LARANJA EM TIRAS CRISTALIZADAS</t>
+          <t>GOJI BERRY</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="O184" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="P184" t="n">
         <v>0</v>
@@ -14615,22 +14615,22 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11662.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11693.png</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>11693</v>
+        <v>11710</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>GOJI BERRY</t>
+          <t>GENGIBRE EM CUBOS</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -14666,10 +14666,10 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="O185" t="n">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
@@ -14692,22 +14692,22 @@
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11693.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11710.jpg</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>11710</v>
+        <v>11713</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>GENGIBRE EM CUBOS</t>
+          <t>GARCINIA FRUTAS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -14743,10 +14743,10 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="O186" t="n">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="P186" t="n">
         <v>0</v>
@@ -14769,22 +14769,22 @@
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11710.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11713.jpg</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>11713</v>
+        <v>11723</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>124</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>GARCINIA FRUTAS</t>
+          <t>FRUTAS CRISTALIZADAS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -14820,10 +14820,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="O187" t="n">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="P187" t="n">
         <v>0</v>
@@ -14846,22 +14846,22 @@
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11713.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11723.jpg</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>11723</v>
+        <v>11728</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>FRUTAS CRISTALIZADAS</t>
+          <t>FIGO TURCO SECO</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -14897,10 +14897,10 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="O188" t="n">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="P188" t="n">
         <v>0</v>
@@ -14923,22 +14923,22 @@
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11723.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11728.jpg</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>11728</v>
+        <v>11730</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FIGO TURCO SECO</t>
+          <t>FIGO CRISTALIZADO</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -14974,10 +14974,10 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="O189" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="P189" t="n">
         <v>0</v>
@@ -15000,22 +15000,22 @@
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11728.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11730.jpg</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>11730</v>
+        <v>11828</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>FIGO CRISTALIZADO</t>
+          <t>DAMASCO</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="O190" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Q190" t="n">
         <v>0</v>
@@ -15077,22 +15077,22 @@
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11730.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11828.jpg</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>11828</v>
+        <v>11836</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>DAMASCO</t>
+          <t>CRANBERRY INTEIRO</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -15128,13 +15128,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="O191" t="n">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="P191" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="Q191" t="n">
         <v>0</v>
@@ -15154,22 +15154,22 @@
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11828.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11836.jpg</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>11836</v>
+        <v>11929</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>CRANBERRY INTEIRO</t>
+          <t>BLUE BERRY</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -15205,10 +15205,10 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>85</v>
+        <v>278</v>
       </c>
       <c r="O192" t="n">
-        <v>85</v>
+        <v>278</v>
       </c>
       <c r="P192" t="n">
         <v>0</v>
@@ -15231,22 +15231,22 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11836.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11929.jpg</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>11929</v>
+        <v>11943</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>BLUE BERRY</t>
+          <t>BANANA PASSA</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>278</v>
+        <v>55</v>
       </c>
       <c r="O193" t="n">
-        <v>278</v>
+        <v>55</v>
       </c>
       <c r="P193" t="n">
         <v>0</v>
@@ -15308,22 +15308,22 @@
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11929.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11943.png</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>11943</v>
+        <v>12001</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BANANA PASSA</t>
+          <t>AMEIXA SEM CAROCO</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -15385,22 +15385,22 @@
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11943.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12001.jpg</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>12001</v>
+        <v>12035</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>AMEIXA SEM CAROCO</t>
+          <t>ABACAXI CRISTALIZADO</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -15436,10 +15436,10 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="O195" t="n">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="P195" t="n">
         <v>0</v>
@@ -15462,22 +15462,22 @@
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12001.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12035.jpg</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>12035</v>
+        <v>12053</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ABACAXI CRISTALIZADO</t>
+          <t>KIWI GLACEAGO</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -15513,10 +15513,10 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O196" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P196" t="n">
         <v>0</v>
@@ -15539,22 +15539,22 @@
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12035.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12053.webp</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>12053</v>
+        <v>12054</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>KIWI GLACEAGO</t>
+          <t>CEREJA DESIDRATADA</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="O197" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="P197" t="n">
         <v>0</v>
@@ -15616,22 +15616,22 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12053.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12054.jpg</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>12054</v>
+        <v>12151</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>488</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>CEREJA DESIDRATADA</t>
+          <t>TAMARA LARGE JUMBO</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -15667,10 +15667,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O198" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="P198" t="n">
         <v>0</v>
@@ -15693,22 +15693,22 @@
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12054.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.jpg</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>12151</v>
+        <v>10831</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>306</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TAMARA LARGE JUMBO</t>
+          <t>FENO GREGO MOIDO</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -15720,7 +15720,7 @@
         <v>10</v>
       </c>
       <c r="H199" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I199" t="n">
         <v>5</v>
@@ -15740,14 +15740,14 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>FRUTAS SECAS</t>
+          <t>GRAOS</t>
         </is>
       </c>
       <c r="N199" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="O199" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="P199" t="n">
         <v>0</v>
@@ -15765,27 +15765,27 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>100gr</t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.jpg</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>10831</v>
+        <v>11491</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>527</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>FENO GREGO MOIDO</t>
+          <t>TRIGO EM GRAO</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -15821,10 +15821,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="O200" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="P200" t="n">
         <v>0</v>
@@ -15847,22 +15847,22 @@
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.jpg</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>11491</v>
+        <v>11515</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>TRIGO EM GRAO</t>
+          <t>SOJA GRAO</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -15898,10 +15898,10 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="O201" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="P201" t="n">
         <v>0</v>
@@ -15924,22 +15924,22 @@
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.jpg</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>11515</v>
+        <v>11528</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SOJA GRAO</t>
+          <t>SAGU</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -15975,10 +15975,10 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>9.9</v>
+        <v>16</v>
       </c>
       <c r="O202" t="n">
-        <v>9.9</v>
+        <v>16</v>
       </c>
       <c r="P202" t="n">
         <v>0</v>
@@ -16001,22 +16001,22 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11528.webp</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>11528</v>
+        <v>11535</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SAGU</t>
+          <t>QUIRELA 500G</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -16052,10 +16052,10 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>16</v>
+        <v>3.6</v>
       </c>
       <c r="O203" t="n">
-        <v>16</v>
+        <v>3.6</v>
       </c>
       <c r="P203" t="n">
         <v>0</v>
@@ -16078,22 +16078,22 @@
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11528.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.jpg</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>11535</v>
+        <v>11536</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>QUIRELA 500G</t>
+          <t>QUINUA GRAO</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -16129,10 +16129,10 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>3.6</v>
+        <v>38</v>
       </c>
       <c r="O204" t="n">
-        <v>3.6</v>
+        <v>38</v>
       </c>
       <c r="P204" t="n">
         <v>0</v>
@@ -16155,22 +16155,22 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.webp</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>11536</v>
+        <v>11610</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>QUINUA GRAO</t>
+          <t>MIX QUINUA</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O205" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="P205" t="n">
         <v>0</v>
@@ -16232,22 +16232,22 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.jpg</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>11610</v>
+        <v>11617</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MIX QUINUA</t>
+          <t>MILHO DE PIPOCA</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>46</v>
+        <v>7.5</v>
       </c>
       <c r="O206" t="n">
-        <v>46</v>
+        <v>7.5</v>
       </c>
       <c r="P206" t="n">
         <v>0</v>
@@ -16309,22 +16309,22 @@
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.jpg</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>11617</v>
+        <v>11651</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>MILHO DE PIPOCA</t>
+          <t>LENTILHA VERMELHA</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>7.5</v>
+        <v>24.5</v>
       </c>
       <c r="O207" t="n">
-        <v>7.5</v>
+        <v>24.5</v>
       </c>
       <c r="P207" t="n">
         <v>0</v>
@@ -16386,22 +16386,22 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.jpg</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>11651</v>
+        <v>11652</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>LENTILHA VERMELHA</t>
+          <t>LENTILHA</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -16437,10 +16437,10 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
       <c r="O208" t="n">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
       <c r="P208" t="n">
         <v>0</v>
@@ -16463,22 +16463,22 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11652.jpg</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>11652</v>
+        <v>11686</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>LENTILHA</t>
+          <t>GRAO DE BICO  MIUDO</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -16514,10 +16514,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="O209" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="P209" t="n">
         <v>0</v>
@@ -16540,22 +16540,22 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11652.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11686.png</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>11686</v>
+        <v>11687</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>GRAO DE BICO  MIUDO</t>
+          <t>GRAO DE BICO GRAUDO</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -16591,10 +16591,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>17.5</v>
+        <v>26.9</v>
       </c>
       <c r="O210" t="n">
-        <v>17.5</v>
+        <v>26.9</v>
       </c>
       <c r="P210" t="n">
         <v>0</v>
@@ -16617,22 +16617,22 @@
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11686.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11687.webp</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>11687</v>
+        <v>11731</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>GRAO DE BICO GRAUDO</t>
+          <t>FENO GREGO EM GRAOS</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>26.9</v>
+        <v>34</v>
       </c>
       <c r="O211" t="n">
-        <v>26.9</v>
+        <v>34</v>
       </c>
       <c r="P211" t="n">
         <v>0</v>
@@ -16694,27 +16694,27 @@
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11687.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.jpg</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>11731</v>
+        <v>11732</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>FENO GREGO EM GRAOS</t>
+          <t>FEIJAO VERMELHO 500G</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -16745,10 +16745,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="O212" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="P212" t="n">
         <v>0</v>
@@ -16762,36 +16762,36 @@
         </is>
       </c>
       <c r="T212" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>100gr</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11732.jpg</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>11732</v>
+        <v>11734</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>519</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>FEIJAO VERMELHO 500G</t>
+          <t>FEIJAO ROXAO</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -16822,10 +16822,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>11</v>
+        <v>24.8</v>
       </c>
       <c r="O213" t="n">
-        <v>11</v>
+        <v>24.8</v>
       </c>
       <c r="P213" t="n">
         <v>0</v>
@@ -16839,31 +16839,31 @@
         </is>
       </c>
       <c r="T213" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100gr</t>
         </is>
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11732.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11734.jpg</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>11734</v>
+        <v>11735</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>FEIJAO ROXAO</t>
+          <t>FEIJAO ROSINHA</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -16899,10 +16899,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>24.8</v>
+        <v>18</v>
       </c>
       <c r="O214" t="n">
-        <v>24.8</v>
+        <v>18</v>
       </c>
       <c r="P214" t="n">
         <v>0</v>
@@ -16925,22 +16925,22 @@
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11734.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.jpg</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>11735</v>
+        <v>11737</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>FEIJAO ROSINHA</t>
+          <t>FEIJAO PRETO</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -16976,10 +16976,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>18</v>
+        <v>8.9</v>
       </c>
       <c r="O215" t="n">
-        <v>18</v>
+        <v>8.9</v>
       </c>
       <c r="P215" t="n">
         <v>0</v>
@@ -17002,22 +17002,22 @@
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11737.png</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>11737</v>
+        <v>11738</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>FEIJAO PRETO</t>
+          <t>FEIJAO MOYASHI</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>8.9</v>
+        <v>19</v>
       </c>
       <c r="O216" t="n">
-        <v>8.9</v>
+        <v>19</v>
       </c>
       <c r="P216" t="n">
         <v>0</v>
@@ -17079,22 +17079,22 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11737.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.jpg</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>11738</v>
+        <v>11741</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>FEIJAO MOYASHI</t>
+          <t>FEIJAO FRADINHO</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>19</v>
+        <v>9.9</v>
       </c>
       <c r="O217" t="n">
-        <v>19</v>
+        <v>9.9</v>
       </c>
       <c r="P217" t="n">
         <v>0</v>
@@ -17156,22 +17156,22 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.webp</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>11741</v>
+        <v>11743</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>FEIJAO FRADINHO</t>
+          <t>FEIJAO CORDA</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -17207,10 +17207,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="O218" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="P218" t="n">
         <v>0</v>
@@ -17233,22 +17233,22 @@
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11743.webp</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>11743</v>
+        <v>11744</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FEIJAO CORDA</t>
+          <t>FEIJAO CARIOCA</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="O219" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="P219" t="n">
         <v>0</v>
@@ -17310,22 +17310,22 @@
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11743.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.jpg</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>11744</v>
+        <v>11745</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FEIJAO CARIOCA</t>
+          <t>FEIJAO BRANCO</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -17361,10 +17361,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="O220" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="P220" t="n">
         <v>0</v>
@@ -17387,22 +17387,22 @@
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.jpg</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>11745</v>
+        <v>11747</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FEIJAO BRANCO</t>
+          <t>FEIJAO BOLINHA</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -17438,10 +17438,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>15.9</v>
+        <v>24.9</v>
       </c>
       <c r="O221" t="n">
-        <v>15.9</v>
+        <v>24.9</v>
       </c>
       <c r="P221" t="n">
         <v>0</v>
@@ -17464,22 +17464,22 @@
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11747.jpg</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>11747</v>
+        <v>11748</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>335</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>FEIJAO BOLINHA</t>
+          <t>FEIJAO AZUKI</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -17515,10 +17515,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>24.9</v>
+        <v>19</v>
       </c>
       <c r="O222" t="n">
-        <v>24.9</v>
+        <v>19</v>
       </c>
       <c r="P222" t="n">
         <v>0</v>
@@ -17541,22 +17541,22 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11747.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.jpg</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>11748</v>
+        <v>11749</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FEIJAO AZUKI</t>
+          <t>FEIJAO ANDU</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -17592,10 +17592,10 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>19</v>
+        <v>26.9</v>
       </c>
       <c r="O223" t="n">
-        <v>19</v>
+        <v>26.9</v>
       </c>
       <c r="P223" t="n">
         <v>0</v>
@@ -17618,22 +17618,22 @@
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.jpg</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>11749</v>
+        <v>11751</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FEIJAO ANDU</t>
+          <t>FAVA BRANCA MIUDA</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -17669,10 +17669,10 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>26.9</v>
+        <v>42</v>
       </c>
       <c r="O224" t="n">
-        <v>26.9</v>
+        <v>42</v>
       </c>
       <c r="P224" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.jpg</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>11751</v>
+        <v>11752</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FAVA BRANCA MIUDA</t>
+          <t>FAVA BRANCA GRAUDA</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -17746,10 +17746,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>42</v>
+        <v>32.9</v>
       </c>
       <c r="O225" t="n">
-        <v>42</v>
+        <v>32.9</v>
       </c>
       <c r="P225" t="n">
         <v>0</v>
@@ -17772,22 +17772,22 @@
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.jpg</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>11752</v>
+        <v>11804</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FAVA BRANCA GRAUDA</t>
+          <t>ERVILHA PARTIDA</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -17823,10 +17823,10 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>32.9</v>
+        <v>16</v>
       </c>
       <c r="O226" t="n">
-        <v>32.9</v>
+        <v>16</v>
       </c>
       <c r="P226" t="n">
         <v>0</v>
@@ -17849,22 +17849,22 @@
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.webp</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>11804</v>
+        <v>11911</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ERVILHA PARTIDA</t>
+          <t>CANJICA BRANCA</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -17900,10 +17900,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>16</v>
+        <v>9.9</v>
       </c>
       <c r="O227" t="n">
-        <v>16</v>
+        <v>9.9</v>
       </c>
       <c r="P227" t="n">
         <v>0</v>
@@ -17926,22 +17926,22 @@
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.jpg</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>11911</v>
+        <v>11912</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CANJICA BRANCA</t>
+          <t>CANJICA AMARELA</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>9.9</v>
+        <v>6.25</v>
       </c>
       <c r="O228" t="n">
-        <v>9.9</v>
+        <v>6.25</v>
       </c>
       <c r="P228" t="n">
         <v>0</v>
@@ -18003,27 +18003,27 @@
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11912.jpg</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>11912</v>
+        <v>11957</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CANJICA AMARELA</t>
+          <t>ARROZ VERMELHO 500G</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -18054,10 +18054,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="O229" t="n">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="P229" t="n">
         <v>0</v>
@@ -18071,36 +18071,36 @@
         </is>
       </c>
       <c r="T229" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>100gr</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11912.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.jpg</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>11957</v>
+        <v>11958</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ARROZ VERMELHO 500G</t>
+          <t>ARROZ NEGRO</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -18131,10 +18131,10 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="O230" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="P230" t="n">
         <v>0</v>
@@ -18148,31 +18148,31 @@
         </is>
       </c>
       <c r="T230" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100gr</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11958.jpg</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>11958</v>
+        <v>11959</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ARROZ NEGRO</t>
+          <t>ARROZ INTEGRAL CATETO BRANCO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>49</v>
+        <v>22.5</v>
       </c>
       <c r="O231" t="n">
-        <v>49</v>
+        <v>22.5</v>
       </c>
       <c r="P231" t="n">
         <v>0</v>
@@ -18234,22 +18234,22 @@
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11958.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.png</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>11959</v>
+        <v>11960</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ARROZ INTEGRAL CATETO BRANCO</t>
+          <t>ARROZ INTEGRAL AGULHA MISTO</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -18285,10 +18285,10 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>22.5</v>
+        <v>15.9</v>
       </c>
       <c r="O232" t="n">
-        <v>22.5</v>
+        <v>15.9</v>
       </c>
       <c r="P232" t="n">
         <v>0</v>
@@ -18311,22 +18311,22 @@
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11960.jpg</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>11960</v>
+        <v>11961</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>297</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ARROZ INTEGRAL AGULHA MISTO</t>
+          <t>ARROZ INTEGRAL AGULHA BRANCO</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -18362,10 +18362,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>15.9</v>
+        <v>13.5</v>
       </c>
       <c r="O233" t="n">
-        <v>15.9</v>
+        <v>13.5</v>
       </c>
       <c r="P233" t="n">
         <v>0</v>
@@ -18388,22 +18388,22 @@
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11960.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11961.jpg</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>11961</v>
+        <v>11962</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ARROZ INTEGRAL AGULHA BRANCO</t>
+          <t>ARROZ 7 GRAOS</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -18439,10 +18439,10 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="O234" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="P234" t="n">
         <v>0</v>
@@ -18465,22 +18465,22 @@
       </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11961.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11962.webp</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>11962</v>
+        <v>12002</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ARROZ 7 GRAOS</t>
+          <t>AMARANTO GRAO</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -18516,10 +18516,10 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="O235" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="P235" t="n">
         <v>0</v>
@@ -18542,22 +18542,22 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11962.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12002.webp</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>12002</v>
+        <v>12077</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>AMARANTO GRAO</t>
+          <t>CAFE GRAO A GRANEL</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -18593,10 +18593,10 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="O236" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="P236" t="n">
         <v>0</v>
@@ -18619,22 +18619,22 @@
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12002.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.jpg</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>12077</v>
+        <v>12084</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CAFE GRAO A GRANEL</t>
+          <t>FEIJAO RAJADO</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -18670,10 +18670,10 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>98</v>
+        <v>17.9</v>
       </c>
       <c r="O237" t="n">
-        <v>98</v>
+        <v>17.9</v>
       </c>
       <c r="P237" t="n">
         <v>0</v>
@@ -18696,22 +18696,22 @@
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12084.webp</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>12084</v>
+        <v>12101</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>FEIJAO RAJADO</t>
+          <t>ARROZ VERMELHO GRANEL</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -18747,10 +18747,10 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>17.9</v>
+        <v>10</v>
       </c>
       <c r="O238" t="n">
-        <v>17.9</v>
+        <v>10</v>
       </c>
       <c r="P238" t="n">
         <v>0</v>
@@ -18773,22 +18773,22 @@
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12084.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.jpg</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>12101</v>
+        <v>12102</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>741</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ARROZ VERMELHO GRANEL</t>
+          <t>QUIRELA</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -18824,10 +18824,10 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O239" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P239" t="n">
         <v>0</v>
@@ -18850,22 +18850,22 @@
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.png</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>12102</v>
+        <v>10449</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>QUIRELA</t>
+          <t>GERGELIM TORRADO</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -18897,14 +18897,14 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>GRAOS</t>
+          <t>SEMENTES</t>
         </is>
       </c>
       <c r="N240" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="O240" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="P240" t="n">
         <v>0</v>
@@ -18922,27 +18922,27 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>100gr</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.jpg</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>10449</v>
+        <v>10988</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>GERGELIM TORRADO</t>
+          <t>GIRASSOL S/CASCA TORRADO</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -18978,10 +18978,10 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O241" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="P241" t="n">
         <v>0</v>
@@ -19004,40 +19004,40 @@
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.jpg</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>10988</v>
+        <v>11184</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>GIRASSOL S/CASCA TORRADO</t>
+          <t>SEMENTE DE MELANCIA 25G</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UN</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H242" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I242" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J242" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -19055,10 +19055,10 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="O242" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="P242" t="n">
         <v>0</v>
@@ -19072,49 +19072,49 @@
         </is>
       </c>
       <c r="T242" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.jpg</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>11184</v>
+        <v>11518</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>SEMENTE DE MELANCIA 25G</t>
+          <t>SEMENTE DE ABOBORA S/C TOR S/S</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H243" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I243" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J243" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -19132,10 +19132,10 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="O243" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="P243" t="n">
         <v>0</v>
@@ -19149,31 +19149,31 @@
         </is>
       </c>
       <c r="T243" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11518.jpg</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>11518</v>
+        <v>11519</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>SEMENTE DE ABOBORA S/C TOR S/S</t>
+          <t>SEMENTE DE ABOBORA CRUA S/ CASCA</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -19209,10 +19209,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="O244" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="P244" t="n">
         <v>0</v>
@@ -19235,22 +19235,22 @@
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11518.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.jpg</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>11519</v>
+        <v>11645</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>SEMENTE DE ABOBORA CRUA S/ CASCA</t>
+          <t>LINHACA MARROM SEMENTE</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -19286,10 +19286,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="O245" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="P245" t="n">
         <v>0</v>
@@ -19312,22 +19312,22 @@
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.jpg</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>11645</v>
+        <v>11646</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>LINHACA MARROM SEMENTE</t>
+          <t>LINHACA DOURADA SEMENTE</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -19363,10 +19363,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="O246" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="P246" t="n">
         <v>0</v>
@@ -19389,22 +19389,22 @@
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.jpg</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>11646</v>
+        <v>11698</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>LINHACA DOURADA SEMENTE</t>
+          <t>GIRASSOL S/CASCA</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -19440,10 +19440,10 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="O247" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="P247" t="n">
         <v>0</v>
@@ -19466,22 +19466,22 @@
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11698.webp</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>11698</v>
+        <v>11705</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>GIRASSOL S/CASCA</t>
+          <t>GERGELIM S/ PELE</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -19517,10 +19517,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O248" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P248" t="n">
         <v>0</v>
@@ -19543,22 +19543,22 @@
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11698.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.jpg</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>11705</v>
+        <v>11706</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>GERGELIM S/ PELE</t>
+          <t>GERGELIM PRETO</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -19594,10 +19594,10 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="O249" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="P249" t="n">
         <v>0</v>
@@ -19620,22 +19620,22 @@
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.png</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>11706</v>
+        <v>11707</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>GERGELIM PRETO</t>
+          <t>GERGELIM C/ PELE</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -19671,10 +19671,10 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="O250" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="P250" t="n">
         <v>0</v>
@@ -19697,22 +19697,22 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.jpg</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>11707</v>
+        <v>11865</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>822</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>GERGELIM C/ PELE</t>
+          <t>CHIA PREMIUM</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -19748,10 +19748,10 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O251" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="P251" t="n">
         <v>0</v>
@@ -19774,22 +19774,22 @@
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.webp</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>11865</v>
+        <v>10058</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CHIA PREMIUM</t>
+          <t>PIMENTA BRANCA GRAO</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -19821,14 +19821,14 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>SEMENTES</t>
+          <t>TEMPEROS A GRANEL</t>
         </is>
       </c>
       <c r="N252" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="O252" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="P252" t="n">
         <v>0</v>
@@ -19851,22 +19851,22 @@
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.jpg</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>10058</v>
+        <v>10061</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>PIMENTA BRANCA GRAO</t>
+          <t>CALDO DE PEIXE</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -19902,10 +19902,10 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="O253" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="P253" t="n">
         <v>0</v>
@@ -19928,22 +19928,22 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.png</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>10061</v>
+        <v>10102</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>CALDO DE PEIXE</t>
+          <t>TEMPERO TAILANDES</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -19979,10 +19979,10 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="O254" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="P254" t="n">
         <v>0</v>
@@ -20005,27 +20005,27 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10102.webp</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>10102</v>
+        <v>10171</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>TEMPERO TAILANDES</t>
+          <t>LEMON C/ ERVAS FINAS 500G</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNI</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -20035,10 +20035,10 @@
         <v>10</v>
       </c>
       <c r="I255" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J255" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
@@ -20056,10 +20056,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="O255" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="P255" t="n">
         <v>0</v>
@@ -20073,36 +20073,36 @@
         </is>
       </c>
       <c r="T255" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10102.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.jpg</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>10171</v>
+        <v>10256</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>LEMON C/ ERVAS FINAS 500G</t>
+          <t>OREGANO EM PO 20G</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>UNI</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -20112,10 +20112,10 @@
         <v>10</v>
       </c>
       <c r="I256" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J256" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -20133,10 +20133,10 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O256" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P256" t="n">
         <v>0</v>
@@ -20150,31 +20150,31 @@
         </is>
       </c>
       <c r="T256" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.webp</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>10256</v>
+        <v>10264</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>OREGANO EM PO 20G</t>
+          <t>MANJERICAO EM PO</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="O257" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P257" t="n">
         <v>0</v>
@@ -20236,22 +20236,22 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>10264</v>
+        <v>10306</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>MANJERICAO EM PO</t>
+          <t>CANELA PO PURA PREMIUM</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -20287,10 +20287,10 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="O258" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="P258" t="n">
         <v>0</v>
@@ -20313,22 +20313,22 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.jpg</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>10306</v>
+        <v>10308</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>CANELA PO PURA PREMIUM</t>
+          <t>CHIMICHURRI DEFUMADO</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="O259" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="P259" t="n">
         <v>0</v>
@@ -20390,22 +20390,22 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.jpg</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>10308</v>
+        <v>10550</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>CHIMICHURRI DEFUMADO</t>
+          <t>ORANGE PEPPER</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -20441,10 +20441,10 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="O260" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="P260" t="n">
         <v>0</v>
@@ -20467,22 +20467,22 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>10550</v>
+        <v>10720</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ORANGE PEPPER</t>
+          <t>ALHO ROXO SOLTO</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -20518,10 +20518,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O261" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P261" t="n">
         <v>0</v>
@@ -20544,22 +20544,22 @@
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>10720</v>
+        <v>10887</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ALHO ROXO SOLTO</t>
+          <t>ACAFRAO IMPORTADO</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -20595,10 +20595,10 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O262" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P262" t="n">
         <v>0</v>
@@ -20621,22 +20621,22 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>10887</v>
+        <v>10902</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ACAFRAO IMPORTADO</t>
+          <t>TEMPERO BAIANO SEM PIMENTA</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -20672,10 +20672,10 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="O263" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="P263" t="n">
         <v>0</v>
@@ -20698,22 +20698,22 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>10902</v>
+        <v>10967</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO SEM PIMENTA</t>
+          <t>CREME DE CEBOLA</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -20749,10 +20749,10 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="O264" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="P264" t="n">
         <v>0</v>
@@ -20775,22 +20775,22 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>10967</v>
+        <v>11029</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>CREME DE CEBOLA</t>
+          <t>CEBOLA CRISPY</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -20826,10 +20826,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="O265" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="P265" t="n">
         <v>0</v>
@@ -20852,22 +20852,22 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.webp</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>11029</v>
+        <v>11167</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CEBOLA CRISPY</t>
+          <t>FIT EDU GUEDES</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -20903,10 +20903,10 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="O266" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="P266" t="n">
         <v>0</v>
@@ -20929,22 +20929,22 @@
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11167.jpg</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>11167</v>
+        <v>11168</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>FIT EDU GUEDES</t>
+          <t>TEMPERO MINEIRO</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -20980,10 +20980,10 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="O267" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="P267" t="n">
         <v>0</v>
@@ -21006,22 +21006,22 @@
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11167.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>11168</v>
+        <v>11170</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>TEMPERO MINEIRO</t>
+          <t>FIT COMPLETO</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -21057,10 +21057,10 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O268" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P268" t="n">
         <v>0</v>
@@ -21083,22 +21083,22 @@
       </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>11170</v>
+        <v>11237</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>FIT COMPLETO</t>
+          <t>TEMPERO SIRIO</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -21134,10 +21134,10 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O269" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="P269" t="n">
         <v>0</v>
@@ -21160,40 +21160,40 @@
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.jpg</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>11237</v>
+        <v>11382</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>TEMPERO SIRIO</t>
+          <t>GARAM MASALA 20G</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UN</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H270" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I270" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J270" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -21211,10 +21211,10 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>38</v>
+        <v>2.5</v>
       </c>
       <c r="O270" t="n">
-        <v>38</v>
+        <v>2.5</v>
       </c>
       <c r="P270" t="n">
         <v>0</v>
@@ -21228,49 +21228,49 @@
         </is>
       </c>
       <c r="T270" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.jpg</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>11382</v>
+        <v>11466</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>GARAM MASALA 20G</t>
+          <t>ZIMBRO</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H271" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I271" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J271" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -21288,10 +21288,10 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>2.5</v>
+        <v>229</v>
       </c>
       <c r="O271" t="n">
-        <v>2.5</v>
+        <v>229</v>
       </c>
       <c r="P271" t="n">
         <v>0</v>
@@ -21305,31 +21305,31 @@
         </is>
       </c>
       <c r="T271" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.jpg</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>11466</v>
+        <v>11468</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>971</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>ZIMBRO</t>
+          <t>ZATTAR</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -21365,10 +21365,10 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>229</v>
+        <v>55</v>
       </c>
       <c r="O272" t="n">
-        <v>229</v>
+        <v>55</v>
       </c>
       <c r="P272" t="n">
         <v>0</v>
@@ -21391,22 +21391,22 @@
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.webp</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>11468</v>
+        <v>11473</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ZATTAR</t>
+          <t>VINAGRETE</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -21442,10 +21442,10 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="O273" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="P273" t="n">
         <v>0</v>
@@ -21468,22 +21468,22 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>11473</v>
+        <v>11487</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>VINAGRETE</t>
+          <t>PEGA MARIDO</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -21519,10 +21519,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="O274" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P274" t="n">
         <v>0</v>
@@ -21545,22 +21545,22 @@
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.jpg</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>11487</v>
+        <v>11493</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>PEGA MARIDO</t>
+          <t>TOMILHO</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -21596,10 +21596,10 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="O275" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="P275" t="n">
         <v>0</v>
@@ -21622,22 +21622,22 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.jpg</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>11493</v>
+        <v>11496</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>TOMILHO</t>
+          <t>TEMPERO FEIJAO</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="O276" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="P276" t="n">
         <v>0</v>
@@ -21699,22 +21699,22 @@
       </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>11496</v>
+        <v>11497</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>TEMPERO FEIJAO</t>
+          <t>LEMON COM ERVAS FINAS</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -21750,10 +21750,10 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="O277" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P277" t="n">
         <v>0</v>
@@ -21776,22 +21776,22 @@
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.png</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>11497</v>
+        <v>11499</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>LEMON COM ERVAS FINAS</t>
+          <t>TEMPERO BAIANO PO</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -21827,10 +21827,10 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="O278" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="P278" t="n">
         <v>0</v>
@@ -21853,22 +21853,22 @@
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>11499</v>
+        <v>11500</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO PO</t>
+          <t>TEMPERO BAIANO GRAO</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -21904,10 +21904,10 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="O279" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="P279" t="n">
         <v>0</v>
@@ -21930,22 +21930,22 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>11500</v>
+        <v>11502</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO GRAO</t>
+          <t>TEMPERO ANA MARIA</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -21981,10 +21981,10 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="O280" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="P280" t="n">
         <v>0</v>
@@ -22007,22 +22007,22 @@
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>11502</v>
+        <v>11523</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>TEMPERO ANA MARIA</t>
+          <t>SALSA DESIDRATADA</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="O281" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P281" t="n">
         <v>0</v>
@@ -22084,22 +22084,22 @@
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>11523</v>
+        <v>11563</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>SALSA DESIDRATADA</t>
+          <t>PIMENTA SIRIA PO (JAMAICA)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -22135,10 +22135,10 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="O282" t="n">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="P282" t="n">
         <v>0</v>
@@ -22161,22 +22161,22 @@
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>11563</v>
+        <v>11565</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>PIMENTA SIRIA PO (JAMAICA)</t>
+          <t>PIMENTA SIRIA GRAO (JAMAICA)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -22212,10 +22212,10 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="O283" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="P283" t="n">
         <v>0</v>
@@ -22238,22 +22238,22 @@
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>11565</v>
+        <v>11567</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>PIMENTA SIRIA GRAO (JAMAICA)</t>
+          <t>PIMENTA ROSA</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -22289,10 +22289,10 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="O284" t="n">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="P284" t="n">
         <v>0</v>
@@ -22315,22 +22315,22 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>11567</v>
+        <v>11568</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>PIMENTA ROSA</t>
+          <t>PIMENTA DO REINO PRETA PO</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="O285" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="P285" t="n">
         <v>0</v>
@@ -22392,22 +22392,22 @@
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.jpg</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>11568</v>
+        <v>11569</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO PRETA PO</t>
+          <t>PIMENTA DO REINO  PRETA  GRAO</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -22443,10 +22443,10 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O286" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="P286" t="n">
         <v>0</v>
@@ -22469,22 +22469,22 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>11569</v>
+        <v>11570</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO  PRETA  GRAO</t>
+          <t>PIMENTA DO REINO BRANCA EM PO</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -22520,10 +22520,10 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="O287" t="n">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="P287" t="n">
         <v>0</v>
@@ -22546,22 +22546,22 @@
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.jpg</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>11570</v>
+        <v>11571</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO BRANCA EM PO</t>
+          <t>PIMENTA CHILLI</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -22597,10 +22597,10 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="O288" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="P288" t="n">
         <v>0</v>
@@ -22623,22 +22623,22 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.jpg</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>11571</v>
+        <v>11572</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>PIMENTA CHILLI</t>
+          <t>PIMENTA CALABRESA FLOCOS</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -22674,10 +22674,10 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="O289" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="P289" t="n">
         <v>0</v>
@@ -22700,22 +22700,22 @@
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.webp</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>11572</v>
+        <v>11573</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>607</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>PIMENTA CALABRESA FLOCOS</t>
+          <t>PIMENTA CAYENA</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -22751,10 +22751,10 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="O290" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="P290" t="n">
         <v>0</v>
@@ -22777,22 +22777,22 @@
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.jpg</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>11573</v>
+        <v>11584</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>PIMENTA CAYENA</t>
+          <t>PAPRICA PICANTE</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -22828,10 +22828,10 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="O291" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="P291" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>11584</v>
+        <v>11586</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>PAPRICA PICANTE</t>
+          <t>PAPRICA DOCE</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -22931,22 +22931,22 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>11586</v>
+        <v>11588</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>PAPRICA DOCE</t>
+          <t>PAPRICA DEFUMADA</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -23008,22 +23008,22 @@
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>11588</v>
+        <v>11592</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>PAPRICA DEFUMADA</t>
+          <t>OREGANO</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -23059,10 +23059,10 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O294" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="P294" t="n">
         <v>0</v>
@@ -23085,22 +23085,22 @@
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>11592</v>
+        <v>11602</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>OREGANO</t>
+          <t>NOZ MOSCADA PO</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -23136,10 +23136,10 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="O295" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="P295" t="n">
         <v>0</v>
@@ -23162,22 +23162,22 @@
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>11602</v>
+        <v>11607</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>NOZ MOSCADA PO</t>
+          <t>MOSTARDA PO PURA</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -23213,10 +23213,10 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="O296" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="P296" t="n">
         <v>0</v>
@@ -23239,22 +23239,22 @@
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.png</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>11607</v>
+        <v>11608</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>MOSTARDA PO PURA</t>
+          <t>MOSTARDA GRAO</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -23290,10 +23290,10 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="O297" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -23316,22 +23316,22 @@
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.jpg</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>11608</v>
+        <v>11629</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>MOSTARDA GRAO</t>
+          <t>MANJERONA DESIDRATADO</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -23367,10 +23367,10 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="O298" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="P298" t="n">
         <v>0</v>
@@ -23393,22 +23393,22 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.jpg</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>11629</v>
+        <v>11630</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>MANJERONA DESIDRATADO</t>
+          <t>MANJERICAO DESIDRATADO</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -23444,10 +23444,10 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O299" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P299" t="n">
         <v>0</v>
@@ -23470,22 +23470,22 @@
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.png</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>11630</v>
+        <v>11642</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>MANJERICAO DESIDRATADO</t>
+          <t>LOURO EM PO</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -23521,10 +23521,10 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="O300" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="P300" t="n">
         <v>0</v>
@@ -23547,22 +23547,22 @@
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.png</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>11642</v>
+        <v>11643</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>811</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>LOURO EM PO</t>
+          <t>LOURO EM FOLHA</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -23598,10 +23598,10 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="O301" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="P301" t="n">
         <v>0</v>
@@ -23624,22 +23624,22 @@
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.webp</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>11643</v>
+        <v>11647</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>LOURO EM FOLHA</t>
+          <t>LEMON PEPPER 0% SODIO</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -23675,10 +23675,10 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O302" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P302" t="n">
         <v>0</v>
@@ -23701,22 +23701,22 @@
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>11647</v>
+        <v>11655</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>LEMON PEPPER 0% SODIO</t>
+          <t>LEMON PEPPER</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -23752,10 +23752,10 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="O303" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="P303" t="n">
         <v>0</v>
@@ -23778,22 +23778,22 @@
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.webp</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>11655</v>
+        <v>11717</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>LEMON PEPPER</t>
+          <t>FUMACA EM PO</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -23829,10 +23829,10 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="O304" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P304" t="n">
         <v>0</v>
@@ -23855,22 +23855,22 @@
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>11717</v>
+        <v>11806</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>FUMACA EM PO</t>
+          <t>ERVAS FINAS</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -23906,10 +23906,10 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="O305" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="P305" t="n">
         <v>0</v>
@@ -23932,22 +23932,22 @@
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>11806</v>
+        <v>11818</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>ERVAS FINAS</t>
+          <t>ENDRO</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -23983,10 +23983,10 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="O306" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -24009,22 +24009,22 @@
       </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>11818</v>
+        <v>11822</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>ENDRO</t>
+          <t>EDU GUEDES</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -24060,10 +24060,10 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="O307" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -24086,22 +24086,22 @@
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>11822</v>
+        <v>11830</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>EDU GUEDES</t>
+          <t>CURRY</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -24137,10 +24137,10 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O308" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P308" t="n">
         <v>0</v>
@@ -24163,22 +24163,22 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.jpg</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>11830</v>
+        <v>11833</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>CURRY</t>
+          <t>CRAVO MOIDO</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -24214,10 +24214,10 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="O309" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="P309" t="n">
         <v>0</v>
@@ -24240,22 +24240,22 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.jpg</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>11833</v>
+        <v>11834</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>CRAVO MOIDO</t>
+          <t>CRAVO GRAO</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -24291,10 +24291,10 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="O310" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="P310" t="n">
         <v>0</v>
@@ -24317,22 +24317,22 @@
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.png</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>11834</v>
+        <v>11838</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>CRAVO GRAO</t>
+          <t>COMINHO PO PURO</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -24368,10 +24368,10 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="O311" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="P311" t="n">
         <v>0</v>
@@ -24394,22 +24394,22 @@
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.png</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>11838</v>
+        <v>11839</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>COMINHO PO PURO</t>
+          <t>COMINHO GRAO 99%</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -24445,10 +24445,10 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="O312" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="P312" t="n">
         <v>0</v>
@@ -24471,22 +24471,22 @@
       </c>
       <c r="V312" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11839.png</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>11839</v>
+        <v>11840</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>571</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>COMINHO GRAO 99%</t>
+          <t>COLORAU</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="O313" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="P313" t="n">
         <v>0</v>
@@ -24548,22 +24548,22 @@
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11839.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>11840</v>
+        <v>11843</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>COLORAU</t>
+          <t>COENTRO GRAO</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -24599,10 +24599,10 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="O314" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="P314" t="n">
         <v>0</v>
@@ -24625,22 +24625,22 @@
       </c>
       <c r="V314" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.jpg</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>11843</v>
+        <v>11844</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>COENTRO GRAO</t>
+          <t>COENTRO FOLHAS</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -24676,10 +24676,10 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>17.5</v>
+        <v>64</v>
       </c>
       <c r="O315" t="n">
-        <v>17.5</v>
+        <v>64</v>
       </c>
       <c r="P315" t="n">
         <v>0</v>
@@ -24702,22 +24702,22 @@
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.jpg</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>11844</v>
+        <v>11845</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>COENTRO FOLHAS</t>
+          <t>COENTRO EM PO</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -24753,10 +24753,10 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="O316" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="P316" t="n">
         <v>0</v>
@@ -24779,22 +24779,22 @@
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.png</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>11845</v>
+        <v>11863</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>404</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>COENTRO EM PO</t>
+          <t>CHIMICHURRI SEM PIMENTA</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -24830,10 +24830,10 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="O317" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="P317" t="n">
         <v>0</v>
@@ -24856,22 +24856,22 @@
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>11863</v>
+        <v>11864</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CHIMICHURRI SEM PIMENTA</t>
+          <t>CHIMICHURRI COM PIMENTA</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -24933,22 +24933,22 @@
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11864.webp</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>11864</v>
+        <v>11874</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>CHIMICHURRI COM PIMENTA</t>
+          <t>CEBOLINHA DESIDRATADA</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -24984,10 +24984,10 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O319" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P319" t="n">
         <v>0</v>
@@ -25010,22 +25010,22 @@
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11864.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11874.webp</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>11874</v>
+        <v>11875</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CEBOLINHA DESIDRATADA</t>
+          <t>CEBOLA, ALHO E SALSA</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -25061,10 +25061,10 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O320" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P320" t="n">
         <v>0</v>
@@ -25087,22 +25087,22 @@
       </c>
       <c r="V320" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11874.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>11875</v>
+        <v>11877</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CEBOLA, ALHO E SALSA</t>
+          <t>CEBOLA FLOCOS</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -25138,10 +25138,10 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O321" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P321" t="n">
         <v>0</v>
@@ -25164,22 +25164,22 @@
       </c>
       <c r="V321" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>11877</v>
+        <v>11879</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>982</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CEBOLA FLOCOS</t>
+          <t>CEBOLA EM PO</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -25215,10 +25215,10 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="O322" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P322" t="n">
         <v>0</v>
@@ -25241,22 +25241,22 @@
       </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11879.jpg</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>11879</v>
+        <v>11909</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>CEBOLA EM PO</t>
+          <t>CARDAMOMO SEMENTES</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -25292,10 +25292,10 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>45</v>
+        <v>680</v>
       </c>
       <c r="O323" t="n">
-        <v>45</v>
+        <v>680</v>
       </c>
       <c r="P323" t="n">
         <v>0</v>
@@ -25318,22 +25318,22 @@
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11879.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.jpg</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>11909</v>
+        <v>11910</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CARDAMOMO SEMENTES</t>
+          <t>CARDAMOMO PO</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -25395,22 +25395,22 @@
       </c>
       <c r="V324" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>11910</v>
+        <v>11913</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>CARDAMOMO PO</t>
+          <t>CANELA EM PO PURA</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -25446,10 +25446,10 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>680</v>
+        <v>35</v>
       </c>
       <c r="O325" t="n">
-        <v>680</v>
+        <v>35</v>
       </c>
       <c r="P325" t="n">
         <v>0</v>
@@ -25472,22 +25472,22 @@
       </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.jpg</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>11913</v>
+        <v>11931</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>CANELA EM PO PURA</t>
+          <t>BICARBONATO DE SODIO</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -25523,10 +25523,10 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>35</v>
+        <v>10.5</v>
       </c>
       <c r="O326" t="n">
-        <v>35</v>
+        <v>10.5</v>
       </c>
       <c r="P326" t="n">
         <v>0</v>
@@ -25549,22 +25549,22 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.webp</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>11931</v>
+        <v>12004</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>BICARBONATO DE SODIO</t>
+          <t>ALHO ROXO</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -25600,10 +25600,10 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>10.5</v>
+        <v>49</v>
       </c>
       <c r="O327" t="n">
-        <v>10.5</v>
+        <v>49</v>
       </c>
       <c r="P327" t="n">
         <v>0</v>
@@ -25626,22 +25626,22 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>12004</v>
+        <v>12006</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>ALHO ROXO</t>
+          <t>ALHO LAMINADO DESIDRATADO</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -25677,10 +25677,10 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="O328" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="P328" t="n">
         <v>0</v>
@@ -25703,22 +25703,22 @@
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.webp</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>12006</v>
+        <v>12008</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ALHO LAMINADO DESIDRATADO</t>
+          <t>ALHO GRANULADO</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -25754,10 +25754,10 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="O329" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="P329" t="n">
         <v>0</v>
@@ -25780,22 +25780,22 @@
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.webp</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>12008</v>
+        <v>12010</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>422</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>ALHO GRANULADO</t>
+          <t>ALHO FRITO</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -25831,10 +25831,10 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O330" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P330" t="n">
         <v>0</v>
@@ -25857,22 +25857,22 @@
       </c>
       <c r="V330" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>12010</v>
+        <v>12011</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>ALHO FRITO</t>
+          <t>ALHO EM PO 100% PURO</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -25908,10 +25908,10 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O331" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P331" t="n">
         <v>0</v>
@@ -25934,22 +25934,22 @@
       </c>
       <c r="V331" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>12011</v>
+        <v>12019</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>ALHO EM PO 100% PURO</t>
+          <t>ALECRIM</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -26011,22 +26011,22 @@
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>12019</v>
+        <v>12023</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>ALECRIM</t>
+          <t>AIPO</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -26062,10 +26062,10 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O333" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P333" t="n">
         <v>0</v>
@@ -26088,22 +26088,22 @@
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12023.jpg</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>12023</v>
+        <v>12031</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>AIPO</t>
+          <t>ACAFRAO NACIONAL</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -26139,10 +26139,10 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="O334" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="P334" t="n">
         <v>0</v>
@@ -26165,22 +26165,22 @@
       </c>
       <c r="V334" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12023.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>12031</v>
+        <v>12080</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>ACAFRAO NACIONAL</t>
+          <t>CALDO DE GALINHA</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -26216,10 +26216,10 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="O335" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="P335" t="n">
         <v>0</v>
@@ -26242,22 +26242,22 @@
       </c>
       <c r="V335" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.jpg</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>12080</v>
+        <v>12098</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CALDO DE GALINHA</t>
+          <t>CALDO DE LEGUMES</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -26293,10 +26293,10 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O336" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P336" t="n">
         <v>0</v>
@@ -26319,22 +26319,22 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>12098</v>
+        <v>12105</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>CALDO DE LEGUMES</t>
+          <t>EDU GUEDES</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -26370,10 +26370,10 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O337" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P337" t="n">
         <v>0</v>
@@ -26396,22 +26396,22 @@
       </c>
       <c r="V337" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>12105</v>
+        <v>12106</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>EDU GUEDES</t>
+          <t>ANA MARIA</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -26447,10 +26447,10 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="O338" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="P338" t="n">
         <v>0</v>
@@ -26473,22 +26473,22 @@
       </c>
       <c r="V338" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>12106</v>
+        <v>12107</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>ANA MARIA</t>
+          <t>CEBOLA, ALHO E SALSA</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -26524,10 +26524,10 @@
         </is>
       </c>
       <c r="N339" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="O339" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="P339" t="n">
         <v>0</v>
@@ -26550,22 +26550,22 @@
       </c>
       <c r="V339" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>12107</v>
+        <v>12108</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>CEBOLA, ALHO E SALSA</t>
+          <t>CHIMICHURRI SEM PIMENTA</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -26601,10 +26601,10 @@
         </is>
       </c>
       <c r="N340" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="O340" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P340" t="n">
         <v>0</v>
@@ -26627,22 +26627,22 @@
       </c>
       <c r="V340" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>12108</v>
+        <v>12109</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>CHIMICHURRI SEM PIMENTA</t>
+          <t>CHIMICHURRI COM PIMENTA</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -26704,22 +26704,22 @@
       </c>
       <c r="V341" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12109.webp</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>12109</v>
+        <v>12096</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>CHIMICHURRI COM PIMENTA</t>
+          <t>PEGA MARIDO FIT</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -26755,10 +26755,10 @@
         </is>
       </c>
       <c r="N342" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="O342" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P342" t="n">
         <v>0</v>
@@ -26781,22 +26781,22 @@
       </c>
       <c r="V342" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12109.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.jpg</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>12096</v>
+        <v>12097</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>PEGA MARIDO FIT</t>
+          <t>EDU GUEDES FIT</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -26832,10 +26832,10 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="O343" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="P343" t="n">
         <v>0</v>
@@ -26858,22 +26858,22 @@
       </c>
       <c r="V343" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12097.jpg</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>12097</v>
+        <v>12119</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>EDU GUEDES FIT</t>
+          <t>CEBOLA GRANULADA</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -26909,10 +26909,10 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O344" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P344" t="n">
         <v>0</v>
@@ -26935,22 +26935,22 @@
       </c>
       <c r="V344" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12097.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.jpg</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>12119</v>
+        <v>12115</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>CEBOLA GRANULADA</t>
+          <t>LEMON PEPPER C/ GLUTAMATO</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -26986,10 +26986,10 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O345" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P345" t="n">
         <v>0</v>
@@ -27012,22 +27012,22 @@
       </c>
       <c r="V345" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.png</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>12115</v>
+        <v>12145</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>LEMON PEPPER C/ GLUTAMATO</t>
+          <t>CHIMICHURRI FIT</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -27063,10 +27063,10 @@
         </is>
       </c>
       <c r="N346" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O346" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P346" t="n">
         <v>0</v>
@@ -27089,22 +27089,22 @@
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.webp</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>12145</v>
+        <v>12146</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>CHIMICHURRI FIT</t>
+          <t>CHIMICHURRI C/ PIMENTA FIT</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -27166,22 +27166,22 @@
       </c>
       <c r="V347" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.webp</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>12146</v>
+        <v>12147</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>716</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>CHIMICHURRI C/ PIMENTA FIT</t>
+          <t>LEMON PEPPER FIT</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -27217,10 +27217,10 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="O348" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P348" t="n">
         <v>0</v>
@@ -27243,22 +27243,22 @@
       </c>
       <c r="V348" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.jpg</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>12147</v>
+        <v>12148</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>LEMON PEPPER FIT</t>
+          <t>TEMPERO ANA MARIA FIT</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -27294,10 +27294,10 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="O349" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="P349" t="n">
         <v>0</v>
@@ -27320,37 +27320,37 @@
       </c>
       <c r="V349" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>12148</v>
+        <v>12160</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>TEMPERO ANA MARIA FIT</t>
+          <t>MOSTARDA GRAO MARROM 100G</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G350" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H350" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I350" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J350" t="n">
         <v>100</v>
@@ -27371,10 +27371,10 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="O350" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="P350" t="n">
         <v>0</v>
@@ -27388,46 +27388,46 @@
         </is>
       </c>
       <c r="T350" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U350" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V350" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>12160</v>
+        <v>12161</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>MOSTARDA GRAO MARROM 100G</t>
+          <t>NOZ MOSCADA PO CONDIMENTADA</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H351" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I351" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J351" t="n">
         <v>100</v>
@@ -27448,10 +27448,10 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="O351" t="n">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="P351" t="n">
         <v>0</v>
@@ -27465,31 +27465,31 @@
         </is>
       </c>
       <c r="T351" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U351" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V351" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>12161</v>
+        <v>12164</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>NOZ MOSCADA PO CONDIMENTADA</t>
+          <t>PIMENTA JAMAICA (SIRIA PO)</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -27525,10 +27525,10 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="O352" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="P352" t="n">
         <v>0</v>
@@ -27550,83 +27550,6 @@
         </is>
       </c>
       <c r="V352" t="inlineStr">
-        <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>12164</v>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>PIMENTA JAMAICA (SIRIA PO)</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="G353" t="n">
-        <v>10</v>
-      </c>
-      <c r="H353" t="n">
-        <v>10</v>
-      </c>
-      <c r="I353" t="n">
-        <v>5</v>
-      </c>
-      <c r="J353" t="n">
-        <v>100</v>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M353" t="inlineStr">
-        <is>
-          <t>TEMPEROS A GRANEL</t>
-        </is>
-      </c>
-      <c r="N353" t="n">
-        <v>85</v>
-      </c>
-      <c r="O353" t="n">
-        <v>85</v>
-      </c>
-      <c r="P353" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
-      <c r="S353" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="T353" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U353" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="V353" t="inlineStr">
         <is>
           <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.jpg</t>
         </is>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -6068,7 +6068,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12176.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/apicultura/12176.jpg</t>
         </is>
       </c>
     </row>
@@ -23778,7 +23778,7 @@
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.jpg</t>
         </is>
       </c>
     </row>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF351"/>
+  <dimension ref="A1:AF349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11763.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11763.jpg</t>
         </is>
       </c>
     </row>
@@ -19934,21 +19934,21 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>10171</v>
+        <v>10256</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>LEMON C/ ERVAS FINAS 500G</t>
+          <t>OREGANO EM PO 20G</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>UNI</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -19958,10 +19958,10 @@
         <v>10</v>
       </c>
       <c r="I254" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J254" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -19979,10 +19979,10 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O254" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P254" t="n">
         <v>0</v>
@@ -19996,31 +19996,31 @@
         </is>
       </c>
       <c r="T254" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10171.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.webp</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>10256</v>
+        <v>10264</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>OREGANO EM PO 20G</t>
+          <t>MANJERICAO EM PO</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -20056,10 +20056,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="O255" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P255" t="n">
         <v>0</v>
@@ -20082,22 +20082,22 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>10264</v>
+        <v>10306</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>MANJERICAO EM PO</t>
+          <t>CANELA PO PURA PREMIUM</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -20133,10 +20133,10 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="O256" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="P256" t="n">
         <v>0</v>
@@ -20159,22 +20159,22 @@
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.jpg</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>10306</v>
+        <v>10308</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>CANELA PO PURA PREMIUM</t>
+          <t>CHIMICHURRI DEFUMADO</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="O257" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="P257" t="n">
         <v>0</v>
@@ -20236,22 +20236,22 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.jpg</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>10308</v>
+        <v>10550</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>CHIMICHURRI DEFUMADO</t>
+          <t>ORANGE PEPPER</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -20287,10 +20287,10 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="O258" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="P258" t="n">
         <v>0</v>
@@ -20313,22 +20313,22 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>10550</v>
+        <v>10720</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ORANGE PEPPER</t>
+          <t>ALHO ROXO SOLTO</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O259" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P259" t="n">
         <v>0</v>
@@ -20390,22 +20390,22 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>10720</v>
+        <v>10887</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ALHO ROXO SOLTO</t>
+          <t>ACAFRAO IMPORTADO</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -20441,10 +20441,10 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O260" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P260" t="n">
         <v>0</v>
@@ -20467,22 +20467,22 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>10887</v>
+        <v>10902</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ACAFRAO IMPORTADO</t>
+          <t>TEMPERO BAIANO SEM PIMENTA</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -20518,10 +20518,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="O261" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="P261" t="n">
         <v>0</v>
@@ -20544,22 +20544,22 @@
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>10902</v>
+        <v>10967</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO SEM PIMENTA</t>
+          <t>CREME DE CEBOLA</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -20595,10 +20595,10 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="O262" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="P262" t="n">
         <v>0</v>
@@ -20621,22 +20621,22 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>10967</v>
+        <v>11029</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>CREME DE CEBOLA</t>
+          <t>CEBOLA CRISPY</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -20672,10 +20672,10 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="O263" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="P263" t="n">
         <v>0</v>
@@ -20698,22 +20698,22 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.webp</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>11029</v>
+        <v>11167</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>CEBOLA CRISPY</t>
+          <t>FIT EDU GUEDES</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -20749,10 +20749,10 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="O264" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="P264" t="n">
         <v>0</v>
@@ -20775,22 +20775,22 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11167.jpg</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>11167</v>
+        <v>11168</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>FIT EDU GUEDES</t>
+          <t>TEMPERO MINEIRO</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -20826,10 +20826,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="O265" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="P265" t="n">
         <v>0</v>
@@ -20852,22 +20852,22 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11167.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>11168</v>
+        <v>11170</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>TEMPERO MINEIRO</t>
+          <t>FIT COMPLETO</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -20903,10 +20903,10 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O266" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P266" t="n">
         <v>0</v>
@@ -20929,22 +20929,22 @@
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>11170</v>
+        <v>11237</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>FIT COMPLETO</t>
+          <t>TEMPERO SIRIO</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -20980,10 +20980,10 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O267" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="P267" t="n">
         <v>0</v>
@@ -21006,22 +21006,22 @@
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.jpg</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>11237</v>
+        <v>11466</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>TEMPERO SIRIO</t>
+          <t>ZIMBRO</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -21057,10 +21057,10 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>38</v>
+        <v>229</v>
       </c>
       <c r="O268" t="n">
-        <v>38</v>
+        <v>229</v>
       </c>
       <c r="P268" t="n">
         <v>0</v>
@@ -21083,40 +21083,40 @@
       </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.jpg</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>11382</v>
+        <v>11468</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>971</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>GARAM MASALA 20G</t>
+          <t>ZATTAR</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H269" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I269" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J269" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -21134,10 +21134,10 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>2.5</v>
+        <v>55</v>
       </c>
       <c r="O269" t="n">
-        <v>2.5</v>
+        <v>55</v>
       </c>
       <c r="P269" t="n">
         <v>0</v>
@@ -21151,31 +21151,31 @@
         </is>
       </c>
       <c r="T269" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11382.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.webp</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>11466</v>
+        <v>11473</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ZIMBRO</t>
+          <t>VINAGRETE</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -21211,10 +21211,10 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>229</v>
+        <v>68</v>
       </c>
       <c r="O270" t="n">
-        <v>229</v>
+        <v>68</v>
       </c>
       <c r="P270" t="n">
         <v>0</v>
@@ -21237,22 +21237,22 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>11468</v>
+        <v>11487</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ZATTAR</t>
+          <t>PEGA MARIDO</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -21288,10 +21288,10 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O271" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="P271" t="n">
         <v>0</v>
@@ -21314,22 +21314,22 @@
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.jpg</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>11473</v>
+        <v>11493</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>VINAGRETE</t>
+          <t>TOMILHO</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -21365,10 +21365,10 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="O272" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="P272" t="n">
         <v>0</v>
@@ -21391,22 +21391,22 @@
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.jpg</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>11487</v>
+        <v>11496</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>PEGA MARIDO</t>
+          <t>TEMPERO FEIJAO</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -21442,10 +21442,10 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="O273" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="P273" t="n">
         <v>0</v>
@@ -21468,22 +21468,22 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>11493</v>
+        <v>11497</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>TOMILHO</t>
+          <t>LEMON COM ERVAS FINAS</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -21519,10 +21519,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="O274" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="P274" t="n">
         <v>0</v>
@@ -21545,22 +21545,22 @@
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.png</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>11496</v>
+        <v>11499</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>TEMPERO FEIJAO</t>
+          <t>TEMPERO BAIANO PO</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -21596,10 +21596,10 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O275" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="P275" t="n">
         <v>0</v>
@@ -21622,22 +21622,22 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>11497</v>
+        <v>11500</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>LEMON COM ERVAS FINAS</t>
+          <t>TEMPERO BAIANO GRAO</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="O276" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="P276" t="n">
         <v>0</v>
@@ -21699,22 +21699,22 @@
       </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>11499</v>
+        <v>11502</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO PO</t>
+          <t>TEMPERO ANA MARIA</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -21750,10 +21750,10 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="O277" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="P277" t="n">
         <v>0</v>
@@ -21776,22 +21776,22 @@
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>11500</v>
+        <v>11523</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO GRAO</t>
+          <t>SALSA DESIDRATADA</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -21827,10 +21827,10 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="O278" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="P278" t="n">
         <v>0</v>
@@ -21853,22 +21853,22 @@
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>11502</v>
+        <v>11563</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>TEMPERO ANA MARIA</t>
+          <t>PIMENTA SIRIA PO (JAMAICA)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -21904,10 +21904,10 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="O279" t="n">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="P279" t="n">
         <v>0</v>
@@ -21930,22 +21930,22 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>11523</v>
+        <v>11565</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>SALSA DESIDRATADA</t>
+          <t>PIMENTA SIRIA GRAO (JAMAICA)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -21981,10 +21981,10 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="O280" t="n">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="P280" t="n">
         <v>0</v>
@@ -22007,22 +22007,22 @@
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>11563</v>
+        <v>11567</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>PIMENTA SIRIA PO (JAMAICA)</t>
+          <t>PIMENTA ROSA</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="O281" t="n">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="P281" t="n">
         <v>0</v>
@@ -22084,22 +22084,22 @@
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>11565</v>
+        <v>11568</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>PIMENTA SIRIA GRAO (JAMAICA)</t>
+          <t>PIMENTA DO REINO PRETA PO</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -22135,10 +22135,10 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>220</v>
+        <v>68</v>
       </c>
       <c r="O282" t="n">
-        <v>220</v>
+        <v>68</v>
       </c>
       <c r="P282" t="n">
         <v>0</v>
@@ -22161,22 +22161,22 @@
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.jpg</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>11567</v>
+        <v>11569</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>PIMENTA ROSA</t>
+          <t>PIMENTA DO REINO  PRETA  GRAO</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -22212,10 +22212,10 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="O283" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="P283" t="n">
         <v>0</v>
@@ -22238,22 +22238,22 @@
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>11568</v>
+        <v>11570</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO PRETA PO</t>
+          <t>PIMENTA DO REINO BRANCA EM PO</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -22289,10 +22289,10 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>68</v>
+        <v>225</v>
       </c>
       <c r="O284" t="n">
-        <v>68</v>
+        <v>225</v>
       </c>
       <c r="P284" t="n">
         <v>0</v>
@@ -22315,22 +22315,22 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.jpg</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>11569</v>
+        <v>11571</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO  PRETA  GRAO</t>
+          <t>PIMENTA CHILLI</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="O285" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="P285" t="n">
         <v>0</v>
@@ -22392,22 +22392,22 @@
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.png</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>11570</v>
+        <v>11572</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO BRANCA EM PO</t>
+          <t>PIMENTA CALABRESA FLOCOS</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -22443,10 +22443,10 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="O286" t="n">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="P286" t="n">
         <v>0</v>
@@ -22469,22 +22469,22 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.webp</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>11571</v>
+        <v>11573</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>607</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>PIMENTA CHILLI</t>
+          <t>PIMENTA CAYENA</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -22520,10 +22520,10 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="O287" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="P287" t="n">
         <v>0</v>
@@ -22546,22 +22546,22 @@
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.jpg</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>11572</v>
+        <v>11584</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>PIMENTA CALABRESA FLOCOS</t>
+          <t>PAPRICA PICANTE</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -22597,10 +22597,10 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="O288" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P288" t="n">
         <v>0</v>
@@ -22623,22 +22623,22 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>11573</v>
+        <v>11586</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>PIMENTA CAYENA</t>
+          <t>PAPRICA DOCE</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -22674,10 +22674,10 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="O289" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="P289" t="n">
         <v>0</v>
@@ -22700,22 +22700,22 @@
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>11584</v>
+        <v>11588</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>PAPRICA PICANTE</t>
+          <t>PAPRICA DEFUMADA</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -22777,22 +22777,22 @@
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>11586</v>
+        <v>11592</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>PAPRICA DOCE</t>
+          <t>OREGANO</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -22828,10 +22828,10 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O291" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="P291" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>11588</v>
+        <v>11602</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>PAPRICA DEFUMADA</t>
+          <t>NOZ MOSCADA PO</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -22905,10 +22905,10 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="O292" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="P292" t="n">
         <v>0</v>
@@ -22931,22 +22931,22 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>11592</v>
+        <v>11607</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>OREGANO</t>
+          <t>MOSTARDA PO PURA</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -22982,10 +22982,10 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="O293" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="P293" t="n">
         <v>0</v>
@@ -23008,22 +23008,22 @@
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.png</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>11602</v>
+        <v>11608</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>NOZ MOSCADA PO</t>
+          <t>MOSTARDA GRAO</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -23059,10 +23059,10 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="O294" t="n">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="P294" t="n">
         <v>0</v>
@@ -23085,22 +23085,22 @@
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.jpg</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>11607</v>
+        <v>11629</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>MOSTARDA PO PURA</t>
+          <t>MANJERONA DESIDRATADO</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -23136,10 +23136,10 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="O295" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="P295" t="n">
         <v>0</v>
@@ -23162,22 +23162,22 @@
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.jpg</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>11608</v>
+        <v>11630</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>MOSTARDA GRAO</t>
+          <t>MANJERICAO DESIDRATADO</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -23213,10 +23213,10 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="O296" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="P296" t="n">
         <v>0</v>
@@ -23239,22 +23239,22 @@
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.png</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>11629</v>
+        <v>11642</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>MANJERONA DESIDRATADO</t>
+          <t>LOURO EM PO</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -23290,10 +23290,10 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="O297" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -23316,22 +23316,22 @@
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.png</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>11630</v>
+        <v>11643</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>811</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>MANJERICAO DESIDRATADO</t>
+          <t>LOURO EM FOLHA</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -23367,10 +23367,10 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="O298" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="P298" t="n">
         <v>0</v>
@@ -23393,22 +23393,22 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.webp</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>11642</v>
+        <v>11647</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>LOURO EM PO</t>
+          <t>LEMON PEPPER 0% SODIO</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -23444,10 +23444,10 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="O299" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="P299" t="n">
         <v>0</v>
@@ -23470,22 +23470,22 @@
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>11643</v>
+        <v>11655</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>LOURO EM FOLHA</t>
+          <t>LEMON PEPPER</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -23521,10 +23521,10 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="O300" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="P300" t="n">
         <v>0</v>
@@ -23547,22 +23547,22 @@
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.jpg</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>11647</v>
+        <v>11717</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>LEMON PEPPER 0% SODIO</t>
+          <t>FUMACA EM PO</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -23598,10 +23598,10 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="O301" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P301" t="n">
         <v>0</v>
@@ -23624,22 +23624,22 @@
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>11655</v>
+        <v>11806</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>LEMON PEPPER</t>
+          <t>ERVAS FINAS</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -23675,10 +23675,10 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="O302" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="P302" t="n">
         <v>0</v>
@@ -23701,22 +23701,22 @@
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>11717</v>
+        <v>11818</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>FUMACA EM PO</t>
+          <t>ENDRO</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -23752,10 +23752,10 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="O303" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="P303" t="n">
         <v>0</v>
@@ -23778,22 +23778,22 @@
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>11806</v>
+        <v>11822</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ERVAS FINAS</t>
+          <t>EDU GUEDES</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -23829,10 +23829,10 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="O304" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="P304" t="n">
         <v>0</v>
@@ -23855,22 +23855,22 @@
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>11818</v>
+        <v>11830</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>ENDRO</t>
+          <t>CURRY</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -23906,10 +23906,10 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="O305" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="P305" t="n">
         <v>0</v>
@@ -23932,22 +23932,22 @@
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.jpg</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>11822</v>
+        <v>11833</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>EDU GUEDES</t>
+          <t>CRAVO MOIDO</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -23983,10 +23983,10 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O306" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -24009,22 +24009,22 @@
       </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.jpg</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>11830</v>
+        <v>11834</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>CURRY</t>
+          <t>CRAVO GRAO</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -24060,10 +24060,10 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="O307" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -24086,22 +24086,22 @@
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.jpg</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>11833</v>
+        <v>11838</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>CRAVO MOIDO</t>
+          <t>COMINHO PO PURO</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -24137,10 +24137,10 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="O308" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="P308" t="n">
         <v>0</v>
@@ -24163,22 +24163,22 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.png</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>11834</v>
+        <v>11839</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>CRAVO GRAO</t>
+          <t>COMINHO GRAO 99%</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -24214,10 +24214,10 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="O309" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="P309" t="n">
         <v>0</v>
@@ -24240,22 +24240,22 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11839.png</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>11838</v>
+        <v>11840</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>571</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>COMINHO PO PURO</t>
+          <t>COLORAU</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -24291,10 +24291,10 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="O310" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="P310" t="n">
         <v>0</v>
@@ -24317,22 +24317,22 @@
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>11839</v>
+        <v>11843</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>COMINHO GRAO 99%</t>
+          <t>COENTRO GRAO</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -24368,10 +24368,10 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>48</v>
+        <v>17.5</v>
       </c>
       <c r="O311" t="n">
-        <v>48</v>
+        <v>17.5</v>
       </c>
       <c r="P311" t="n">
         <v>0</v>
@@ -24394,22 +24394,22 @@
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11839.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.jpg</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>11840</v>
+        <v>11844</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>COLORAU</t>
+          <t>COENTRO FOLHAS</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -24445,10 +24445,10 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="O312" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="P312" t="n">
         <v>0</v>
@@ -24471,22 +24471,22 @@
       </c>
       <c r="V312" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.webp</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>11843</v>
+        <v>11845</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>COENTRO GRAO</t>
+          <t>COENTRO EM PO</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="O313" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="P313" t="n">
         <v>0</v>
@@ -24548,22 +24548,22 @@
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.png</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>11844</v>
+        <v>11863</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>404</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>COENTRO FOLHAS</t>
+          <t>CHIMICHURRI SEM PIMENTA</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -24599,10 +24599,10 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="O314" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="P314" t="n">
         <v>0</v>
@@ -24625,22 +24625,22 @@
       </c>
       <c r="V314" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>11845</v>
+        <v>11864</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>COENTRO EM PO</t>
+          <t>CHIMICHURRI COM PIMENTA</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -24676,10 +24676,10 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="O315" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="P315" t="n">
         <v>0</v>
@@ -24702,22 +24702,22 @@
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11864.webp</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>11863</v>
+        <v>11874</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>CHIMICHURRI SEM PIMENTA</t>
+          <t>CEBOLINHA DESIDRATADA</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -24753,10 +24753,10 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O316" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P316" t="n">
         <v>0</v>
@@ -24779,22 +24779,22 @@
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11874.webp</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>11864</v>
+        <v>11875</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CHIMICHURRI COM PIMENTA</t>
+          <t>CEBOLA, ALHO E SALSA</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -24830,10 +24830,10 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="O317" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P317" t="n">
         <v>0</v>
@@ -24856,22 +24856,22 @@
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11864.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>11874</v>
+        <v>11877</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CEBOLINHA DESIDRATADA</t>
+          <t>CEBOLA FLOCOS</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -24907,10 +24907,10 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="O318" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="P318" t="n">
         <v>0</v>
@@ -24933,22 +24933,22 @@
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11874.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>11875</v>
+        <v>11879</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>982</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>CEBOLA, ALHO E SALSA</t>
+          <t>CEBOLA EM PO</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -24984,10 +24984,10 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="O319" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="P319" t="n">
         <v>0</v>
@@ -25010,22 +25010,22 @@
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11879.jpg</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>11877</v>
+        <v>11909</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CEBOLA FLOCOS</t>
+          <t>CARDAMOMO SEMENTES</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -25061,10 +25061,10 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>53</v>
+        <v>680</v>
       </c>
       <c r="O320" t="n">
-        <v>53</v>
+        <v>680</v>
       </c>
       <c r="P320" t="n">
         <v>0</v>
@@ -25087,22 +25087,22 @@
       </c>
       <c r="V320" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.jpg</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>11879</v>
+        <v>11910</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CEBOLA EM PO</t>
+          <t>CARDAMOMO PO</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -25138,10 +25138,10 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>45</v>
+        <v>680</v>
       </c>
       <c r="O321" t="n">
-        <v>45</v>
+        <v>680</v>
       </c>
       <c r="P321" t="n">
         <v>0</v>
@@ -25164,22 +25164,22 @@
       </c>
       <c r="V321" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11879.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>11909</v>
+        <v>11913</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CARDAMOMO SEMENTES</t>
+          <t>CANELA EM PO PURA</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -25215,10 +25215,10 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>680</v>
+        <v>35</v>
       </c>
       <c r="O322" t="n">
-        <v>680</v>
+        <v>35</v>
       </c>
       <c r="P322" t="n">
         <v>0</v>
@@ -25241,22 +25241,22 @@
       </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.jpg</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>11910</v>
+        <v>11931</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>CARDAMOMO PO</t>
+          <t>BICARBONATO DE SODIO</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -25292,10 +25292,10 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>680</v>
+        <v>10.5</v>
       </c>
       <c r="O323" t="n">
-        <v>680</v>
+        <v>10.5</v>
       </c>
       <c r="P323" t="n">
         <v>0</v>
@@ -25318,22 +25318,22 @@
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.webp</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>11913</v>
+        <v>12004</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CANELA EM PO PURA</t>
+          <t>ALHO ROXO</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -25369,10 +25369,10 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="O324" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="P324" t="n">
         <v>0</v>
@@ -25395,22 +25395,22 @@
       </c>
       <c r="V324" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>11931</v>
+        <v>12006</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>BICARBONATO DE SODIO</t>
+          <t>ALHO LAMINADO DESIDRATADO</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -25446,10 +25446,10 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>10.5</v>
+        <v>85</v>
       </c>
       <c r="O325" t="n">
-        <v>10.5</v>
+        <v>85</v>
       </c>
       <c r="P325" t="n">
         <v>0</v>
@@ -25472,22 +25472,22 @@
       </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.webp</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>12004</v>
+        <v>12008</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>ALHO ROXO</t>
+          <t>ALHO GRANULADO</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -25549,22 +25549,22 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.webp</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>12006</v>
+        <v>12010</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>422</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>ALHO LAMINADO DESIDRATADO</t>
+          <t>ALHO FRITO</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -25600,10 +25600,10 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="O327" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="P327" t="n">
         <v>0</v>
@@ -25626,22 +25626,22 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>12008</v>
+        <v>12011</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>ALHO GRANULADO</t>
+          <t>ALHO EM PO 100% PURO</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -25677,10 +25677,10 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="O328" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="P328" t="n">
         <v>0</v>
@@ -25703,22 +25703,22 @@
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>12010</v>
+        <v>12019</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ALHO FRITO</t>
+          <t>ALECRIM</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -25754,10 +25754,10 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O329" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P329" t="n">
         <v>0</v>
@@ -25780,22 +25780,22 @@
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>12011</v>
+        <v>12023</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>ALHO EM PO 100% PURO</t>
+          <t>AIPO</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -25831,10 +25831,10 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O330" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P330" t="n">
         <v>0</v>
@@ -25857,22 +25857,22 @@
       </c>
       <c r="V330" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12023.jpg</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>12019</v>
+        <v>12031</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>ALECRIM</t>
+          <t>ACAFRAO NACIONAL</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -25908,10 +25908,10 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="O331" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="P331" t="n">
         <v>0</v>
@@ -25934,22 +25934,22 @@
       </c>
       <c r="V331" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>12023</v>
+        <v>12080</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>AIPO</t>
+          <t>CALDO DE GALINHA</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -25985,10 +25985,10 @@
         </is>
       </c>
       <c r="N332" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="O332" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P332" t="n">
         <v>0</v>
@@ -26011,22 +26011,22 @@
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12023.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.jpg</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>12031</v>
+        <v>12098</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>ACAFRAO NACIONAL</t>
+          <t>CALDO DE LEGUMES</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -26062,10 +26062,10 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="O333" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="P333" t="n">
         <v>0</v>
@@ -26088,22 +26088,22 @@
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>12080</v>
+        <v>12105</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>CALDO DE GALINHA</t>
+          <t>EDU GUEDES</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -26139,10 +26139,10 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="O334" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="P334" t="n">
         <v>0</v>
@@ -26165,22 +26165,22 @@
       </c>
       <c r="V334" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>12098</v>
+        <v>12106</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>CALDO DE LEGUMES</t>
+          <t>ANA MARIA</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -26216,10 +26216,10 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O335" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="P335" t="n">
         <v>0</v>
@@ -26242,22 +26242,22 @@
       </c>
       <c r="V335" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>12105</v>
+        <v>12107</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>EDU GUEDES</t>
+          <t>CEBOLA, ALHO E SALSA</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -26293,10 +26293,10 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="O336" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P336" t="n">
         <v>0</v>
@@ -26319,22 +26319,22 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>12106</v>
+        <v>12108</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>ANA MARIA</t>
+          <t>CHIMICHURRI SEM PIMENTA</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -26370,10 +26370,10 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="O337" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="P337" t="n">
         <v>0</v>
@@ -26396,22 +26396,22 @@
       </c>
       <c r="V337" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>12107</v>
+        <v>12109</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>CEBOLA, ALHO E SALSA</t>
+          <t>CHIMICHURRI COM PIMENTA</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -26447,10 +26447,10 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="O338" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P338" t="n">
         <v>0</v>
@@ -26473,22 +26473,22 @@
       </c>
       <c r="V338" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12109.webp</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>12108</v>
+        <v>12096</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>CHIMICHURRI SEM PIMENTA</t>
+          <t>PEGA MARIDO FIT</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -26524,10 +26524,10 @@
         </is>
       </c>
       <c r="N339" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="O339" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P339" t="n">
         <v>0</v>
@@ -26550,22 +26550,22 @@
       </c>
       <c r="V339" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.jpg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>12109</v>
+        <v>12097</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>CHIMICHURRI COM PIMENTA</t>
+          <t>EDU GUEDES FIT</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -26627,22 +26627,22 @@
       </c>
       <c r="V340" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12109.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12097.jpg</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>12096</v>
+        <v>12119</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>PEGA MARIDO FIT</t>
+          <t>CEBOLA GRANULADA</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -26678,10 +26678,10 @@
         </is>
       </c>
       <c r="N341" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="O341" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="P341" t="n">
         <v>0</v>
@@ -26704,22 +26704,22 @@
       </c>
       <c r="V341" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.jpg</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>12097</v>
+        <v>12115</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>EDU GUEDES FIT</t>
+          <t>LEMON PEPPER C/ GLUTAMATO</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -26755,10 +26755,10 @@
         </is>
       </c>
       <c r="N342" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O342" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P342" t="n">
         <v>0</v>
@@ -26781,22 +26781,22 @@
       </c>
       <c r="V342" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12097.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.png</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>12119</v>
+        <v>12145</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>CEBOLA GRANULADA</t>
+          <t>CHIMICHURRI FIT</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -26832,10 +26832,10 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="O343" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="P343" t="n">
         <v>0</v>
@@ -26858,22 +26858,22 @@
       </c>
       <c r="V343" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.webp</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>12115</v>
+        <v>12146</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>LEMON PEPPER C/ GLUTAMATO</t>
+          <t>CHIMICHURRI C/ PIMENTA FIT</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -26909,10 +26909,10 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O344" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P344" t="n">
         <v>0</v>
@@ -26935,22 +26935,22 @@
       </c>
       <c r="V344" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.webp</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>12145</v>
+        <v>12147</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>716</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>CHIMICHURRI FIT</t>
+          <t>LEMON PEPPER FIT</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -26986,10 +26986,10 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="O345" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P345" t="n">
         <v>0</v>
@@ -27012,22 +27012,22 @@
       </c>
       <c r="V345" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.jpg</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>12146</v>
+        <v>12148</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>CHIMICHURRI C/ PIMENTA FIT</t>
+          <t>TEMPERO ANA MARIA FIT</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -27063,10 +27063,10 @@
         </is>
       </c>
       <c r="N346" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="O346" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="P346" t="n">
         <v>0</v>
@@ -27089,37 +27089,37 @@
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>12147</v>
+        <v>12160</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>LEMON PEPPER FIT</t>
+          <t>MOSTARDA GRAO MARROM 100G</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H347" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I347" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J347" t="n">
         <v>100</v>
@@ -27140,10 +27140,10 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="O347" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="P347" t="n">
         <v>0</v>
@@ -27157,31 +27157,31 @@
         </is>
       </c>
       <c r="T347" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U347" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V347" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>12148</v>
+        <v>12161</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>TEMPERO ANA MARIA FIT</t>
+          <t>NOZ MOSCADA PO CONDIMENTADA</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -27217,10 +27217,10 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="O348" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="P348" t="n">
         <v>0</v>
@@ -27243,37 +27243,37 @@
       </c>
       <c r="V348" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>12160</v>
+        <v>12164</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>MOSTARDA GRAO MARROM 100G</t>
+          <t>PIMENTA JAMAICA (SIRIA PO)</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H349" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I349" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J349" t="n">
         <v>100</v>
@@ -27294,10 +27294,10 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="O349" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="P349" t="n">
         <v>0</v>
@@ -27311,168 +27311,14 @@
         </is>
       </c>
       <c r="T349" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U349" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V349" t="inlineStr">
-        <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="n">
-        <v>12161</v>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>NOZ MOSCADA PO CONDIMENTADA</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="G350" t="n">
-        <v>10</v>
-      </c>
-      <c r="H350" t="n">
-        <v>10</v>
-      </c>
-      <c r="I350" t="n">
-        <v>5</v>
-      </c>
-      <c r="J350" t="n">
-        <v>100</v>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>TEMPEROS A GRANEL</t>
-        </is>
-      </c>
-      <c r="N350" t="n">
-        <v>160</v>
-      </c>
-      <c r="O350" t="n">
-        <v>160</v>
-      </c>
-      <c r="P350" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="T350" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U350" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="V350" t="inlineStr">
-        <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>12164</v>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>PIMENTA JAMAICA (SIRIA PO)</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="G351" t="n">
-        <v>10</v>
-      </c>
-      <c r="H351" t="n">
-        <v>10</v>
-      </c>
-      <c r="I351" t="n">
-        <v>5</v>
-      </c>
-      <c r="J351" t="n">
-        <v>100</v>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t>TEMPEROS A GRANEL</t>
-        </is>
-      </c>
-      <c r="N351" t="n">
-        <v>85</v>
-      </c>
-      <c r="O351" t="n">
-        <v>85</v>
-      </c>
-      <c r="P351" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
-      <c r="S351" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="T351" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U351" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="V351" t="inlineStr">
         <is>
           <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.jpg</t>
         </is>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF349"/>
+  <dimension ref="A1:AF348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15545,16 +15545,16 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>12151</v>
+        <v>10831</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>306</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TAMARA LARGE JUMBO</t>
+          <t>FENO GREGO MOIDO</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -15566,7 +15566,7 @@
         <v>10</v>
       </c>
       <c r="H197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I197" t="n">
         <v>5</v>
@@ -15586,14 +15586,14 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>FRUTAS SECAS</t>
+          <t>GRAOS</t>
         </is>
       </c>
       <c r="N197" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="O197" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="P197" t="n">
         <v>0</v>
@@ -15611,27 +15611,27 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>100gr</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/12151.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.jpg</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>10831</v>
+        <v>11491</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>527</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>FENO GREGO MOIDO</t>
+          <t>TRIGO EM GRAO</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -15667,10 +15667,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="O198" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="P198" t="n">
         <v>0</v>
@@ -15693,22 +15693,22 @@
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/10831.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.jpg</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>11491</v>
+        <v>11515</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TRIGO EM GRAO</t>
+          <t>SOJA GRAO</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -15744,10 +15744,10 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="O199" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="P199" t="n">
         <v>0</v>
@@ -15770,22 +15770,22 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11491.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.jpg</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>11515</v>
+        <v>11528</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SOJA GRAO</t>
+          <t>SAGU</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -15821,10 +15821,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>9.9</v>
+        <v>16</v>
       </c>
       <c r="O200" t="n">
-        <v>9.9</v>
+        <v>16</v>
       </c>
       <c r="P200" t="n">
         <v>0</v>
@@ -15847,22 +15847,22 @@
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11515.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11528.webp</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>11528</v>
+        <v>11535</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SAGU</t>
+          <t>QUIRELA 500G</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -15898,10 +15898,10 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>16</v>
+        <v>3.6</v>
       </c>
       <c r="O201" t="n">
-        <v>16</v>
+        <v>3.6</v>
       </c>
       <c r="P201" t="n">
         <v>0</v>
@@ -15924,22 +15924,22 @@
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11528.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.jpg</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>11535</v>
+        <v>11536</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>QUIRELA 500G</t>
+          <t>QUINUA GRAO</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -15975,10 +15975,10 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>3.6</v>
+        <v>38</v>
       </c>
       <c r="O202" t="n">
-        <v>3.6</v>
+        <v>38</v>
       </c>
       <c r="P202" t="n">
         <v>0</v>
@@ -16001,22 +16001,22 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11535.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.webp</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>11536</v>
+        <v>11610</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>QUINUA GRAO</t>
+          <t>MIX QUINUA</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -16052,10 +16052,10 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O203" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="P203" t="n">
         <v>0</v>
@@ -16078,22 +16078,22 @@
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11536.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.jpg</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>11610</v>
+        <v>11617</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>MIX QUINUA</t>
+          <t>MILHO DE PIPOCA</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -16129,10 +16129,10 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>46</v>
+        <v>7.5</v>
       </c>
       <c r="O204" t="n">
-        <v>46</v>
+        <v>7.5</v>
       </c>
       <c r="P204" t="n">
         <v>0</v>
@@ -16155,22 +16155,22 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11610.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.jpg</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>11617</v>
+        <v>11651</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MILHO DE PIPOCA</t>
+          <t>LENTILHA VERMELHA</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>7.5</v>
+        <v>24.5</v>
       </c>
       <c r="O205" t="n">
-        <v>7.5</v>
+        <v>24.5</v>
       </c>
       <c r="P205" t="n">
         <v>0</v>
@@ -16232,22 +16232,22 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11617.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.jpg</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>11651</v>
+        <v>11652</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>LENTILHA VERMELHA</t>
+          <t>LENTILHA</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
       <c r="O206" t="n">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
       <c r="P206" t="n">
         <v>0</v>
@@ -16309,22 +16309,22 @@
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11651.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11652.jpg</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>11652</v>
+        <v>11686</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>LENTILHA</t>
+          <t>GRAO DE BICO  MIUDO</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="O207" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="P207" t="n">
         <v>0</v>
@@ -16386,22 +16386,22 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11652.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11686.png</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>11686</v>
+        <v>11687</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>GRAO DE BICO  MIUDO</t>
+          <t>GRAO DE BICO GRAUDO</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -16437,10 +16437,10 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>17.5</v>
+        <v>26.9</v>
       </c>
       <c r="O208" t="n">
-        <v>17.5</v>
+        <v>26.9</v>
       </c>
       <c r="P208" t="n">
         <v>0</v>
@@ -16463,22 +16463,22 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11686.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11687.webp</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>11687</v>
+        <v>11731</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>GRAO DE BICO GRAUDO</t>
+          <t>FENO GREGO EM GRAOS</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -16514,10 +16514,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>26.9</v>
+        <v>34</v>
       </c>
       <c r="O209" t="n">
-        <v>26.9</v>
+        <v>34</v>
       </c>
       <c r="P209" t="n">
         <v>0</v>
@@ -16540,27 +16540,27 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11687.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.jpg</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>11731</v>
+        <v>11732</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>FENO GREGO EM GRAOS</t>
+          <t>FEIJAO VERMELHO 500G</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -16591,10 +16591,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="O210" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="P210" t="n">
         <v>0</v>
@@ -16608,36 +16608,36 @@
         </is>
       </c>
       <c r="T210" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>100gr</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11731.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11732.jpg</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>11732</v>
+        <v>11734</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>519</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>FEIJAO VERMELHO 500G</t>
+          <t>FEIJAO ROXAO</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>11</v>
+        <v>24.8</v>
       </c>
       <c r="O211" t="n">
-        <v>11</v>
+        <v>24.8</v>
       </c>
       <c r="P211" t="n">
         <v>0</v>
@@ -16685,31 +16685,31 @@
         </is>
       </c>
       <c r="T211" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100gr</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11732.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11734.jpg</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>11734</v>
+        <v>11735</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>FEIJAO ROXAO</t>
+          <t>FEIJAO ROSINHA</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -16745,10 +16745,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>24.8</v>
+        <v>18</v>
       </c>
       <c r="O212" t="n">
-        <v>24.8</v>
+        <v>18</v>
       </c>
       <c r="P212" t="n">
         <v>0</v>
@@ -16771,22 +16771,22 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11734.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.jpg</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>11735</v>
+        <v>11737</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>FEIJAO ROSINHA</t>
+          <t>FEIJAO PRETO</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -16822,10 +16822,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>18</v>
+        <v>8.9</v>
       </c>
       <c r="O213" t="n">
-        <v>18</v>
+        <v>8.9</v>
       </c>
       <c r="P213" t="n">
         <v>0</v>
@@ -16848,22 +16848,22 @@
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11735.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11737.png</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>11737</v>
+        <v>11738</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>FEIJAO PRETO</t>
+          <t>FEIJAO MOYASHI</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -16899,10 +16899,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>8.9</v>
+        <v>19</v>
       </c>
       <c r="O214" t="n">
-        <v>8.9</v>
+        <v>19</v>
       </c>
       <c r="P214" t="n">
         <v>0</v>
@@ -16925,22 +16925,22 @@
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11737.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.jpg</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>11738</v>
+        <v>11741</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>FEIJAO MOYASHI</t>
+          <t>FEIJAO FRADINHO</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -16976,10 +16976,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>19</v>
+        <v>9.9</v>
       </c>
       <c r="O215" t="n">
-        <v>19</v>
+        <v>9.9</v>
       </c>
       <c r="P215" t="n">
         <v>0</v>
@@ -17002,22 +17002,22 @@
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11738.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.webp</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>11741</v>
+        <v>11743</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>FEIJAO FRADINHO</t>
+          <t>FEIJAO CORDA</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="O216" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="P216" t="n">
         <v>0</v>
@@ -17079,22 +17079,22 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11741.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11743.webp</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>11743</v>
+        <v>11744</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>FEIJAO CORDA</t>
+          <t>FEIJAO CARIOCA</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="O217" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="P217" t="n">
         <v>0</v>
@@ -17156,22 +17156,22 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11743.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.jpg</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>11744</v>
+        <v>11745</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>FEIJAO CARIOCA</t>
+          <t>FEIJAO BRANCO</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -17207,10 +17207,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="O218" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="P218" t="n">
         <v>0</v>
@@ -17233,22 +17233,22 @@
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11744.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.jpg</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>11745</v>
+        <v>11747</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FEIJAO BRANCO</t>
+          <t>FEIJAO BOLINHA</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>15.9</v>
+        <v>24.9</v>
       </c>
       <c r="O219" t="n">
-        <v>15.9</v>
+        <v>24.9</v>
       </c>
       <c r="P219" t="n">
         <v>0</v>
@@ -17310,22 +17310,22 @@
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11745.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11747.jpg</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>11747</v>
+        <v>11748</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>335</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FEIJAO BOLINHA</t>
+          <t>FEIJAO AZUKI</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -17361,10 +17361,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>24.9</v>
+        <v>19</v>
       </c>
       <c r="O220" t="n">
-        <v>24.9</v>
+        <v>19</v>
       </c>
       <c r="P220" t="n">
         <v>0</v>
@@ -17387,22 +17387,22 @@
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11747.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.jpg</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>11748</v>
+        <v>11749</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FEIJAO AZUKI</t>
+          <t>FEIJAO ANDU</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -17438,10 +17438,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>19</v>
+        <v>26.9</v>
       </c>
       <c r="O221" t="n">
-        <v>19</v>
+        <v>26.9</v>
       </c>
       <c r="P221" t="n">
         <v>0</v>
@@ -17464,22 +17464,22 @@
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11748.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.jpg</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>11749</v>
+        <v>11751</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>FEIJAO ANDU</t>
+          <t>FAVA BRANCA MIUDA</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -17515,10 +17515,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>26.9</v>
+        <v>42</v>
       </c>
       <c r="O222" t="n">
-        <v>26.9</v>
+        <v>42</v>
       </c>
       <c r="P222" t="n">
         <v>0</v>
@@ -17541,22 +17541,22 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11749.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.jpg</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>11751</v>
+        <v>11752</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FAVA BRANCA MIUDA</t>
+          <t>FAVA BRANCA GRAUDA</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -17592,10 +17592,10 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>42</v>
+        <v>32.9</v>
       </c>
       <c r="O223" t="n">
-        <v>42</v>
+        <v>32.9</v>
       </c>
       <c r="P223" t="n">
         <v>0</v>
@@ -17618,22 +17618,22 @@
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11751.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.jpg</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>11752</v>
+        <v>11804</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FAVA BRANCA GRAUDA</t>
+          <t>ERVILHA PARTIDA</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -17669,10 +17669,10 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>32.9</v>
+        <v>16</v>
       </c>
       <c r="O224" t="n">
-        <v>32.9</v>
+        <v>16</v>
       </c>
       <c r="P224" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11752.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.webp</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>11804</v>
+        <v>11911</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ERVILHA PARTIDA</t>
+          <t>CANJICA BRANCA</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -17746,10 +17746,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>16</v>
+        <v>9.9</v>
       </c>
       <c r="O225" t="n">
-        <v>16</v>
+        <v>9.9</v>
       </c>
       <c r="P225" t="n">
         <v>0</v>
@@ -17772,22 +17772,22 @@
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11804.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.jpg</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>11911</v>
+        <v>11912</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CANJICA BRANCA</t>
+          <t>CANJICA AMARELA</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -17823,10 +17823,10 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>9.9</v>
+        <v>6.25</v>
       </c>
       <c r="O226" t="n">
-        <v>9.9</v>
+        <v>6.25</v>
       </c>
       <c r="P226" t="n">
         <v>0</v>
@@ -17849,27 +17849,27 @@
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11911.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11912.jpg</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>11912</v>
+        <v>11957</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CANJICA AMARELA</t>
+          <t>ARROZ VERMELHO 500G</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -17900,10 +17900,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="O227" t="n">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="P227" t="n">
         <v>0</v>
@@ -17917,36 +17917,36 @@
         </is>
       </c>
       <c r="T227" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>100gr</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11912.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.jpg</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>11957</v>
+        <v>11958</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ARROZ VERMELHO 500G</t>
+          <t>ARROZ NEGRO</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="O228" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="P228" t="n">
         <v>0</v>
@@ -17994,31 +17994,31 @@
         </is>
       </c>
       <c r="T228" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100gr</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11957.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11958.jpg</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>11958</v>
+        <v>11959</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ARROZ NEGRO</t>
+          <t>ARROZ INTEGRAL CATETO BRANCO</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -18054,10 +18054,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>49</v>
+        <v>22.5</v>
       </c>
       <c r="O229" t="n">
-        <v>49</v>
+        <v>22.5</v>
       </c>
       <c r="P229" t="n">
         <v>0</v>
@@ -18080,22 +18080,22 @@
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11958.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.png</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>11959</v>
+        <v>11960</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ARROZ INTEGRAL CATETO BRANCO</t>
+          <t>ARROZ INTEGRAL AGULHA MISTO</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -18131,10 +18131,10 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>22.5</v>
+        <v>15.9</v>
       </c>
       <c r="O230" t="n">
-        <v>22.5</v>
+        <v>15.9</v>
       </c>
       <c r="P230" t="n">
         <v>0</v>
@@ -18157,22 +18157,22 @@
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11959.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11960.jpg</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>11960</v>
+        <v>11961</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>297</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ARROZ INTEGRAL AGULHA MISTO</t>
+          <t>ARROZ INTEGRAL AGULHA BRANCO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>15.9</v>
+        <v>13.5</v>
       </c>
       <c r="O231" t="n">
-        <v>15.9</v>
+        <v>13.5</v>
       </c>
       <c r="P231" t="n">
         <v>0</v>
@@ -18234,22 +18234,22 @@
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11960.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11961.jpg</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>11961</v>
+        <v>11962</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ARROZ INTEGRAL AGULHA BRANCO</t>
+          <t>ARROZ 7 GRAOS</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -18285,10 +18285,10 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="O232" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="P232" t="n">
         <v>0</v>
@@ -18311,22 +18311,22 @@
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11961.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11962.webp</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>11962</v>
+        <v>12002</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ARROZ 7 GRAOS</t>
+          <t>AMARANTO GRAO</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -18362,10 +18362,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="O233" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="P233" t="n">
         <v>0</v>
@@ -18388,22 +18388,22 @@
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/11962.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12002.webp</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>12002</v>
+        <v>12077</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>AMARANTO GRAO</t>
+          <t>CAFE GRAO A GRANEL</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -18439,10 +18439,10 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="O234" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="P234" t="n">
         <v>0</v>
@@ -18465,22 +18465,22 @@
       </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12002.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.jpg</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>12077</v>
+        <v>12084</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>CAFE GRAO A GRANEL</t>
+          <t>FEIJAO RAJADO</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -18516,10 +18516,10 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>98</v>
+        <v>17.9</v>
       </c>
       <c r="O235" t="n">
-        <v>98</v>
+        <v>17.9</v>
       </c>
       <c r="P235" t="n">
         <v>0</v>
@@ -18542,22 +18542,22 @@
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12077.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12084.webp</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>12084</v>
+        <v>12101</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>FEIJAO RAJADO</t>
+          <t>ARROZ VERMELHO GRANEL</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -18593,10 +18593,10 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>17.9</v>
+        <v>10</v>
       </c>
       <c r="O236" t="n">
-        <v>17.9</v>
+        <v>10</v>
       </c>
       <c r="P236" t="n">
         <v>0</v>
@@ -18619,22 +18619,22 @@
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12084.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.jpg</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>12101</v>
+        <v>12102</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>741</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ARROZ VERMELHO GRANEL</t>
+          <t>QUIRELA</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -18670,10 +18670,10 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O237" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P237" t="n">
         <v>0</v>
@@ -18696,22 +18696,22 @@
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12101.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.png</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>12102</v>
+        <v>10449</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>QUIRELA</t>
+          <t>GERGELIM TORRADO</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -18743,14 +18743,14 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>GRAOS</t>
+          <t>SEMENTES</t>
         </is>
       </c>
       <c r="N238" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="O238" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="P238" t="n">
         <v>0</v>
@@ -18768,27 +18768,27 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>100gr</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/graos/12102.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.jpg</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>10449</v>
+        <v>10988</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>GERGELIM TORRADO</t>
+          <t>GIRASSOL S/CASCA TORRADO</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -18824,10 +18824,10 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O239" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="P239" t="n">
         <v>0</v>
@@ -18850,40 +18850,40 @@
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10449.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.jpg</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>10988</v>
+        <v>11184</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>GIRASSOL S/CASCA TORRADO</t>
+          <t>SEMENTE DE MELANCIA 25G</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UN</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H240" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I240" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J240" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -18901,10 +18901,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="O240" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="P240" t="n">
         <v>0</v>
@@ -18918,49 +18918,49 @@
         </is>
       </c>
       <c r="T240" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/10988.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.jpg</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>11184</v>
+        <v>11518</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SEMENTE DE MELANCIA 25G</t>
+          <t>SEMENTE DE ABOBORA S/C TOR S/S</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>UN</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H241" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I241" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J241" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -18978,10 +18978,10 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="O241" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="P241" t="n">
         <v>0</v>
@@ -18995,31 +18995,31 @@
         </is>
       </c>
       <c r="T241" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11184.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11518.jpg</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>11518</v>
+        <v>11519</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SEMENTE DE ABOBORA S/C TOR S/S</t>
+          <t>SEMENTE DE ABOBORA CRUA S/ CASCA</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -19055,10 +19055,10 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="O242" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="P242" t="n">
         <v>0</v>
@@ -19081,22 +19081,22 @@
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11518.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.jpg</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>11519</v>
+        <v>11645</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>SEMENTE DE ABOBORA CRUA S/ CASCA</t>
+          <t>LINHACA MARROM SEMENTE</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -19132,10 +19132,10 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="O243" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="P243" t="n">
         <v>0</v>
@@ -19158,22 +19158,22 @@
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11519.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.jpg</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>11645</v>
+        <v>11646</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>LINHACA MARROM SEMENTE</t>
+          <t>LINHACA DOURADA SEMENTE</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -19209,10 +19209,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="O244" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="P244" t="n">
         <v>0</v>
@@ -19235,22 +19235,22 @@
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11645.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.jpg</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>11646</v>
+        <v>11698</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>LINHACA DOURADA SEMENTE</t>
+          <t>GIRASSOL S/CASCA</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -19286,10 +19286,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="O245" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="P245" t="n">
         <v>0</v>
@@ -19312,22 +19312,22 @@
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11646.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11698.webp</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>11698</v>
+        <v>11705</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>GIRASSOL S/CASCA</t>
+          <t>GERGELIM S/ PELE</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -19363,10 +19363,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O246" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P246" t="n">
         <v>0</v>
@@ -19389,22 +19389,22 @@
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11698.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.jpg</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>11705</v>
+        <v>11706</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>GERGELIM S/ PELE</t>
+          <t>GERGELIM PRETO</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -19440,10 +19440,10 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="O247" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="P247" t="n">
         <v>0</v>
@@ -19466,22 +19466,22 @@
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11705.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.png</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>11706</v>
+        <v>11707</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>GERGELIM PRETO</t>
+          <t>GERGELIM C/ PELE</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -19517,10 +19517,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="O248" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="P248" t="n">
         <v>0</v>
@@ -19543,22 +19543,22 @@
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11706.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.jpg</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>11707</v>
+        <v>11865</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>822</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>GERGELIM C/ PELE</t>
+          <t>CHIA PREMIUM</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -19594,10 +19594,10 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O249" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="P249" t="n">
         <v>0</v>
@@ -19620,22 +19620,22 @@
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11707.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.webp</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>11865</v>
+        <v>10058</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CHIA PREMIUM</t>
+          <t>PIMENTA BRANCA GRAO</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -19667,14 +19667,14 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>SEMENTES</t>
+          <t>TEMPEROS A GRANEL</t>
         </is>
       </c>
       <c r="N250" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="O250" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="P250" t="n">
         <v>0</v>
@@ -19697,22 +19697,22 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/sementes/11865.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.jpg</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>10058</v>
+        <v>10061</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>PIMENTA BRANCA GRAO</t>
+          <t>CALDO DE PEIXE</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -19748,10 +19748,10 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="O251" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="P251" t="n">
         <v>0</v>
@@ -19774,22 +19774,22 @@
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10058.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.png</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>10061</v>
+        <v>10102</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CALDO DE PEIXE</t>
+          <t>TEMPERO TAILANDES</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -19825,10 +19825,10 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="O252" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="P252" t="n">
         <v>0</v>
@@ -19851,22 +19851,22 @@
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10061.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10102.webp</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>10102</v>
+        <v>10256</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>TEMPERO TAILANDES</t>
+          <t>OREGANO EM PO 20G</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -19902,10 +19902,10 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="O253" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="P253" t="n">
         <v>0</v>
@@ -19928,22 +19928,22 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10102.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.webp</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>10256</v>
+        <v>10264</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>OREGANO EM PO 20G</t>
+          <t>MANJERICAO EM PO</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -19979,10 +19979,10 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="O254" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P254" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10256.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>10264</v>
+        <v>10306</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>MANJERICAO EM PO</t>
+          <t>CANELA PO PURA PREMIUM</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -20056,10 +20056,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="O255" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="P255" t="n">
         <v>0</v>
@@ -20082,22 +20082,22 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10264.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.jpg</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>10306</v>
+        <v>10308</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>CANELA PO PURA PREMIUM</t>
+          <t>CHIMICHURRI DEFUMADO</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -20133,10 +20133,10 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="O256" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="P256" t="n">
         <v>0</v>
@@ -20159,22 +20159,22 @@
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10306.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.jpg</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>10308</v>
+        <v>10550</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>CHIMICHURRI DEFUMADO</t>
+          <t>ORANGE PEPPER</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="O257" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="P257" t="n">
         <v>0</v>
@@ -20236,22 +20236,22 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10308.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>10550</v>
+        <v>10720</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ORANGE PEPPER</t>
+          <t>ALHO ROXO SOLTO</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -20287,10 +20287,10 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O258" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P258" t="n">
         <v>0</v>
@@ -20313,22 +20313,22 @@
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10550.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>10720</v>
+        <v>10887</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ALHO ROXO SOLTO</t>
+          <t>ACAFRAO IMPORTADO</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O259" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P259" t="n">
         <v>0</v>
@@ -20390,22 +20390,22 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10720.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>10887</v>
+        <v>10902</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ACAFRAO IMPORTADO</t>
+          <t>TEMPERO BAIANO SEM PIMENTA</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -20441,10 +20441,10 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="O260" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="P260" t="n">
         <v>0</v>
@@ -20467,22 +20467,22 @@
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10887.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>10902</v>
+        <v>10967</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO SEM PIMENTA</t>
+          <t>CREME DE CEBOLA</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -20518,10 +20518,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="O261" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="P261" t="n">
         <v>0</v>
@@ -20544,22 +20544,22 @@
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10902.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>10967</v>
+        <v>11029</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CREME DE CEBOLA</t>
+          <t>CEBOLA CRISPY</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -20595,10 +20595,10 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="O262" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="P262" t="n">
         <v>0</v>
@@ -20621,22 +20621,22 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/10967.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.webp</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>11029</v>
+        <v>11167</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>CEBOLA CRISPY</t>
+          <t>FIT EDU GUEDES</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -20672,10 +20672,10 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="O263" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="P263" t="n">
         <v>0</v>
@@ -20698,22 +20698,22 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11029.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11167.jpg</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>11167</v>
+        <v>11168</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>FIT EDU GUEDES</t>
+          <t>TEMPERO MINEIRO</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -20749,10 +20749,10 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="O264" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="P264" t="n">
         <v>0</v>
@@ -20775,22 +20775,22 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11167.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>11168</v>
+        <v>11170</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>TEMPERO MINEIRO</t>
+          <t>FIT COMPLETO</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -20826,10 +20826,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O265" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P265" t="n">
         <v>0</v>
@@ -20852,22 +20852,22 @@
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11168.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>11170</v>
+        <v>11237</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>FIT COMPLETO</t>
+          <t>TEMPERO SIRIO</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -20903,10 +20903,10 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O266" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="P266" t="n">
         <v>0</v>
@@ -20929,22 +20929,22 @@
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11170.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.jpg</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>11237</v>
+        <v>11466</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>TEMPERO SIRIO</t>
+          <t>ZIMBRO</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -20980,10 +20980,10 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>38</v>
+        <v>229</v>
       </c>
       <c r="O267" t="n">
-        <v>38</v>
+        <v>229</v>
       </c>
       <c r="P267" t="n">
         <v>0</v>
@@ -21006,22 +21006,22 @@
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11237.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.jpg</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>11466</v>
+        <v>11468</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>971</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>ZIMBRO</t>
+          <t>ZATTAR</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -21057,10 +21057,10 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>229</v>
+        <v>55</v>
       </c>
       <c r="O268" t="n">
-        <v>229</v>
+        <v>55</v>
       </c>
       <c r="P268" t="n">
         <v>0</v>
@@ -21083,22 +21083,22 @@
       </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11466.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.webp</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>11468</v>
+        <v>11473</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>ZATTAR</t>
+          <t>VINAGRETE</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -21134,10 +21134,10 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="O269" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="P269" t="n">
         <v>0</v>
@@ -21160,22 +21160,22 @@
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11468.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>11473</v>
+        <v>11487</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>VINAGRETE</t>
+          <t>PEGA MARIDO</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -21211,10 +21211,10 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="O270" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P270" t="n">
         <v>0</v>
@@ -21237,22 +21237,22 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11473.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.jpg</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>11487</v>
+        <v>11493</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>PEGA MARIDO</t>
+          <t>TOMILHO</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -21288,10 +21288,10 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="O271" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="P271" t="n">
         <v>0</v>
@@ -21314,22 +21314,22 @@
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11487.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.jpg</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>11493</v>
+        <v>11496</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>TOMILHO</t>
+          <t>TEMPERO FEIJAO</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -21365,10 +21365,10 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="O272" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="P272" t="n">
         <v>0</v>
@@ -21391,22 +21391,22 @@
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11493.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>11496</v>
+        <v>11497</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>TEMPERO FEIJAO</t>
+          <t>LEMON COM ERVAS FINAS</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -21442,10 +21442,10 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="O273" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P273" t="n">
         <v>0</v>
@@ -21468,22 +21468,22 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11496.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.png</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>11497</v>
+        <v>11499</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>LEMON COM ERVAS FINAS</t>
+          <t>TEMPERO BAIANO PO</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -21519,10 +21519,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="O274" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="P274" t="n">
         <v>0</v>
@@ -21545,22 +21545,22 @@
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>11499</v>
+        <v>11500</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO PO</t>
+          <t>TEMPERO BAIANO GRAO</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -21596,10 +21596,10 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="O275" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="P275" t="n">
         <v>0</v>
@@ -21622,22 +21622,22 @@
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11499.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>11500</v>
+        <v>11502</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>TEMPERO BAIANO GRAO</t>
+          <t>TEMPERO ANA MARIA</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="O276" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="P276" t="n">
         <v>0</v>
@@ -21699,22 +21699,22 @@
       </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11500.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>11502</v>
+        <v>11523</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>TEMPERO ANA MARIA</t>
+          <t>SALSA DESIDRATADA</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -21750,10 +21750,10 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="O277" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P277" t="n">
         <v>0</v>
@@ -21776,22 +21776,22 @@
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11502.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>11523</v>
+        <v>11563</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>SALSA DESIDRATADA</t>
+          <t>PIMENTA SIRIA PO (JAMAICA)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -21827,10 +21827,10 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="O278" t="n">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="P278" t="n">
         <v>0</v>
@@ -21853,22 +21853,22 @@
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11523.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>11563</v>
+        <v>11565</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>PIMENTA SIRIA PO (JAMAICA)</t>
+          <t>PIMENTA SIRIA GRAO (JAMAICA)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -21904,10 +21904,10 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="O279" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="P279" t="n">
         <v>0</v>
@@ -21930,22 +21930,22 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11563.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>11565</v>
+        <v>11567</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>PIMENTA SIRIA GRAO (JAMAICA)</t>
+          <t>PIMENTA ROSA</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -21981,10 +21981,10 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="O280" t="n">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="P280" t="n">
         <v>0</v>
@@ -22007,22 +22007,22 @@
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11565.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>11567</v>
+        <v>11568</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>PIMENTA ROSA</t>
+          <t>PIMENTA DO REINO PRETA PO</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="O281" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="P281" t="n">
         <v>0</v>
@@ -22084,22 +22084,22 @@
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11567.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.jpg</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>11568</v>
+        <v>11569</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO PRETA PO</t>
+          <t>PIMENTA DO REINO  PRETA  GRAO</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -22135,10 +22135,10 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O282" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="P282" t="n">
         <v>0</v>
@@ -22161,22 +22161,22 @@
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11568.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>11569</v>
+        <v>11570</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO  PRETA  GRAO</t>
+          <t>PIMENTA DO REINO BRANCA EM PO</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -22212,10 +22212,10 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="O283" t="n">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="P283" t="n">
         <v>0</v>
@@ -22238,22 +22238,22 @@
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11569.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.jpg</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>11570</v>
+        <v>11571</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>PIMENTA DO REINO BRANCA EM PO</t>
+          <t>PIMENTA CHILLI</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -22289,10 +22289,10 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="O284" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="P284" t="n">
         <v>0</v>
@@ -22315,22 +22315,22 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11570.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.png</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>11571</v>
+        <v>11572</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>PIMENTA CHILLI</t>
+          <t>PIMENTA CALABRESA FLOCOS</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -22366,10 +22366,10 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="O285" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="P285" t="n">
         <v>0</v>
@@ -22392,22 +22392,22 @@
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11571.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.webp</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>11572</v>
+        <v>11573</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>607</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>PIMENTA CALABRESA FLOCOS</t>
+          <t>PIMENTA CAYENA</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -22443,10 +22443,10 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="O286" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="P286" t="n">
         <v>0</v>
@@ -22469,22 +22469,22 @@
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11572.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.jpg</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>11573</v>
+        <v>11584</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>PIMENTA CAYENA</t>
+          <t>PAPRICA PICANTE</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -22520,10 +22520,10 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="O287" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="P287" t="n">
         <v>0</v>
@@ -22546,22 +22546,22 @@
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11573.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>11584</v>
+        <v>11586</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>PAPRICA PICANTE</t>
+          <t>PAPRICA DOCE</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -22623,22 +22623,22 @@
       </c>
       <c r="V288" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11584.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>11586</v>
+        <v>11588</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>PAPRICA DOCE</t>
+          <t>PAPRICA DEFUMADA</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -22700,22 +22700,22 @@
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11586.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>11588</v>
+        <v>11592</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>PAPRICA DEFUMADA</t>
+          <t>OREGANO</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -22751,10 +22751,10 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O290" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="P290" t="n">
         <v>0</v>
@@ -22777,22 +22777,22 @@
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11588.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>11592</v>
+        <v>11602</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>OREGANO</t>
+          <t>NOZ MOSCADA PO</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -22828,10 +22828,10 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="O291" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="P291" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11592.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>11602</v>
+        <v>11607</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>NOZ MOSCADA PO</t>
+          <t>MOSTARDA PO PURA</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -22905,10 +22905,10 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="O292" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="P292" t="n">
         <v>0</v>
@@ -22931,22 +22931,22 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11602.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.png</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>11607</v>
+        <v>11608</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>MOSTARDA PO PURA</t>
+          <t>MOSTARDA GRAO</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -22982,10 +22982,10 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="O293" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="P293" t="n">
         <v>0</v>
@@ -23008,22 +23008,22 @@
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11607.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.jpg</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>11608</v>
+        <v>11629</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>MOSTARDA GRAO</t>
+          <t>MANJERONA DESIDRATADO</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -23059,10 +23059,10 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="O294" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="P294" t="n">
         <v>0</v>
@@ -23085,22 +23085,22 @@
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11608.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.jpg</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>11629</v>
+        <v>11630</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>MANJERONA DESIDRATADO</t>
+          <t>MANJERICAO DESIDRATADO</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -23136,10 +23136,10 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O295" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P295" t="n">
         <v>0</v>
@@ -23162,22 +23162,22 @@
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11629.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.png</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>11630</v>
+        <v>11642</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>MANJERICAO DESIDRATADO</t>
+          <t>LOURO EM PO</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -23213,10 +23213,10 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="O296" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="P296" t="n">
         <v>0</v>
@@ -23239,22 +23239,22 @@
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11630.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.png</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>11642</v>
+        <v>11643</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>811</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>LOURO EM PO</t>
+          <t>LOURO EM FOLHA</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -23290,10 +23290,10 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="O297" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -23316,22 +23316,22 @@
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11642.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.webp</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>11643</v>
+        <v>11647</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>LOURO EM FOLHA</t>
+          <t>LEMON PEPPER 0% SODIO</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -23367,10 +23367,10 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O298" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P298" t="n">
         <v>0</v>
@@ -23393,22 +23393,22 @@
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11643.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>11647</v>
+        <v>11655</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>LEMON PEPPER 0% SODIO</t>
+          <t>LEMON PEPPER</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -23444,10 +23444,10 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="O299" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="P299" t="n">
         <v>0</v>
@@ -23470,22 +23470,22 @@
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11647.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.jpg</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>11655</v>
+        <v>11717</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>LEMON PEPPER</t>
+          <t>FUMACA EM PO</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -23521,10 +23521,10 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="O300" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P300" t="n">
         <v>0</v>
@@ -23547,22 +23547,22 @@
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11655.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>11717</v>
+        <v>11806</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>FUMACA EM PO</t>
+          <t>ERVAS FINAS</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -23598,10 +23598,10 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="O301" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="P301" t="n">
         <v>0</v>
@@ -23624,22 +23624,22 @@
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11717.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>11806</v>
+        <v>11818</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>ERVAS FINAS</t>
+          <t>ENDRO</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -23675,10 +23675,10 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="O302" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="P302" t="n">
         <v>0</v>
@@ -23701,22 +23701,22 @@
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11806.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>11818</v>
+        <v>11822</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>ENDRO</t>
+          <t>EDU GUEDES</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -23752,10 +23752,10 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="O303" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P303" t="n">
         <v>0</v>
@@ -23778,22 +23778,22 @@
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11818.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>11822</v>
+        <v>11830</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>EDU GUEDES</t>
+          <t>CURRY</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -23829,10 +23829,10 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O304" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P304" t="n">
         <v>0</v>
@@ -23855,22 +23855,22 @@
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11822.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.jpg</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>11830</v>
+        <v>11833</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>CURRY</t>
+          <t>CRAVO MOIDO</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -23906,10 +23906,10 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="O305" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="P305" t="n">
         <v>0</v>
@@ -23932,22 +23932,22 @@
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11830.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.jpg</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>11833</v>
+        <v>11834</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>CRAVO MOIDO</t>
+          <t>CRAVO GRAO</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -23983,10 +23983,10 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="O306" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -24009,22 +24009,22 @@
       </c>
       <c r="V306" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11833.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.jpg</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>11834</v>
+        <v>11838</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>CRAVO GRAO</t>
+          <t>COMINHO PO PURO</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -24060,10 +24060,10 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="O307" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -24086,22 +24086,22 @@
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11834.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.png</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>11838</v>
+        <v>11839</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>COMINHO PO PURO</t>
+          <t>COMINHO GRAO 99%</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -24137,10 +24137,10 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="O308" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="P308" t="n">
         <v>0</v>
@@ -24163,22 +24163,22 @@
       </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11838.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11839.png</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>11839</v>
+        <v>11840</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>571</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>COMINHO GRAO 99%</t>
+          <t>COLORAU</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -24214,10 +24214,10 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="O309" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="P309" t="n">
         <v>0</v>
@@ -24240,22 +24240,22 @@
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11839.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>11840</v>
+        <v>11843</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>COLORAU</t>
+          <t>COENTRO GRAO</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -24291,10 +24291,10 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="O310" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="P310" t="n">
         <v>0</v>
@@ -24317,22 +24317,22 @@
       </c>
       <c r="V310" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11840.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.jpg</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>11843</v>
+        <v>11844</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>COENTRO GRAO</t>
+          <t>COENTRO FOLHAS</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -24368,10 +24368,10 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>17.5</v>
+        <v>64</v>
       </c>
       <c r="O311" t="n">
-        <v>17.5</v>
+        <v>64</v>
       </c>
       <c r="P311" t="n">
         <v>0</v>
@@ -24394,22 +24394,22 @@
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11843.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.webp</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>11844</v>
+        <v>11845</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>COENTRO FOLHAS</t>
+          <t>COENTRO EM PO</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -24445,10 +24445,10 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="O312" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="P312" t="n">
         <v>0</v>
@@ -24471,22 +24471,22 @@
       </c>
       <c r="V312" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11844.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.png</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>11845</v>
+        <v>11863</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>404</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>COENTRO EM PO</t>
+          <t>CHIMICHURRI SEM PIMENTA</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="O313" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="P313" t="n">
         <v>0</v>
@@ -24548,22 +24548,22 @@
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11845.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>11863</v>
+        <v>11864</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>CHIMICHURRI SEM PIMENTA</t>
+          <t>CHIMICHURRI COM PIMENTA</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -24625,22 +24625,22 @@
       </c>
       <c r="V314" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11863.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11864.webp</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>11864</v>
+        <v>11874</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>CHIMICHURRI COM PIMENTA</t>
+          <t>CEBOLINHA DESIDRATADA</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -24676,10 +24676,10 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O315" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P315" t="n">
         <v>0</v>
@@ -24702,22 +24702,22 @@
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11864.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11874.webp</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>11874</v>
+        <v>11875</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>CEBOLINHA DESIDRATADA</t>
+          <t>CEBOLA, ALHO E SALSA</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -24753,10 +24753,10 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O316" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P316" t="n">
         <v>0</v>
@@ -24779,22 +24779,22 @@
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11874.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>11875</v>
+        <v>11877</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CEBOLA, ALHO E SALSA</t>
+          <t>CEBOLA FLOCOS</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -24830,10 +24830,10 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O317" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P317" t="n">
         <v>0</v>
@@ -24856,22 +24856,22 @@
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11875.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>11877</v>
+        <v>11879</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>982</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CEBOLA FLOCOS</t>
+          <t>CEBOLA EM PO</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -24907,10 +24907,10 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="O318" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P318" t="n">
         <v>0</v>
@@ -24933,22 +24933,22 @@
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11877.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11879.jpg</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>11879</v>
+        <v>11909</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>CEBOLA EM PO</t>
+          <t>CARDAMOMO SEMENTES</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -24984,10 +24984,10 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>45</v>
+        <v>680</v>
       </c>
       <c r="O319" t="n">
-        <v>45</v>
+        <v>680</v>
       </c>
       <c r="P319" t="n">
         <v>0</v>
@@ -25010,22 +25010,22 @@
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11879.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.jpg</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>11909</v>
+        <v>11910</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CARDAMOMO SEMENTES</t>
+          <t>CARDAMOMO PO</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -25087,22 +25087,22 @@
       </c>
       <c r="V320" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11909.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>11910</v>
+        <v>11913</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CARDAMOMO PO</t>
+          <t>CANELA EM PO PURA</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -25138,10 +25138,10 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>680</v>
+        <v>35</v>
       </c>
       <c r="O321" t="n">
-        <v>680</v>
+        <v>35</v>
       </c>
       <c r="P321" t="n">
         <v>0</v>
@@ -25164,22 +25164,22 @@
       </c>
       <c r="V321" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11910.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.jpg</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>11913</v>
+        <v>11931</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CANELA EM PO PURA</t>
+          <t>BICARBONATO DE SODIO</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -25215,10 +25215,10 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>35</v>
+        <v>10.5</v>
       </c>
       <c r="O322" t="n">
-        <v>35</v>
+        <v>10.5</v>
       </c>
       <c r="P322" t="n">
         <v>0</v>
@@ -25241,22 +25241,22 @@
       </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11913.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.webp</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>11931</v>
+        <v>12004</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>BICARBONATO DE SODIO</t>
+          <t>ALHO ROXO</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -25292,10 +25292,10 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>10.5</v>
+        <v>49</v>
       </c>
       <c r="O323" t="n">
-        <v>10.5</v>
+        <v>49</v>
       </c>
       <c r="P323" t="n">
         <v>0</v>
@@ -25318,22 +25318,22 @@
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11931.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>12004</v>
+        <v>12006</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>ALHO ROXO</t>
+          <t>ALHO LAMINADO DESIDRATADO</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -25369,10 +25369,10 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="O324" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="P324" t="n">
         <v>0</v>
@@ -25395,22 +25395,22 @@
       </c>
       <c r="V324" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12004.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.webp</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>12006</v>
+        <v>12008</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>ALHO LAMINADO DESIDRATADO</t>
+          <t>ALHO GRANULADO</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -25446,10 +25446,10 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="O325" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="P325" t="n">
         <v>0</v>
@@ -25472,22 +25472,22 @@
       </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12006.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.webp</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>12008</v>
+        <v>12010</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>422</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>ALHO GRANULADO</t>
+          <t>ALHO FRITO</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -25523,10 +25523,10 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O326" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P326" t="n">
         <v>0</v>
@@ -25549,22 +25549,22 @@
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12008.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>12010</v>
+        <v>12011</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>ALHO FRITO</t>
+          <t>ALHO EM PO 100% PURO</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -25600,10 +25600,10 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O327" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P327" t="n">
         <v>0</v>
@@ -25626,22 +25626,22 @@
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12010.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>12011</v>
+        <v>12019</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>ALHO EM PO 100% PURO</t>
+          <t>ALECRIM</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -25703,22 +25703,22 @@
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12011.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>12019</v>
+        <v>12023</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ALECRIM</t>
+          <t>AIPO</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -25754,10 +25754,10 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O329" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P329" t="n">
         <v>0</v>
@@ -25780,22 +25780,22 @@
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12019.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12023.jpg</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>12023</v>
+        <v>12031</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>AIPO</t>
+          <t>ACAFRAO NACIONAL</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -25831,10 +25831,10 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="O330" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="P330" t="n">
         <v>0</v>
@@ -25857,22 +25857,22 @@
       </c>
       <c r="V330" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12023.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>12031</v>
+        <v>12080</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>ACAFRAO NACIONAL</t>
+          <t>CALDO DE GALINHA</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -25908,10 +25908,10 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="O331" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="P331" t="n">
         <v>0</v>
@@ -25934,22 +25934,22 @@
       </c>
       <c r="V331" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12031.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.jpg</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>12080</v>
+        <v>12098</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>CALDO DE GALINHA</t>
+          <t>CALDO DE LEGUMES</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -25985,10 +25985,10 @@
         </is>
       </c>
       <c r="N332" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O332" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P332" t="n">
         <v>0</v>
@@ -26011,22 +26011,22 @@
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12080.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>12098</v>
+        <v>12105</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>CALDO DE LEGUMES</t>
+          <t>EDU GUEDES</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -26062,10 +26062,10 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O333" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P333" t="n">
         <v>0</v>
@@ -26088,22 +26088,22 @@
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12098.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>12105</v>
+        <v>12106</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>EDU GUEDES</t>
+          <t>ANA MARIA</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -26139,10 +26139,10 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="O334" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="P334" t="n">
         <v>0</v>
@@ -26165,22 +26165,22 @@
       </c>
       <c r="V334" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12105.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>12106</v>
+        <v>12107</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>ANA MARIA</t>
+          <t>CEBOLA, ALHO E SALSA</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -26216,10 +26216,10 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="O335" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="P335" t="n">
         <v>0</v>
@@ -26242,22 +26242,22 @@
       </c>
       <c r="V335" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12106.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>12107</v>
+        <v>12108</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CEBOLA, ALHO E SALSA</t>
+          <t>CHIMICHURRI SEM PIMENTA</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -26293,10 +26293,10 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="O336" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P336" t="n">
         <v>0</v>
@@ -26319,22 +26319,22 @@
       </c>
       <c r="V336" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12107.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>12108</v>
+        <v>12109</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>CHIMICHURRI SEM PIMENTA</t>
+          <t>CHIMICHURRI COM PIMENTA</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -26396,22 +26396,22 @@
       </c>
       <c r="V337" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12108.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12109.webp</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>12109</v>
+        <v>12096</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>CHIMICHURRI COM PIMENTA</t>
+          <t>PEGA MARIDO FIT</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -26447,10 +26447,10 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="O338" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P338" t="n">
         <v>0</v>
@@ -26473,22 +26473,22 @@
       </c>
       <c r="V338" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12109.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.jpg</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>12096</v>
+        <v>12097</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>PEGA MARIDO FIT</t>
+          <t>EDU GUEDES FIT</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -26524,10 +26524,10 @@
         </is>
       </c>
       <c r="N339" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="O339" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="P339" t="n">
         <v>0</v>
@@ -26550,22 +26550,22 @@
       </c>
       <c r="V339" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12096.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12097.jpg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>12097</v>
+        <v>12119</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>EDU GUEDES FIT</t>
+          <t>CEBOLA GRANULADA</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -26601,10 +26601,10 @@
         </is>
       </c>
       <c r="N340" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O340" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P340" t="n">
         <v>0</v>
@@ -26627,22 +26627,22 @@
       </c>
       <c r="V340" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12097.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.jpg</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>12119</v>
+        <v>12115</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>CEBOLA GRANULADA</t>
+          <t>LEMON PEPPER C/ GLUTAMATO</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -26678,10 +26678,10 @@
         </is>
       </c>
       <c r="N341" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O341" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P341" t="n">
         <v>0</v>
@@ -26704,22 +26704,22 @@
       </c>
       <c r="V341" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12119.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.png</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>12115</v>
+        <v>12145</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>LEMON PEPPER C/ GLUTAMATO</t>
+          <t>CHIMICHURRI FIT</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -26755,10 +26755,10 @@
         </is>
       </c>
       <c r="N342" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O342" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P342" t="n">
         <v>0</v>
@@ -26781,22 +26781,22 @@
       </c>
       <c r="V342" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12115.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.webp</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>12145</v>
+        <v>12146</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>CHIMICHURRI FIT</t>
+          <t>CHIMICHURRI C/ PIMENTA FIT</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -26858,22 +26858,22 @@
       </c>
       <c r="V343" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12145.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.webp</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>12146</v>
+        <v>12147</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>716</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>CHIMICHURRI C/ PIMENTA FIT</t>
+          <t>LEMON PEPPER FIT</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -26909,10 +26909,10 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="O344" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P344" t="n">
         <v>0</v>
@@ -26935,22 +26935,22 @@
       </c>
       <c r="V344" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12146.webp</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.jpg</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>12147</v>
+        <v>12148</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>LEMON PEPPER FIT</t>
+          <t>TEMPERO ANA MARIA FIT</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -26986,10 +26986,10 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="O345" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="P345" t="n">
         <v>0</v>
@@ -27012,37 +27012,37 @@
       </c>
       <c r="V345" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12147.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>12148</v>
+        <v>12160</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>TEMPERO ANA MARIA FIT</t>
+          <t>MOSTARDA GRAO MARROM 100G</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UNID</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H346" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I346" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J346" t="n">
         <v>100</v>
@@ -27063,10 +27063,10 @@
         </is>
       </c>
       <c r="N346" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="O346" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="P346" t="n">
         <v>0</v>
@@ -27080,46 +27080,46 @@
         </is>
       </c>
       <c r="T346" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U346" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12148.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>12160</v>
+        <v>12161</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>MOSTARDA GRAO MARROM 100G</t>
+          <t>NOZ MOSCADA PO CONDIMENTADA</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>UNID</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H347" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I347" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J347" t="n">
         <v>100</v>
@@ -27140,10 +27140,10 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="O347" t="n">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="P347" t="n">
         <v>0</v>
@@ -27157,31 +27157,31 @@
         </is>
       </c>
       <c r="T347" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U347" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="V347" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12160.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>12161</v>
+        <v>12164</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>NOZ MOSCADA PO CONDIMENTADA</t>
+          <t>PIMENTA JAMAICA (SIRIA PO)</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -27217,10 +27217,10 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="O348" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="P348" t="n">
         <v>0</v>
@@ -27242,83 +27242,6 @@
         </is>
       </c>
       <c r="V348" t="inlineStr">
-        <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12161.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>12164</v>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>PIMENTA JAMAICA (SIRIA PO)</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="G349" t="n">
-        <v>10</v>
-      </c>
-      <c r="H349" t="n">
-        <v>10</v>
-      </c>
-      <c r="I349" t="n">
-        <v>5</v>
-      </c>
-      <c r="J349" t="n">
-        <v>100</v>
-      </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>TEMPEROS A GRANEL</t>
-        </is>
-      </c>
-      <c r="N349" t="n">
-        <v>85</v>
-      </c>
-      <c r="O349" t="n">
-        <v>85</v>
-      </c>
-      <c r="P349" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
-      <c r="S349" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="T349" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U349" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
-      <c r="V349" t="inlineStr">
         <is>
           <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/12164.jpg</t>
         </is>

--- a/PLANILHA-FOTOS-NOVAS-355.xlsx
+++ b/PLANILHA-FOTOS-NOVAS-355.xlsx
@@ -11535,7 +11535,7 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/farinaceos/11769.jpg</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.jpg</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/frutas-secas/11509.png</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.png</t>
+          <t>https://rodrigo2612jr.github.io/pascoto-fotos-novas/temperos/11497.jpg</t>
         </is>
       </c>
     </row>
